--- a/research/traditional_assets/database/data/ireland/ireland_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_beverage_alcoholic.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="lse_ccr" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.105</v>
+        <v>0.237</v>
+      </c>
+      <c r="F2">
+        <v>0.36</v>
       </c>
       <c r="G2">
-        <v>-0.07408341742347796</v>
+        <v>0.0505955891024885</v>
       </c>
       <c r="H2">
-        <v>-0.07408341742347796</v>
+        <v>0.0505955891024885</v>
       </c>
       <c r="I2">
-        <v>-0.05785401950891355</v>
+        <v>0.04959311239532964</v>
       </c>
       <c r="J2">
-        <v>-0.05785401950891355</v>
+        <v>0.03942323409954431</v>
       </c>
       <c r="K2">
-        <v>-74.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.06273124789774638</v>
+        <v>0.03886071470692299</v>
       </c>
       <c r="M2">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0003838022442673606</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.006327077747989276</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0003838022442673606</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.006327077747989276</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>105.1</v>
+        <v>132.7</v>
       </c>
       <c r="V2">
-        <v>0.08546105057732964</v>
+        <v>0.1604788970855001</v>
       </c>
       <c r="W2">
-        <v>-0.1209076175040519</v>
+        <v>0.0870771670190275</v>
       </c>
       <c r="X2">
-        <v>0.06842952535049954</v>
+        <v>0.1159637161761251</v>
       </c>
       <c r="Y2">
-        <v>-0.1893371428545514</v>
+        <v>-0.02888654915709758</v>
       </c>
       <c r="Z2">
-        <v>2.697822141560798</v>
+        <v>3.97701688555347</v>
       </c>
       <c r="AA2">
-        <v>-0.1560798548094374</v>
+        <v>0.1567868676970151</v>
       </c>
       <c r="AB2">
-        <v>0.05927366314306265</v>
+        <v>0.09938243769180009</v>
       </c>
       <c r="AC2">
-        <v>-0.2153535179525</v>
+        <v>0.05740443000521496</v>
       </c>
       <c r="AD2">
-        <v>395.2</v>
+        <v>313.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>395.2</v>
+        <v>313.7</v>
       </c>
       <c r="AG2">
-        <v>290.1</v>
+        <v>181</v>
       </c>
       <c r="AH2">
-        <v>0.2432</v>
+        <v>0.2750306856040681</v>
       </c>
       <c r="AI2">
-        <v>0.3430555555555556</v>
+        <v>0.2977976077463451</v>
       </c>
       <c r="AJ2">
-        <v>0.1908678202513323</v>
+        <v>0.1795813076694117</v>
       </c>
       <c r="AK2">
-        <v>0.27710383035629</v>
+        <v>0.1965895514282611</v>
       </c>
       <c r="AL2">
-        <v>17.5</v>
+        <v>11.8</v>
       </c>
       <c r="AM2">
-        <v>17.5</v>
+        <v>10.894</v>
       </c>
       <c r="AN2">
-        <v>-7.133574007220217</v>
+        <v>2.674339300937767</v>
       </c>
       <c r="AO2">
-        <v>-3.931428571428571</v>
+        <v>7.127118644067796</v>
       </c>
       <c r="AP2">
-        <v>-5.236462093862817</v>
+        <v>1.54305200341006</v>
       </c>
       <c r="AQ2">
-        <v>-3.931428571428571</v>
+        <v>7.719845786671562</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +721,8830 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.105</v>
+        <v>0.237</v>
+      </c>
+      <c r="F3">
+        <v>0.36</v>
       </c>
       <c r="G3">
-        <v>-0.07408341742347796</v>
+        <v>0.0505955891024885</v>
       </c>
       <c r="H3">
-        <v>-0.07408341742347796</v>
+        <v>0.0505955891024885</v>
       </c>
       <c r="I3">
-        <v>-0.05785401950891355</v>
+        <v>0.04959311239532964</v>
       </c>
       <c r="J3">
-        <v>-0.05785401950891355</v>
+        <v>0.03942323409954431</v>
       </c>
       <c r="K3">
-        <v>-74.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.06273124789774638</v>
+        <v>0.03886071470692299</v>
       </c>
       <c r="M3">
-        <v>0.472</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0003838022442673606</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.006327077747989276</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.472</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0003838022442673606</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.006327077747989276</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>132.7</v>
+      </c>
+      <c r="V3">
+        <v>0.1604788970855001</v>
+      </c>
+      <c r="W3">
+        <v>0.0870771670190275</v>
+      </c>
+      <c r="X3">
+        <v>0.1159637161761251</v>
+      </c>
+      <c r="Y3">
+        <v>-0.02888654915709758</v>
+      </c>
+      <c r="Z3">
+        <v>3.97701688555347</v>
+      </c>
+      <c r="AA3">
+        <v>0.1567868676970151</v>
+      </c>
+      <c r="AB3">
+        <v>0.09938243769180009</v>
+      </c>
+      <c r="AC3">
+        <v>0.05740443000521496</v>
+      </c>
+      <c r="AD3">
+        <v>313.7</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>313.7</v>
+      </c>
+      <c r="AG3">
+        <v>181</v>
+      </c>
+      <c r="AH3">
+        <v>0.2750306856040681</v>
+      </c>
+      <c r="AI3">
+        <v>0.2977976077463451</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1795813076694117</v>
+      </c>
+      <c r="AK3">
+        <v>0.1965895514282611</v>
+      </c>
+      <c r="AL3">
+        <v>11.8</v>
+      </c>
+      <c r="AM3">
+        <v>10.894</v>
+      </c>
+      <c r="AN3">
+        <v>2.674339300937767</v>
+      </c>
+      <c r="AO3">
+        <v>7.127118644067796</v>
+      </c>
+      <c r="AP3">
+        <v>1.54305200341006</v>
+      </c>
+      <c r="AQ3">
+        <v>7.719845786671562</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C&amp;C Group plc (LSE:CCR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LSE:CCR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Beverage (Alcoholic)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.275030685604068</v>
+      </c>
+      <c r="F2">
+        <v>0.12</v>
+      </c>
+      <c r="G2">
+        <v>826.9</v>
+      </c>
+      <c r="H2">
+        <v>1040.05596886146</v>
+      </c>
+      <c r="I2">
+        <v>1007.9</v>
+      </c>
+      <c r="J2">
+        <v>1044.22796886146</v>
+      </c>
+      <c r="K2">
+        <v>313.7</v>
+      </c>
+      <c r="L2">
+        <v>136.872</v>
+      </c>
+      <c r="M2">
+        <v>0.09938243769180009</v>
+      </c>
+      <c r="N2">
+        <v>0.0960065004107975</v>
+      </c>
+      <c r="O2">
+        <v>0.0556748853211009</v>
+      </c>
+      <c r="P2">
+        <v>0.0399875</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.115963716176125</v>
+      </c>
+      <c r="T2">
+        <v>0.10364545501227</v>
+      </c>
+      <c r="U2">
+        <v>1.08202921700538</v>
+      </c>
+      <c r="V2">
+        <v>0.909296239091625</v>
+      </c>
+      <c r="W2">
+        <v>13.63698044703205</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>826.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.06362844036697247</v>
+      </c>
+      <c r="AD2">
+        <v>0.125</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>117.3</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>9.060000000000002</v>
+      </c>
+      <c r="AJ2">
+        <v>313.7</v>
+      </c>
+      <c r="AK2">
+        <v>313.7</v>
+      </c>
+      <c r="AL2">
+        <v>11.8</v>
+      </c>
+      <c r="AM2">
+        <v>313.7</v>
+      </c>
+      <c r="AN2">
+        <v>132.7</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09673299534091119</v>
+      </c>
+      <c r="C2">
+        <v>1168.890827017516</v>
+      </c>
+      <c r="D2">
+        <v>1036.190827017516</v>
+      </c>
+      <c r="E2">
+        <v>-313.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>132.7</v>
+      </c>
+      <c r="H2">
+        <v>826.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>117.3</v>
+      </c>
+      <c r="K2">
+        <v>32</v>
+      </c>
+      <c r="L2">
+        <v>85.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>85.3</v>
+      </c>
+      <c r="O2">
+        <v>10.6625</v>
+      </c>
+      <c r="P2">
+        <v>74.6375</v>
+      </c>
+      <c r="Q2">
+        <v>106.6375</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09673299534091119</v>
+      </c>
+      <c r="T2">
+        <v>0.8123661831478475</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.125</v>
+      </c>
+      <c r="W2">
+        <v>0.0399875</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09667245409673506</v>
+      </c>
+      <c r="C3">
+        <v>1158.149860409835</v>
+      </c>
+      <c r="D3">
+        <v>1036.855860409835</v>
+      </c>
+      <c r="E3">
+        <v>-302.294</v>
+      </c>
+      <c r="F3">
+        <v>11.406</v>
+      </c>
+      <c r="G3">
+        <v>132.7</v>
+      </c>
+      <c r="H3">
+        <v>826.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>117.3</v>
+      </c>
+      <c r="K3">
+        <v>32</v>
+      </c>
+      <c r="L3">
+        <v>85.3</v>
+      </c>
+      <c r="M3">
+        <v>0.5212542</v>
+      </c>
+      <c r="N3">
+        <v>84.7787458</v>
+      </c>
+      <c r="O3">
+        <v>10.597343225</v>
+      </c>
+      <c r="P3">
+        <v>74.18140257499999</v>
+      </c>
+      <c r="Q3">
+        <v>106.181402575</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09724502939064147</v>
+      </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.819546187291831</v>
       </c>
       <c r="U3">
-        <v>105.1</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.08546105057732964</v>
+        <v>0.125</v>
       </c>
       <c r="W3">
-        <v>-0.1209076175040519</v>
-      </c>
-      <c r="X3">
-        <v>0.06842952535049954</v>
+        <v>0.0399875</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.1893371428545514</v>
+        <v>163.6437653643846</v>
       </c>
       <c r="Z3">
-        <v>2.697822141560798</v>
-      </c>
-      <c r="AA3">
-        <v>-0.1560798548094374</v>
-      </c>
-      <c r="AB3">
-        <v>0.05927366314306265</v>
-      </c>
-      <c r="AC3">
-        <v>-0.2153535179525</v>
-      </c>
-      <c r="AD3">
-        <v>395.2</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>395.2</v>
-      </c>
-      <c r="AG3">
-        <v>290.1</v>
-      </c>
-      <c r="AH3">
-        <v>0.2432</v>
-      </c>
-      <c r="AI3">
-        <v>0.3430555555555556</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1908678202513323</v>
-      </c>
-      <c r="AK3">
-        <v>0.27710383035629</v>
-      </c>
-      <c r="AL3">
-        <v>17.5</v>
-      </c>
-      <c r="AM3">
-        <v>17.5</v>
-      </c>
-      <c r="AN3">
-        <v>-7.133574007220217</v>
-      </c>
-      <c r="AO3">
-        <v>-3.931428571428571</v>
-      </c>
-      <c r="AP3">
-        <v>-5.236462093862817</v>
-      </c>
-      <c r="AQ3">
-        <v>-3.931428571428571</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09661191285255892</v>
+      </c>
+      <c r="C4">
+        <v>1147.409747995097</v>
+      </c>
+      <c r="D4">
+        <v>1037.521747995097</v>
+      </c>
+      <c r="E4">
+        <v>-290.888</v>
+      </c>
+      <c r="F4">
+        <v>22.812</v>
+      </c>
+      <c r="G4">
+        <v>132.7</v>
+      </c>
+      <c r="H4">
+        <v>826.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>117.3</v>
+      </c>
+      <c r="K4">
+        <v>32</v>
+      </c>
+      <c r="L4">
+        <v>85.3</v>
+      </c>
+      <c r="M4">
+        <v>1.0425084</v>
+      </c>
+      <c r="N4">
+        <v>84.25749159999999</v>
+      </c>
+      <c r="O4">
+        <v>10.53218645</v>
+      </c>
+      <c r="P4">
+        <v>73.72530515</v>
+      </c>
+      <c r="Q4">
+        <v>105.72530515</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09776751311485604</v>
+      </c>
+      <c r="T4">
+        <v>0.8268727221326304</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.125</v>
+      </c>
+      <c r="W4">
+        <v>0.0399875</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>81.8218826821923</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09655137160838277</v>
+      </c>
+      <c r="C5">
+        <v>1136.670491420095</v>
+      </c>
+      <c r="D5">
+        <v>1038.188491420095</v>
+      </c>
+      <c r="E5">
+        <v>-279.482</v>
+      </c>
+      <c r="F5">
+        <v>34.218</v>
+      </c>
+      <c r="G5">
+        <v>132.7</v>
+      </c>
+      <c r="H5">
+        <v>826.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>117.3</v>
+      </c>
+      <c r="K5">
+        <v>32</v>
+      </c>
+      <c r="L5">
+        <v>85.3</v>
+      </c>
+      <c r="M5">
+        <v>1.5637626</v>
+      </c>
+      <c r="N5">
+        <v>83.73623739999999</v>
+      </c>
+      <c r="O5">
+        <v>10.467029675</v>
+      </c>
+      <c r="P5">
+        <v>73.269207725</v>
+      </c>
+      <c r="Q5">
+        <v>105.269207725</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09830076969936369</v>
+      </c>
+      <c r="T5">
+        <v>0.834350319547467</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.125</v>
+      </c>
+      <c r="W5">
+        <v>0.0399875</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>54.54792178812819</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09649083036420664</v>
+      </c>
+      <c r="C6">
+        <v>1125.932092335857</v>
+      </c>
+      <c r="D6">
+        <v>1038.856092335857</v>
+      </c>
+      <c r="E6">
+        <v>-268.076</v>
+      </c>
+      <c r="F6">
+        <v>45.624</v>
+      </c>
+      <c r="G6">
+        <v>132.7</v>
+      </c>
+      <c r="H6">
+        <v>826.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>117.3</v>
+      </c>
+      <c r="K6">
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>85.3</v>
+      </c>
+      <c r="M6">
+        <v>2.0850168</v>
+      </c>
+      <c r="N6">
+        <v>83.21498319999999</v>
+      </c>
+      <c r="O6">
+        <v>10.4018729</v>
+      </c>
+      <c r="P6">
+        <v>72.81311029999999</v>
+      </c>
+      <c r="Q6">
+        <v>104.8131103</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09884513579604857</v>
+      </c>
+      <c r="T6">
+        <v>0.8419837002417794</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.125</v>
+      </c>
+      <c r="W6">
+        <v>0.0399875</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>40.91094134109615</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09643028912003049</v>
+      </c>
+      <c r="C7">
+        <v>1115.19455239766</v>
+      </c>
+      <c r="D7">
+        <v>1039.52455239766</v>
+      </c>
+      <c r="E7">
+        <v>-256.67</v>
+      </c>
+      <c r="F7">
+        <v>57.03</v>
+      </c>
+      <c r="G7">
+        <v>132.7</v>
+      </c>
+      <c r="H7">
+        <v>826.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>117.3</v>
+      </c>
+      <c r="K7">
+        <v>32</v>
+      </c>
+      <c r="L7">
+        <v>85.3</v>
+      </c>
+      <c r="M7">
+        <v>2.606271</v>
+      </c>
+      <c r="N7">
+        <v>82.69372899999999</v>
+      </c>
+      <c r="O7">
+        <v>10.336716125</v>
+      </c>
+      <c r="P7">
+        <v>72.357012875</v>
+      </c>
+      <c r="Q7">
+        <v>104.357012875</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09940096223161105</v>
+      </c>
+      <c r="T7">
+        <v>0.849777783687551</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.125</v>
+      </c>
+      <c r="W7">
+        <v>0.0399875</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>32.72875307287691</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09636974787585437</v>
+      </c>
+      <c r="C8">
+        <v>1104.457873265043</v>
+      </c>
+      <c r="D8">
+        <v>1040.193873265043</v>
+      </c>
+      <c r="E8">
+        <v>-245.264</v>
+      </c>
+      <c r="F8">
+        <v>68.43599999999999</v>
+      </c>
+      <c r="G8">
+        <v>132.7</v>
+      </c>
+      <c r="H8">
+        <v>826.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>117.3</v>
+      </c>
+      <c r="K8">
+        <v>32</v>
+      </c>
+      <c r="L8">
+        <v>85.3</v>
+      </c>
+      <c r="M8">
+        <v>3.1275252</v>
+      </c>
+      <c r="N8">
+        <v>82.1724748</v>
+      </c>
+      <c r="O8">
+        <v>10.27155935</v>
+      </c>
+      <c r="P8">
+        <v>71.90091545</v>
+      </c>
+      <c r="Q8">
+        <v>103.90091545</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0999686147615472</v>
+      </c>
+      <c r="T8">
+        <v>0.8577376986959986</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.125</v>
+      </c>
+      <c r="W8">
+        <v>0.0399875</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>27.2739608940641</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09630920663167822</v>
+      </c>
+      <c r="C9">
+        <v>1093.722056601826</v>
+      </c>
+      <c r="D9">
+        <v>1040.864056601826</v>
+      </c>
+      <c r="E9">
+        <v>-233.858</v>
+      </c>
+      <c r="F9">
+        <v>79.842</v>
+      </c>
+      <c r="G9">
+        <v>132.7</v>
+      </c>
+      <c r="H9">
+        <v>826.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>117.3</v>
+      </c>
+      <c r="K9">
+        <v>32</v>
+      </c>
+      <c r="L9">
+        <v>85.3</v>
+      </c>
+      <c r="M9">
+        <v>3.6487794</v>
+      </c>
+      <c r="N9">
+        <v>81.6512206</v>
+      </c>
+      <c r="O9">
+        <v>10.206402575</v>
+      </c>
+      <c r="P9">
+        <v>71.444818025</v>
+      </c>
+      <c r="Q9">
+        <v>103.444818025</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1005484748727723</v>
+      </c>
+      <c r="T9">
+        <v>0.8658687946723698</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.125</v>
+      </c>
+      <c r="W9">
+        <v>0.0399875</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>23.37768076634065</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.0962486653875021</v>
+      </c>
+      <c r="C10">
+        <v>1082.987104076115</v>
+      </c>
+      <c r="D10">
+        <v>1041.535104076115</v>
+      </c>
+      <c r="E10">
+        <v>-222.452</v>
+      </c>
+      <c r="F10">
+        <v>91.24799999999999</v>
+      </c>
+      <c r="G10">
+        <v>132.7</v>
+      </c>
+      <c r="H10">
+        <v>826.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>117.3</v>
+      </c>
+      <c r="K10">
+        <v>32</v>
+      </c>
+      <c r="L10">
+        <v>85.3</v>
+      </c>
+      <c r="M10">
+        <v>4.1700336</v>
+      </c>
+      <c r="N10">
+        <v>81.1299664</v>
+      </c>
+      <c r="O10">
+        <v>10.1412458</v>
+      </c>
+      <c r="P10">
+        <v>70.98872059999999</v>
+      </c>
+      <c r="Q10">
+        <v>102.9887206</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1011409406385892</v>
+      </c>
+      <c r="T10">
+        <v>0.8741766536047491</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.125</v>
+      </c>
+      <c r="W10">
+        <v>0.0399875</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>20.45547067054807</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09618812414332595</v>
+      </c>
+      <c r="C11">
+        <v>1072.253017360325</v>
+      </c>
+      <c r="D11">
+        <v>1042.207017360325</v>
+      </c>
+      <c r="E11">
+        <v>-211.046</v>
+      </c>
+      <c r="F11">
+        <v>102.654</v>
+      </c>
+      <c r="G11">
+        <v>132.7</v>
+      </c>
+      <c r="H11">
+        <v>826.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>117.3</v>
+      </c>
+      <c r="K11">
+        <v>32</v>
+      </c>
+      <c r="L11">
+        <v>85.3</v>
+      </c>
+      <c r="M11">
+        <v>4.6912878</v>
+      </c>
+      <c r="N11">
+        <v>80.6087122</v>
+      </c>
+      <c r="O11">
+        <v>10.076089025</v>
+      </c>
+      <c r="P11">
+        <v>70.532623175</v>
+      </c>
+      <c r="Q11">
+        <v>102.532623175</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1017464276300285</v>
+      </c>
+      <c r="T11">
+        <v>0.8826671028433342</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.125</v>
+      </c>
+      <c r="W11">
+        <v>0.0399875</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>18.18264059604273</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0961275828991498</v>
+      </c>
+      <c r="C12">
+        <v>1061.519798131185</v>
+      </c>
+      <c r="D12">
+        <v>1042.879798131185</v>
+      </c>
+      <c r="E12">
+        <v>-199.64</v>
+      </c>
+      <c r="F12">
+        <v>114.06</v>
+      </c>
+      <c r="G12">
+        <v>132.7</v>
+      </c>
+      <c r="H12">
+        <v>826.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>117.3</v>
+      </c>
+      <c r="K12">
+        <v>32</v>
+      </c>
+      <c r="L12">
+        <v>85.3</v>
+      </c>
+      <c r="M12">
+        <v>5.212542000000001</v>
+      </c>
+      <c r="N12">
+        <v>80.087458</v>
+      </c>
+      <c r="O12">
+        <v>10.01093225</v>
+      </c>
+      <c r="P12">
+        <v>70.07652575</v>
+      </c>
+      <c r="Q12">
+        <v>102.07652575</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1023653698879442</v>
+      </c>
+      <c r="T12">
+        <v>0.891346228731666</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.125</v>
+      </c>
+      <c r="W12">
+        <v>0.0399875</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>16.36437653643846</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09606704165497366</v>
+      </c>
+      <c r="C13">
+        <v>1050.787448069758</v>
+      </c>
+      <c r="D13">
+        <v>1043.553448069758</v>
+      </c>
+      <c r="E13">
+        <v>-188.234</v>
+      </c>
+      <c r="F13">
+        <v>125.466</v>
+      </c>
+      <c r="G13">
+        <v>132.7</v>
+      </c>
+      <c r="H13">
+        <v>826.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>117.3</v>
+      </c>
+      <c r="K13">
+        <v>32</v>
+      </c>
+      <c r="L13">
+        <v>85.3</v>
+      </c>
+      <c r="M13">
+        <v>5.7337962</v>
+      </c>
+      <c r="N13">
+        <v>79.5662038</v>
+      </c>
+      <c r="O13">
+        <v>9.945775475</v>
+      </c>
+      <c r="P13">
+        <v>69.62042832499999</v>
+      </c>
+      <c r="Q13">
+        <v>101.620428325</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1029982209606446</v>
+      </c>
+      <c r="T13">
+        <v>0.9002203911568142</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.125</v>
+      </c>
+      <c r="W13">
+        <v>0.0399875</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.87670594221678</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09600650041079753</v>
+      </c>
+      <c r="C14">
+        <v>1040.055968861455</v>
+      </c>
+      <c r="D14">
+        <v>1044.227968861455</v>
+      </c>
+      <c r="E14">
+        <v>-176.828</v>
+      </c>
+      <c r="F14">
+        <v>136.872</v>
+      </c>
+      <c r="G14">
+        <v>132.7</v>
+      </c>
+      <c r="H14">
+        <v>826.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>117.3</v>
+      </c>
+      <c r="K14">
+        <v>32</v>
+      </c>
+      <c r="L14">
+        <v>85.3</v>
+      </c>
+      <c r="M14">
+        <v>6.2550504</v>
+      </c>
+      <c r="N14">
+        <v>79.0449496</v>
+      </c>
+      <c r="O14">
+        <v>9.880618699999999</v>
+      </c>
+      <c r="P14">
+        <v>69.1643309</v>
+      </c>
+      <c r="Q14">
+        <v>101.1643309</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1036454550122699</v>
+      </c>
+      <c r="T14">
+        <v>0.9092962390916248</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.125</v>
+      </c>
+      <c r="W14">
+        <v>0.0399875</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.63698044703205</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.0961279591666214</v>
+      </c>
+      <c r="C15">
+        <v>1027.297614075819</v>
+      </c>
+      <c r="D15">
+        <v>1042.875614075819</v>
+      </c>
+      <c r="E15">
+        <v>-165.422</v>
+      </c>
+      <c r="F15">
+        <v>148.278</v>
+      </c>
+      <c r="G15">
+        <v>132.7</v>
+      </c>
+      <c r="H15">
+        <v>826.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>117.3</v>
+      </c>
+      <c r="K15">
+        <v>32</v>
+      </c>
+      <c r="L15">
+        <v>85.3</v>
+      </c>
+      <c r="M15">
+        <v>7.0135494</v>
+      </c>
+      <c r="N15">
+        <v>78.28645059999999</v>
+      </c>
+      <c r="O15">
+        <v>9.785806324999999</v>
+      </c>
+      <c r="P15">
+        <v>68.500644275</v>
+      </c>
+      <c r="Q15">
+        <v>100.500644275</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1043075680076108</v>
+      </c>
+      <c r="T15">
+        <v>0.9185807272088448</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.125</v>
+      </c>
+      <c r="W15">
+        <v>0.0413875</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>12.16217283648134</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09608141792244525</v>
+      </c>
+      <c r="C16">
+        <v>1016.409402775748</v>
+      </c>
+      <c r="D16">
+        <v>1043.393402775748</v>
+      </c>
+      <c r="E16">
+        <v>-154.016</v>
+      </c>
+      <c r="F16">
+        <v>159.684</v>
+      </c>
+      <c r="G16">
+        <v>132.7</v>
+      </c>
+      <c r="H16">
+        <v>826.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>117.3</v>
+      </c>
+      <c r="K16">
+        <v>32</v>
+      </c>
+      <c r="L16">
+        <v>85.3</v>
+      </c>
+      <c r="M16">
+        <v>7.5530532</v>
+      </c>
+      <c r="N16">
+        <v>77.7469468</v>
+      </c>
+      <c r="O16">
+        <v>9.71836835</v>
+      </c>
+      <c r="P16">
+        <v>68.02857845</v>
+      </c>
+      <c r="Q16">
+        <v>100.02857845</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1049850789795875</v>
+      </c>
+      <c r="T16">
+        <v>0.9280811336543723</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.125</v>
+      </c>
+      <c r="W16">
+        <v>0.0413875</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.2934462053041</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.0960348766782691</v>
+      </c>
+      <c r="C17">
+        <v>1005.521705896217</v>
+      </c>
+      <c r="D17">
+        <v>1043.911705896217</v>
+      </c>
+      <c r="E17">
+        <v>-142.61</v>
+      </c>
+      <c r="F17">
+        <v>171.09</v>
+      </c>
+      <c r="G17">
+        <v>132.7</v>
+      </c>
+      <c r="H17">
+        <v>826.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>117.3</v>
+      </c>
+      <c r="K17">
+        <v>32</v>
+      </c>
+      <c r="L17">
+        <v>85.3</v>
+      </c>
+      <c r="M17">
+        <v>8.092556999999999</v>
+      </c>
+      <c r="N17">
+        <v>77.207443</v>
+      </c>
+      <c r="O17">
+        <v>9.650930375</v>
+      </c>
+      <c r="P17">
+        <v>67.556512625</v>
+      </c>
+      <c r="Q17">
+        <v>99.556512625</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.105678531386199</v>
+      </c>
+      <c r="T17">
+        <v>0.9378050790750886</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.125</v>
+      </c>
+      <c r="W17">
+        <v>0.0413875</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.54054979161716</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09652033543409297</v>
+      </c>
+      <c r="C18">
+        <v>988.734626559689</v>
+      </c>
+      <c r="D18">
+        <v>1038.530626559689</v>
+      </c>
+      <c r="E18">
+        <v>-131.204</v>
+      </c>
+      <c r="F18">
+        <v>182.496</v>
+      </c>
+      <c r="G18">
+        <v>132.7</v>
+      </c>
+      <c r="H18">
+        <v>826.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>117.3</v>
+      </c>
+      <c r="K18">
+        <v>32</v>
+      </c>
+      <c r="L18">
+        <v>85.3</v>
+      </c>
+      <c r="M18">
+        <v>9.325545599999998</v>
+      </c>
+      <c r="N18">
+        <v>75.9744544</v>
+      </c>
+      <c r="O18">
+        <v>9.4968068</v>
+      </c>
+      <c r="P18">
+        <v>66.4776476</v>
+      </c>
+      <c r="Q18">
+        <v>98.4776476</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1063884945643964</v>
+      </c>
+      <c r="T18">
+        <v>0.9477605470058221</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.125</v>
+      </c>
+      <c r="W18">
+        <v>0.0447125</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>9.146917902583631</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09650704418991683</v>
+      </c>
+      <c r="C19">
+        <v>977.4752149346652</v>
+      </c>
+      <c r="D19">
+        <v>1038.677214934665</v>
+      </c>
+      <c r="E19">
+        <v>-119.798</v>
+      </c>
+      <c r="F19">
+        <v>193.902</v>
+      </c>
+      <c r="G19">
+        <v>132.7</v>
+      </c>
+      <c r="H19">
+        <v>826.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>117.3</v>
+      </c>
+      <c r="K19">
+        <v>32</v>
+      </c>
+      <c r="L19">
+        <v>85.3</v>
+      </c>
+      <c r="M19">
+        <v>9.9083922</v>
+      </c>
+      <c r="N19">
+        <v>75.3916078</v>
+      </c>
+      <c r="O19">
+        <v>9.423950975</v>
+      </c>
+      <c r="P19">
+        <v>65.96765682500001</v>
+      </c>
+      <c r="Q19">
+        <v>97.96765682500001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1071155652890564</v>
+      </c>
+      <c r="T19">
+        <v>0.9579559057300672</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.125</v>
+      </c>
+      <c r="W19">
+        <v>0.0447125</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.608863908314005</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.0964937529457407</v>
+      </c>
+      <c r="C20">
+        <v>966.2158446973192</v>
+      </c>
+      <c r="D20">
+        <v>1038.823844697319</v>
+      </c>
+      <c r="E20">
+        <v>-108.392</v>
+      </c>
+      <c r="F20">
+        <v>205.308</v>
+      </c>
+      <c r="G20">
+        <v>132.7</v>
+      </c>
+      <c r="H20">
+        <v>826.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>117.3</v>
+      </c>
+      <c r="K20">
+        <v>32</v>
+      </c>
+      <c r="L20">
+        <v>85.3</v>
+      </c>
+      <c r="M20">
+        <v>10.4912388</v>
+      </c>
+      <c r="N20">
+        <v>74.80876119999999</v>
+      </c>
+      <c r="O20">
+        <v>9.351095149999999</v>
+      </c>
+      <c r="P20">
+        <v>65.45766605</v>
+      </c>
+      <c r="Q20">
+        <v>97.45766605</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1078603694460252</v>
+      </c>
+      <c r="T20">
+        <v>0.9683999317402694</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.125</v>
+      </c>
+      <c r="W20">
+        <v>0.0447125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.13059369118545</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09679633670156457</v>
+      </c>
+      <c r="C21">
+        <v>951.4819474914618</v>
+      </c>
+      <c r="D21">
+        <v>1035.495947491462</v>
+      </c>
+      <c r="E21">
+        <v>-96.98599999999999</v>
+      </c>
+      <c r="F21">
+        <v>216.714</v>
+      </c>
+      <c r="G21">
+        <v>132.7</v>
+      </c>
+      <c r="H21">
+        <v>826.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>117.3</v>
+      </c>
+      <c r="K21">
+        <v>32</v>
+      </c>
+      <c r="L21">
+        <v>85.3</v>
+      </c>
+      <c r="M21">
+        <v>11.485842</v>
+      </c>
+      <c r="N21">
+        <v>73.81415799999999</v>
+      </c>
+      <c r="O21">
+        <v>9.226769749999999</v>
+      </c>
+      <c r="P21">
+        <v>64.58738824999999</v>
+      </c>
+      <c r="Q21">
+        <v>96.58738824999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.108623563829092</v>
+      </c>
+      <c r="T21">
+        <v>0.9791018349359087</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.125</v>
+      </c>
+      <c r="W21">
+        <v>0.04637500000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.426534336794811</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09679967045738842</v>
+      </c>
+      <c r="C22">
+        <v>940.0394007006968</v>
+      </c>
+      <c r="D22">
+        <v>1035.459400700697</v>
+      </c>
+      <c r="E22">
+        <v>-85.57999999999998</v>
+      </c>
+      <c r="F22">
+        <v>228.12</v>
+      </c>
+      <c r="G22">
+        <v>132.7</v>
+      </c>
+      <c r="H22">
+        <v>826.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>117.3</v>
+      </c>
+      <c r="K22">
+        <v>32</v>
+      </c>
+      <c r="L22">
+        <v>85.3</v>
+      </c>
+      <c r="M22">
+        <v>12.09036</v>
+      </c>
+      <c r="N22">
+        <v>73.20963999999999</v>
+      </c>
+      <c r="O22">
+        <v>9.151204999999999</v>
+      </c>
+      <c r="P22">
+        <v>64.05843499999999</v>
+      </c>
+      <c r="Q22">
+        <v>96.05843499999999</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1094058380717355</v>
+      </c>
+      <c r="T22">
+        <v>0.9900712857114391</v>
+      </c>
+      <c r="U22">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.125</v>
+      </c>
+      <c r="W22">
+        <v>0.04637500000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.05520761995507</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09680300421321228</v>
+      </c>
+      <c r="C23">
+        <v>928.5968564896053</v>
+      </c>
+      <c r="D23">
+        <v>1035.422856489605</v>
+      </c>
+      <c r="E23">
+        <v>-74.17400000000001</v>
+      </c>
+      <c r="F23">
+        <v>239.526</v>
+      </c>
+      <c r="G23">
+        <v>132.7</v>
+      </c>
+      <c r="H23">
+        <v>826.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>117.3</v>
+      </c>
+      <c r="K23">
+        <v>32</v>
+      </c>
+      <c r="L23">
+        <v>85.3</v>
+      </c>
+      <c r="M23">
+        <v>12.694878</v>
+      </c>
+      <c r="N23">
+        <v>72.60512199999999</v>
+      </c>
+      <c r="O23">
+        <v>9.075640249999999</v>
+      </c>
+      <c r="P23">
+        <v>63.52948175</v>
+      </c>
+      <c r="Q23">
+        <v>95.52948175</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1102079167255852</v>
+      </c>
+      <c r="T23">
+        <v>1.00131844410154</v>
+      </c>
+      <c r="U23">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.125</v>
+      </c>
+      <c r="W23">
+        <v>0.04637500000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.719245352338163</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09680633796903615</v>
+      </c>
+      <c r="C24">
+        <v>917.1543148579142</v>
+      </c>
+      <c r="D24">
+        <v>1035.386314857914</v>
+      </c>
+      <c r="E24">
+        <v>-62.768</v>
+      </c>
+      <c r="F24">
+        <v>250.932</v>
+      </c>
+      <c r="G24">
+        <v>132.7</v>
+      </c>
+      <c r="H24">
+        <v>826.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>117.3</v>
+      </c>
+      <c r="K24">
+        <v>32</v>
+      </c>
+      <c r="L24">
+        <v>85.3</v>
+      </c>
+      <c r="M24">
+        <v>13.299396</v>
+      </c>
+      <c r="N24">
+        <v>72.000604</v>
+      </c>
+      <c r="O24">
+        <v>9.000075499999999</v>
+      </c>
+      <c r="P24">
+        <v>63.00052849999999</v>
+      </c>
+      <c r="Q24">
+        <v>95.0005285</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1110305614987643</v>
+      </c>
+      <c r="T24">
+        <v>1.01285399116831</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.125</v>
+      </c>
+      <c r="W24">
+        <v>0.04637500000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.413825109050064</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09721217172485999</v>
+      </c>
+      <c r="C25">
+        <v>901.3191161053319</v>
+      </c>
+      <c r="D25">
+        <v>1030.957116105332</v>
+      </c>
+      <c r="E25">
+        <v>-51.36200000000002</v>
+      </c>
+      <c r="F25">
+        <v>262.338</v>
+      </c>
+      <c r="G25">
+        <v>132.7</v>
+      </c>
+      <c r="H25">
+        <v>826.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>117.3</v>
+      </c>
+      <c r="K25">
+        <v>32</v>
+      </c>
+      <c r="L25">
+        <v>85.3</v>
+      </c>
+      <c r="M25">
+        <v>14.42859</v>
+      </c>
+      <c r="N25">
+        <v>70.87141</v>
+      </c>
+      <c r="O25">
+        <v>8.85892625</v>
+      </c>
+      <c r="P25">
+        <v>62.01248375</v>
+      </c>
+      <c r="Q25">
+        <v>94.01248375</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1118745736686493</v>
+      </c>
+      <c r="T25">
+        <v>1.024689162834217</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.125</v>
+      </c>
+      <c r="W25">
+        <v>0.048125</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.911873578776582</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09723300548068387</v>
+      </c>
+      <c r="C26">
+        <v>889.6867625142399</v>
+      </c>
+      <c r="D26">
+        <v>1030.73076251424</v>
+      </c>
+      <c r="E26">
+        <v>-39.95600000000002</v>
+      </c>
+      <c r="F26">
+        <v>273.744</v>
+      </c>
+      <c r="G26">
+        <v>132.7</v>
+      </c>
+      <c r="H26">
+        <v>826.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>117.3</v>
+      </c>
+      <c r="K26">
+        <v>32</v>
+      </c>
+      <c r="L26">
+        <v>85.3</v>
+      </c>
+      <c r="M26">
+        <v>15.05592</v>
+      </c>
+      <c r="N26">
+        <v>70.24408</v>
+      </c>
+      <c r="O26">
+        <v>8.78051</v>
+      </c>
+      <c r="P26">
+        <v>61.46357</v>
+      </c>
+      <c r="Q26">
+        <v>93.46357</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1127407966851103</v>
+      </c>
+      <c r="T26">
+        <v>1.036835786386068</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.125</v>
+      </c>
+      <c r="W26">
+        <v>0.048125</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.665545512994225</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09725383923650771</v>
+      </c>
+      <c r="C27">
+        <v>878.0545082962464</v>
+      </c>
+      <c r="D27">
+        <v>1030.504508296246</v>
+      </c>
+      <c r="E27">
+        <v>-28.55000000000001</v>
+      </c>
+      <c r="F27">
+        <v>285.15</v>
+      </c>
+      <c r="G27">
+        <v>132.7</v>
+      </c>
+      <c r="H27">
+        <v>826.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>117.3</v>
+      </c>
+      <c r="K27">
+        <v>32</v>
+      </c>
+      <c r="L27">
+        <v>85.3</v>
+      </c>
+      <c r="M27">
+        <v>15.68325</v>
+      </c>
+      <c r="N27">
+        <v>69.61675</v>
+      </c>
+      <c r="O27">
+        <v>8.70209375</v>
+      </c>
+      <c r="P27">
+        <v>60.91465624999999</v>
+      </c>
+      <c r="Q27">
+        <v>92.91465624999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1136301189820103</v>
+      </c>
+      <c r="T27">
+        <v>1.049306319899303</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.125</v>
+      </c>
+      <c r="W27">
+        <v>0.048125</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.438923692474456</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09727467299233157</v>
+      </c>
+      <c r="C28">
+        <v>866.4223533859258</v>
+      </c>
+      <c r="D28">
+        <v>1030.278353385926</v>
+      </c>
+      <c r="E28">
+        <v>-17.14400000000001</v>
+      </c>
+      <c r="F28">
+        <v>296.556</v>
+      </c>
+      <c r="G28">
+        <v>132.7</v>
+      </c>
+      <c r="H28">
+        <v>826.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>117.3</v>
+      </c>
+      <c r="K28">
+        <v>32</v>
+      </c>
+      <c r="L28">
+        <v>85.3</v>
+      </c>
+      <c r="M28">
+        <v>16.31058</v>
+      </c>
+      <c r="N28">
+        <v>68.98942</v>
+      </c>
+      <c r="O28">
+        <v>8.623677499999999</v>
+      </c>
+      <c r="P28">
+        <v>60.3657425</v>
+      </c>
+      <c r="Q28">
+        <v>92.3657425</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1145434770166643</v>
+      </c>
+      <c r="T28">
+        <v>1.062113894858841</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.125</v>
+      </c>
+      <c r="W28">
+        <v>0.048125</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.229734319686976</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09729550674815544</v>
+      </c>
+      <c r="C29">
+        <v>854.7902977179103</v>
+      </c>
+      <c r="D29">
+        <v>1030.05229771791</v>
+      </c>
+      <c r="E29">
+        <v>-5.738</v>
+      </c>
+      <c r="F29">
+        <v>307.962</v>
+      </c>
+      <c r="G29">
+        <v>132.7</v>
+      </c>
+      <c r="H29">
+        <v>826.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>117.3</v>
+      </c>
+      <c r="K29">
+        <v>32</v>
+      </c>
+      <c r="L29">
+        <v>85.3</v>
+      </c>
+      <c r="M29">
+        <v>16.93791</v>
+      </c>
+      <c r="N29">
+        <v>68.36208999999999</v>
+      </c>
+      <c r="O29">
+        <v>8.545261249999999</v>
+      </c>
+      <c r="P29">
+        <v>59.81682875</v>
+      </c>
+      <c r="Q29">
+        <v>91.81682875</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1154818585591171</v>
+      </c>
+      <c r="T29">
+        <v>1.075272362283024</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.125</v>
+      </c>
+      <c r="W29">
+        <v>0.048125</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.036040455994866</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.0973163405039793</v>
+      </c>
+      <c r="C30">
+        <v>843.1583412268892</v>
+      </c>
+      <c r="D30">
+        <v>1029.826341226889</v>
+      </c>
+      <c r="E30">
+        <v>5.668000000000006</v>
+      </c>
+      <c r="F30">
+        <v>319.368</v>
+      </c>
+      <c r="G30">
+        <v>132.7</v>
+      </c>
+      <c r="H30">
+        <v>826.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>117.3</v>
+      </c>
+      <c r="K30">
+        <v>32</v>
+      </c>
+      <c r="L30">
+        <v>85.3</v>
+      </c>
+      <c r="M30">
+        <v>17.56524</v>
+      </c>
+      <c r="N30">
+        <v>67.73475999999999</v>
+      </c>
+      <c r="O30">
+        <v>8.466844999999999</v>
+      </c>
+      <c r="P30">
+        <v>59.267915</v>
+      </c>
+      <c r="Q30">
+        <v>91.26791499999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1164463062555268</v>
+      </c>
+      <c r="T30">
+        <v>1.088796342691212</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.125</v>
+      </c>
+      <c r="W30">
+        <v>0.048125</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.856181868280764</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09733717425980315</v>
+      </c>
+      <c r="C31">
+        <v>831.5264838476098</v>
+      </c>
+      <c r="D31">
+        <v>1029.60048384761</v>
+      </c>
+      <c r="E31">
+        <v>17.07399999999996</v>
+      </c>
+      <c r="F31">
+        <v>330.7739999999999</v>
+      </c>
+      <c r="G31">
+        <v>132.7</v>
+      </c>
+      <c r="H31">
+        <v>826.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>117.3</v>
+      </c>
+      <c r="K31">
+        <v>32</v>
+      </c>
+      <c r="L31">
+        <v>85.3</v>
+      </c>
+      <c r="M31">
+        <v>18.19257</v>
+      </c>
+      <c r="N31">
+        <v>67.10742999999999</v>
+      </c>
+      <c r="O31">
+        <v>8.388428749999999</v>
+      </c>
+      <c r="P31">
+        <v>58.71900124999999</v>
+      </c>
+      <c r="Q31">
+        <v>90.71900124999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1174379214926805</v>
+      </c>
+      <c r="T31">
+        <v>1.102701280293997</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.125</v>
+      </c>
+      <c r="W31">
+        <v>0.048125</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.688727321098669</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09735800801562702</v>
+      </c>
+      <c r="C32">
+        <v>819.8947255148749</v>
+      </c>
+      <c r="D32">
+        <v>1029.374725514875</v>
+      </c>
+      <c r="E32">
+        <v>28.47999999999996</v>
+      </c>
+      <c r="F32">
+        <v>342.1799999999999</v>
+      </c>
+      <c r="G32">
+        <v>132.7</v>
+      </c>
+      <c r="H32">
+        <v>826.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>117.3</v>
+      </c>
+      <c r="K32">
+        <v>32</v>
+      </c>
+      <c r="L32">
+        <v>85.3</v>
+      </c>
+      <c r="M32">
+        <v>18.8199</v>
+      </c>
+      <c r="N32">
+        <v>66.48009999999999</v>
+      </c>
+      <c r="O32">
+        <v>8.310012499999999</v>
+      </c>
+      <c r="P32">
+        <v>58.17008749999999</v>
+      </c>
+      <c r="Q32">
+        <v>90.17008749999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1184578685937529</v>
+      </c>
+      <c r="T32">
+        <v>1.11700350182829</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.125</v>
+      </c>
+      <c r="W32">
+        <v>0.048125</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.53243641039538</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09840959177145088</v>
+      </c>
+      <c r="C33">
+        <v>797.2207815055465</v>
+      </c>
+      <c r="D33">
+        <v>1018.106781505546</v>
+      </c>
+      <c r="E33">
+        <v>39.88599999999997</v>
+      </c>
+      <c r="F33">
+        <v>353.586</v>
+      </c>
+      <c r="G33">
+        <v>132.7</v>
+      </c>
+      <c r="H33">
+        <v>826.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>117.3</v>
+      </c>
+      <c r="K33">
+        <v>32</v>
+      </c>
+      <c r="L33">
+        <v>85.3</v>
+      </c>
+      <c r="M33">
+        <v>20.7908568</v>
+      </c>
+      <c r="N33">
+        <v>64.5091432</v>
+      </c>
+      <c r="O33">
+        <v>8.0636429</v>
+      </c>
+      <c r="P33">
+        <v>56.4455003</v>
+      </c>
+      <c r="Q33">
+        <v>88.44550029999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1195073793789143</v>
+      </c>
+      <c r="T33">
+        <v>1.131720280508505</v>
+      </c>
+      <c r="U33">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.125</v>
+      </c>
+      <c r="W33">
+        <v>0.05145</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.102765019284823</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09963967552727475</v>
+      </c>
+      <c r="C34">
+        <v>772.9432652329965</v>
+      </c>
+      <c r="D34">
+        <v>1005.235265232996</v>
+      </c>
+      <c r="E34">
+        <v>51.29199999999997</v>
+      </c>
+      <c r="F34">
+        <v>364.992</v>
+      </c>
+      <c r="G34">
+        <v>132.7</v>
+      </c>
+      <c r="H34">
+        <v>826.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>117.3</v>
+      </c>
+      <c r="K34">
+        <v>32</v>
+      </c>
+      <c r="L34">
+        <v>85.3</v>
+      </c>
+      <c r="M34">
+        <v>22.994496</v>
+      </c>
+      <c r="N34">
+        <v>62.305504</v>
+      </c>
+      <c r="O34">
+        <v>7.788188</v>
+      </c>
+      <c r="P34">
+        <v>54.517316</v>
+      </c>
+      <c r="Q34">
+        <v>86.51731599999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1205877581283452</v>
+      </c>
+      <c r="T34">
+        <v>1.146869905620491</v>
+      </c>
+      <c r="U34">
+        <v>0.063</v>
+      </c>
+      <c r="V34">
+        <v>0.125</v>
+      </c>
+      <c r="W34">
+        <v>0.055125</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.709583371603361</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09973050928309861</v>
+      </c>
+      <c r="C35">
+        <v>760.5996785565126</v>
+      </c>
+      <c r="D35">
+        <v>1004.297678556513</v>
+      </c>
+      <c r="E35">
+        <v>62.69799999999998</v>
+      </c>
+      <c r="F35">
+        <v>376.398</v>
+      </c>
+      <c r="G35">
+        <v>132.7</v>
+      </c>
+      <c r="H35">
+        <v>826.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>117.3</v>
+      </c>
+      <c r="K35">
+        <v>32</v>
+      </c>
+      <c r="L35">
+        <v>85.3</v>
+      </c>
+      <c r="M35">
+        <v>23.713074</v>
+      </c>
+      <c r="N35">
+        <v>61.586926</v>
+      </c>
+      <c r="O35">
+        <v>7.69836575</v>
+      </c>
+      <c r="P35">
+        <v>53.88856025</v>
+      </c>
+      <c r="Q35">
+        <v>85.88856025</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1217003869896994</v>
+      </c>
+      <c r="T35">
+        <v>1.16247175834776</v>
+      </c>
+      <c r="U35">
+        <v>0.063</v>
+      </c>
+      <c r="V35">
+        <v>0.125</v>
+      </c>
+      <c r="W35">
+        <v>0.055125</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>3.597171754282047</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1019335930389225</v>
+      </c>
+      <c r="C36">
+        <v>726.9772188465173</v>
+      </c>
+      <c r="D36">
+        <v>982.0812188465173</v>
+      </c>
+      <c r="E36">
+        <v>74.10399999999998</v>
+      </c>
+      <c r="F36">
+        <v>387.804</v>
+      </c>
+      <c r="G36">
+        <v>132.7</v>
+      </c>
+      <c r="H36">
+        <v>826.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>117.3</v>
+      </c>
+      <c r="K36">
+        <v>32</v>
+      </c>
+      <c r="L36">
+        <v>85.3</v>
+      </c>
+      <c r="M36">
+        <v>27.1850604</v>
+      </c>
+      <c r="N36">
+        <v>58.1149396</v>
+      </c>
+      <c r="O36">
+        <v>7.26436745</v>
+      </c>
+      <c r="P36">
+        <v>50.85057215</v>
+      </c>
+      <c r="Q36">
+        <v>82.85057215</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1228467318771553</v>
+      </c>
+      <c r="T36">
+        <v>1.178546394491006</v>
+      </c>
+      <c r="U36">
+        <v>0.0701</v>
+      </c>
+      <c r="V36">
+        <v>0.125</v>
+      </c>
+      <c r="W36">
+        <v>0.0613375</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.137752822502466</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1020865517947463</v>
+      </c>
+      <c r="C37">
+        <v>714.065178438876</v>
+      </c>
+      <c r="D37">
+        <v>980.575178438876</v>
+      </c>
+      <c r="E37">
+        <v>85.50999999999999</v>
+      </c>
+      <c r="F37">
+        <v>399.21</v>
+      </c>
+      <c r="G37">
+        <v>132.7</v>
+      </c>
+      <c r="H37">
+        <v>826.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>117.3</v>
+      </c>
+      <c r="K37">
+        <v>32</v>
+      </c>
+      <c r="L37">
+        <v>85.3</v>
+      </c>
+      <c r="M37">
+        <v>27.984621</v>
+      </c>
+      <c r="N37">
+        <v>57.315379</v>
+      </c>
+      <c r="O37">
+        <v>7.164422375</v>
+      </c>
+      <c r="P37">
+        <v>50.150956625</v>
+      </c>
+      <c r="Q37">
+        <v>82.15095662499999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1240283489149944</v>
+      </c>
+      <c r="T37">
+        <v>1.195115634823276</v>
+      </c>
+      <c r="U37">
+        <v>0.0701</v>
+      </c>
+      <c r="V37">
+        <v>0.125</v>
+      </c>
+      <c r="W37">
+        <v>0.0613375</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.048102741859538</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1089490105505702</v>
+      </c>
+      <c r="C38">
+        <v>639.5374800338786</v>
+      </c>
+      <c r="D38">
+        <v>917.4534800338787</v>
+      </c>
+      <c r="E38">
+        <v>96.91599999999994</v>
+      </c>
+      <c r="F38">
+        <v>410.6159999999999</v>
+      </c>
+      <c r="G38">
+        <v>132.7</v>
+      </c>
+      <c r="H38">
+        <v>826.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>117.3</v>
+      </c>
+      <c r="K38">
+        <v>32</v>
+      </c>
+      <c r="L38">
+        <v>85.3</v>
+      </c>
+      <c r="M38">
+        <v>37.5303024</v>
+      </c>
+      <c r="N38">
+        <v>47.7696976</v>
+      </c>
+      <c r="O38">
+        <v>5.9712122</v>
+      </c>
+      <c r="P38">
+        <v>41.7984854</v>
+      </c>
+      <c r="Q38">
+        <v>73.7984854</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1252468914852659</v>
+      </c>
+      <c r="T38">
+        <v>1.212202663915929</v>
+      </c>
+      <c r="U38">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.125</v>
+      </c>
+      <c r="W38">
+        <v>0.079975</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.272830074505342</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.109288344306394</v>
+      </c>
+      <c r="C39">
+        <v>625.2204347692559</v>
+      </c>
+      <c r="D39">
+        <v>914.5424347692558</v>
+      </c>
+      <c r="E39">
+        <v>108.3219999999999</v>
+      </c>
+      <c r="F39">
+        <v>422.0219999999999</v>
+      </c>
+      <c r="G39">
+        <v>132.7</v>
+      </c>
+      <c r="H39">
+        <v>826.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>117.3</v>
+      </c>
+      <c r="K39">
+        <v>32</v>
+      </c>
+      <c r="L39">
+        <v>85.3</v>
+      </c>
+      <c r="M39">
+        <v>38.5728108</v>
+      </c>
+      <c r="N39">
+        <v>46.7271892</v>
+      </c>
+      <c r="O39">
+        <v>5.84089865</v>
+      </c>
+      <c r="P39">
+        <v>40.88629055</v>
+      </c>
+      <c r="Q39">
+        <v>72.88629055</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1265041179466572</v>
+      </c>
+      <c r="T39">
+        <v>1.229832138376602</v>
+      </c>
+      <c r="U39">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.125</v>
+      </c>
+      <c r="W39">
+        <v>0.079975</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.211402234653846</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1096276780622179</v>
+      </c>
+      <c r="C40">
+        <v>610.921804348534</v>
+      </c>
+      <c r="D40">
+        <v>911.649804348534</v>
+      </c>
+      <c r="E40">
+        <v>119.728</v>
+      </c>
+      <c r="F40">
+        <v>433.428</v>
+      </c>
+      <c r="G40">
+        <v>132.7</v>
+      </c>
+      <c r="H40">
+        <v>826.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>117.3</v>
+      </c>
+      <c r="K40">
+        <v>32</v>
+      </c>
+      <c r="L40">
+        <v>85.3</v>
+      </c>
+      <c r="M40">
+        <v>39.6153192</v>
+      </c>
+      <c r="N40">
+        <v>45.6846808</v>
+      </c>
+      <c r="O40">
+        <v>5.710585099999999</v>
+      </c>
+      <c r="P40">
+        <v>39.97409569999999</v>
+      </c>
+      <c r="Q40">
+        <v>71.97409569999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1278019001003515</v>
+      </c>
+      <c r="T40">
+        <v>1.248030305561814</v>
+      </c>
+      <c r="U40">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.125</v>
+      </c>
+      <c r="W40">
+        <v>0.079975</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.15320743900506</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1099670118180418</v>
+      </c>
+      <c r="C41">
+        <v>596.6414145882541</v>
+      </c>
+      <c r="D41">
+        <v>908.7754145882541</v>
+      </c>
+      <c r="E41">
+        <v>131.134</v>
+      </c>
+      <c r="F41">
+        <v>444.834</v>
+      </c>
+      <c r="G41">
+        <v>132.7</v>
+      </c>
+      <c r="H41">
+        <v>826.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>117.3</v>
+      </c>
+      <c r="K41">
+        <v>32</v>
+      </c>
+      <c r="L41">
+        <v>85.3</v>
+      </c>
+      <c r="M41">
+        <v>40.6578276</v>
+      </c>
+      <c r="N41">
+        <v>44.64217239999999</v>
+      </c>
+      <c r="O41">
+        <v>5.580271549999999</v>
+      </c>
+      <c r="P41">
+        <v>39.06190084999999</v>
+      </c>
+      <c r="Q41">
+        <v>71.06190085</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1291422324885931</v>
+      </c>
+      <c r="T41">
+        <v>1.266825133966213</v>
+      </c>
+      <c r="U41">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.125</v>
+      </c>
+      <c r="W41">
+        <v>0.079975</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.097996991851084</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1103063455738656</v>
+      </c>
+      <c r="C42">
+        <v>582.3790934948227</v>
+      </c>
+      <c r="D42">
+        <v>905.9190934948226</v>
+      </c>
+      <c r="E42">
+        <v>142.54</v>
+      </c>
+      <c r="F42">
+        <v>456.24</v>
+      </c>
+      <c r="G42">
+        <v>132.7</v>
+      </c>
+      <c r="H42">
+        <v>826.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>117.3</v>
+      </c>
+      <c r="K42">
+        <v>32</v>
+      </c>
+      <c r="L42">
+        <v>85.3</v>
+      </c>
+      <c r="M42">
+        <v>41.70033600000001</v>
+      </c>
+      <c r="N42">
+        <v>43.59966399999999</v>
+      </c>
+      <c r="O42">
+        <v>5.449957999999999</v>
+      </c>
+      <c r="P42">
+        <v>38.14970599999999</v>
+      </c>
+      <c r="Q42">
+        <v>70.14970599999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1305272426231094</v>
+      </c>
+      <c r="T42">
+        <v>1.286246456650759</v>
+      </c>
+      <c r="U42">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.125</v>
+      </c>
+      <c r="W42">
+        <v>0.079975</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.045547067054807</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1182153043296895</v>
+      </c>
+      <c r="C43">
+        <v>509.1388820991198</v>
+      </c>
+      <c r="D43">
+        <v>844.0848820991199</v>
+      </c>
+      <c r="E43">
+        <v>153.946</v>
+      </c>
+      <c r="F43">
+        <v>467.646</v>
+      </c>
+      <c r="G43">
+        <v>132.7</v>
+      </c>
+      <c r="H43">
+        <v>826.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>117.3</v>
+      </c>
+      <c r="K43">
+        <v>32</v>
+      </c>
+      <c r="L43">
+        <v>85.3</v>
+      </c>
+      <c r="M43">
+        <v>52.61017500000001</v>
+      </c>
+      <c r="N43">
+        <v>32.68982499999999</v>
+      </c>
+      <c r="O43">
+        <v>4.086228124999999</v>
+      </c>
+      <c r="P43">
+        <v>28.60359687499999</v>
+      </c>
+      <c r="Q43">
+        <v>60.60359687499999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.131959202253711</v>
+      </c>
+      <c r="T43">
+        <v>1.306326129256814</v>
+      </c>
+      <c r="U43">
+        <v>0.1125</v>
+      </c>
+      <c r="V43">
+        <v>0.125</v>
+      </c>
+      <c r="W43">
+        <v>0.0984375</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.621359366320298</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1187392630855134</v>
+      </c>
+      <c r="C44">
+        <v>493.9332291231469</v>
+      </c>
+      <c r="D44">
+        <v>840.2852291231469</v>
+      </c>
+      <c r="E44">
+        <v>165.352</v>
+      </c>
+      <c r="F44">
+        <v>479.052</v>
+      </c>
+      <c r="G44">
+        <v>132.7</v>
+      </c>
+      <c r="H44">
+        <v>826.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>117.3</v>
+      </c>
+      <c r="K44">
+        <v>32</v>
+      </c>
+      <c r="L44">
+        <v>85.3</v>
+      </c>
+      <c r="M44">
+        <v>53.89335</v>
+      </c>
+      <c r="N44">
+        <v>31.40665</v>
+      </c>
+      <c r="O44">
+        <v>3.92583125</v>
+      </c>
+      <c r="P44">
+        <v>27.48081875</v>
+      </c>
+      <c r="Q44">
+        <v>59.48081875</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1334405398026092</v>
+      </c>
+      <c r="T44">
+        <v>1.327098204366527</v>
+      </c>
+      <c r="U44">
+        <v>0.1125</v>
+      </c>
+      <c r="V44">
+        <v>0.125</v>
+      </c>
+      <c r="W44">
+        <v>0.0984375</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>1.582755571884101</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1192632218413372</v>
+      </c>
+      <c r="C45">
+        <v>478.7616311679711</v>
+      </c>
+      <c r="D45">
+        <v>836.5196311679712</v>
+      </c>
+      <c r="E45">
+        <v>176.758</v>
+      </c>
+      <c r="F45">
+        <v>490.458</v>
+      </c>
+      <c r="G45">
+        <v>132.7</v>
+      </c>
+      <c r="H45">
+        <v>826.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>117.3</v>
+      </c>
+      <c r="K45">
+        <v>32</v>
+      </c>
+      <c r="L45">
+        <v>85.3</v>
+      </c>
+      <c r="M45">
+        <v>55.176525</v>
+      </c>
+      <c r="N45">
+        <v>30.123475</v>
+      </c>
+      <c r="O45">
+        <v>3.765434375</v>
+      </c>
+      <c r="P45">
+        <v>26.358040625</v>
+      </c>
+      <c r="Q45">
+        <v>58.358040625</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1349738541076091</v>
+      </c>
+      <c r="T45">
+        <v>1.348599124216931</v>
+      </c>
+      <c r="U45">
+        <v>0.1125</v>
+      </c>
+      <c r="V45">
+        <v>0.125</v>
+      </c>
+      <c r="W45">
+        <v>0.0984375</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>1.545947302770517</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1197871805971611</v>
+      </c>
+      <c r="C46">
+        <v>463.6236324404845</v>
+      </c>
+      <c r="D46">
+        <v>832.7876324404845</v>
+      </c>
+      <c r="E46">
+        <v>188.164</v>
+      </c>
+      <c r="F46">
+        <v>501.864</v>
+      </c>
+      <c r="G46">
+        <v>132.7</v>
+      </c>
+      <c r="H46">
+        <v>826.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>117.3</v>
+      </c>
+      <c r="K46">
+        <v>32</v>
+      </c>
+      <c r="L46">
+        <v>85.3</v>
+      </c>
+      <c r="M46">
+        <v>56.4597</v>
+      </c>
+      <c r="N46">
+        <v>28.8403</v>
+      </c>
+      <c r="O46">
+        <v>3.6050375</v>
+      </c>
+      <c r="P46">
+        <v>25.2352625</v>
+      </c>
+      <c r="Q46">
+        <v>57.2352625</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1365619296377876</v>
+      </c>
+      <c r="T46">
+        <v>1.370867934061993</v>
+      </c>
+      <c r="U46">
+        <v>0.1125</v>
+      </c>
+      <c r="V46">
+        <v>0.125</v>
+      </c>
+      <c r="W46">
+        <v>0.0984375</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>1.51081213679846</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1556401843289915</v>
+      </c>
+      <c r="C47">
+        <v>257.4461169703006</v>
+      </c>
+      <c r="D47">
+        <v>638.0161169703007</v>
+      </c>
+      <c r="E47">
+        <v>199.57</v>
+      </c>
+      <c r="F47">
+        <v>513.27</v>
+      </c>
+      <c r="G47">
+        <v>132.7</v>
+      </c>
+      <c r="H47">
+        <v>826.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>117.3</v>
+      </c>
+      <c r="K47">
+        <v>32</v>
+      </c>
+      <c r="L47">
+        <v>85.3</v>
+      </c>
+      <c r="M47">
+        <v>100.908882</v>
+      </c>
+      <c r="N47">
+        <v>-15.60888199999999</v>
+      </c>
+      <c r="O47">
+        <v>-1.951110249999999</v>
+      </c>
+      <c r="P47">
+        <v>-13.65777174999999</v>
+      </c>
+      <c r="Q47">
+        <v>18.34222825000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1391242444098762</v>
+      </c>
+      <c r="T47">
+        <v>1.406798026389793</v>
+      </c>
+      <c r="U47">
+        <v>0.1966</v>
+      </c>
+      <c r="V47">
+        <v>0.1056646331687631</v>
+      </c>
+      <c r="W47">
+        <v>0.1758263331190212</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8453170653501048</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1572181843289915</v>
+      </c>
+      <c r="C48">
+        <v>239.5394693882256</v>
+      </c>
+      <c r="D48">
+        <v>631.5154693882256</v>
+      </c>
+      <c r="E48">
+        <v>210.9759999999999</v>
+      </c>
+      <c r="F48">
+        <v>524.6759999999999</v>
+      </c>
+      <c r="G48">
+        <v>132.7</v>
+      </c>
+      <c r="H48">
+        <v>826.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>117.3</v>
+      </c>
+      <c r="K48">
+        <v>32</v>
+      </c>
+      <c r="L48">
+        <v>85.3</v>
+      </c>
+      <c r="M48">
+        <v>103.1513016</v>
+      </c>
+      <c r="N48">
+        <v>-17.85130159999999</v>
+      </c>
+      <c r="O48">
+        <v>-2.231412699999998</v>
+      </c>
+      <c r="P48">
+        <v>-15.61988889999999</v>
+      </c>
+      <c r="Q48">
+        <v>16.38011110000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1409821007878369</v>
+      </c>
+      <c r="T48">
+        <v>1.432849841693308</v>
+      </c>
+      <c r="U48">
+        <v>0.1966</v>
+      </c>
+      <c r="V48">
+        <v>0.1033675759259639</v>
+      </c>
+      <c r="W48">
+        <v>0.1762779345729555</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.8269406074077112</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1587961843289915</v>
+      </c>
+      <c r="C49">
+        <v>221.7639539079374</v>
+      </c>
+      <c r="D49">
+        <v>625.1459539079374</v>
+      </c>
+      <c r="E49">
+        <v>222.382</v>
+      </c>
+      <c r="F49">
+        <v>536.082</v>
+      </c>
+      <c r="G49">
+        <v>132.7</v>
+      </c>
+      <c r="H49">
+        <v>826.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>117.3</v>
+      </c>
+      <c r="K49">
+        <v>32</v>
+      </c>
+      <c r="L49">
+        <v>85.3</v>
+      </c>
+      <c r="M49">
+        <v>105.3937212</v>
+      </c>
+      <c r="N49">
+        <v>-20.0937212</v>
+      </c>
+      <c r="O49">
+        <v>-2.511715150000001</v>
+      </c>
+      <c r="P49">
+        <v>-17.58200605</v>
+      </c>
+      <c r="Q49">
+        <v>14.41799395</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1429100649536451</v>
+      </c>
+      <c r="T49">
+        <v>1.459884744366766</v>
+      </c>
+      <c r="U49">
+        <v>0.1966</v>
+      </c>
+      <c r="V49">
+        <v>0.1011682657998795</v>
+      </c>
+      <c r="W49">
+        <v>0.1767103189437437</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.8093461263990364</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1688517940939411</v>
+      </c>
+      <c r="C50">
+        <v>172.6048656267604</v>
+      </c>
+      <c r="D50">
+        <v>587.3928656267603</v>
+      </c>
+      <c r="E50">
+        <v>233.788</v>
+      </c>
+      <c r="F50">
+        <v>547.4879999999999</v>
+      </c>
+      <c r="G50">
+        <v>132.7</v>
+      </c>
+      <c r="H50">
+        <v>826.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>117.3</v>
+      </c>
+      <c r="K50">
+        <v>32</v>
+      </c>
+      <c r="L50">
+        <v>85.3</v>
+      </c>
+      <c r="M50">
+        <v>117.0529344</v>
+      </c>
+      <c r="N50">
+        <v>-31.75293439999999</v>
+      </c>
+      <c r="O50">
+        <v>-3.969116799999998</v>
+      </c>
+      <c r="P50">
+        <v>-27.78381759999999</v>
+      </c>
+      <c r="Q50">
+        <v>4.216182400000012</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1453383542122723</v>
+      </c>
+      <c r="T50">
+        <v>1.493935462183126</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.09109126614086832</v>
+      </c>
+      <c r="W50">
+        <v>0.1943246872990824</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.7287301291269466</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1706017940939412</v>
+      </c>
+      <c r="C51">
+        <v>155.0896033630626</v>
+      </c>
+      <c r="D51">
+        <v>581.2836033630625</v>
+      </c>
+      <c r="E51">
+        <v>245.1939999999999</v>
+      </c>
+      <c r="F51">
+        <v>558.8939999999999</v>
+      </c>
+      <c r="G51">
+        <v>132.7</v>
+      </c>
+      <c r="H51">
+        <v>826.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>117.3</v>
+      </c>
+      <c r="K51">
+        <v>32</v>
+      </c>
+      <c r="L51">
+        <v>85.3</v>
+      </c>
+      <c r="M51">
+        <v>119.4915372</v>
+      </c>
+      <c r="N51">
+        <v>-34.19153719999997</v>
+      </c>
+      <c r="O51">
+        <v>-4.273942149999996</v>
+      </c>
+      <c r="P51">
+        <v>-29.91759504999997</v>
+      </c>
+      <c r="Q51">
+        <v>2.082404950000026</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1474273415497679</v>
+      </c>
+      <c r="T51">
+        <v>1.523228314382796</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.08923226070942204</v>
+      </c>
+      <c r="W51">
+        <v>0.1947221426603256</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.7138580856753763</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1723517940939411</v>
+      </c>
+      <c r="C52">
+        <v>137.7001134720415</v>
+      </c>
+      <c r="D52">
+        <v>575.3001134720414</v>
+      </c>
+      <c r="E52">
+        <v>256.6</v>
+      </c>
+      <c r="F52">
+        <v>570.3</v>
+      </c>
+      <c r="G52">
+        <v>132.7</v>
+      </c>
+      <c r="H52">
+        <v>826.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>117.3</v>
+      </c>
+      <c r="K52">
+        <v>32</v>
+      </c>
+      <c r="L52">
+        <v>85.3</v>
+      </c>
+      <c r="M52">
+        <v>121.93014</v>
+      </c>
+      <c r="N52">
+        <v>-36.63013999999998</v>
+      </c>
+      <c r="O52">
+        <v>-4.578767499999998</v>
+      </c>
+      <c r="P52">
+        <v>-32.05137249999999</v>
+      </c>
+      <c r="Q52">
+        <v>-0.05137249999998517</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1495998883807632</v>
+      </c>
+      <c r="T52">
+        <v>1.553692880670452</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.0874476154952336</v>
+      </c>
+      <c r="W52">
+        <v>0.1951036998071191</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6995809239618688</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1741017940939411</v>
+      </c>
+      <c r="C53">
+        <v>120.4325515817108</v>
+      </c>
+      <c r="D53">
+        <v>569.4385515817108</v>
+      </c>
+      <c r="E53">
+        <v>268.006</v>
+      </c>
+      <c r="F53">
+        <v>581.706</v>
+      </c>
+      <c r="G53">
+        <v>132.7</v>
+      </c>
+      <c r="H53">
+        <v>826.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>117.3</v>
+      </c>
+      <c r="K53">
+        <v>32</v>
+      </c>
+      <c r="L53">
+        <v>85.3</v>
+      </c>
+      <c r="M53">
+        <v>124.3687428</v>
+      </c>
+      <c r="N53">
+        <v>-39.0687428</v>
+      </c>
+      <c r="O53">
+        <v>-4.883592849999999</v>
+      </c>
+      <c r="P53">
+        <v>-34.18514995</v>
+      </c>
+      <c r="Q53">
+        <v>-2.185149949999996</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1518611105926155</v>
+      </c>
+      <c r="T53">
+        <v>1.585400898643318</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.08573295636787606</v>
+      </c>
+      <c r="W53">
+        <v>0.1954702939285481</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.6858636509430085</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1758517940939411</v>
+      </c>
+      <c r="C54">
+        <v>103.2832284165089</v>
+      </c>
+      <c r="D54">
+        <v>563.6952284165088</v>
+      </c>
+      <c r="E54">
+        <v>279.412</v>
+      </c>
+      <c r="F54">
+        <v>593.112</v>
+      </c>
+      <c r="G54">
+        <v>132.7</v>
+      </c>
+      <c r="H54">
+        <v>826.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>117.3</v>
+      </c>
+      <c r="K54">
+        <v>32</v>
+      </c>
+      <c r="L54">
+        <v>85.3</v>
+      </c>
+      <c r="M54">
+        <v>126.8073456</v>
+      </c>
+      <c r="N54">
+        <v>-41.50734559999999</v>
+      </c>
+      <c r="O54">
+        <v>-5.188418199999999</v>
+      </c>
+      <c r="P54">
+        <v>-36.31892739999999</v>
+      </c>
+      <c r="Q54">
+        <v>-4.318927399999993</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1542165503966284</v>
+      </c>
+      <c r="T54">
+        <v>1.618430084031721</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.08408424566849383</v>
+      </c>
+      <c r="W54">
+        <v>0.195822788276076</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.6726739653479507</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1776017940939411</v>
+      </c>
+      <c r="C55">
+        <v>86.24860205392906</v>
+      </c>
+      <c r="D55">
+        <v>558.066602053929</v>
+      </c>
+      <c r="E55">
+        <v>290.818</v>
+      </c>
+      <c r="F55">
+        <v>604.518</v>
+      </c>
+      <c r="G55">
+        <v>132.7</v>
+      </c>
+      <c r="H55">
+        <v>826.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>117.3</v>
+      </c>
+      <c r="K55">
+        <v>32</v>
+      </c>
+      <c r="L55">
+        <v>85.3</v>
+      </c>
+      <c r="M55">
+        <v>129.2459484</v>
+      </c>
+      <c r="N55">
+        <v>-43.94594840000001</v>
+      </c>
+      <c r="O55">
+        <v>-5.493243550000001</v>
+      </c>
+      <c r="P55">
+        <v>-38.45270485</v>
+      </c>
+      <c r="Q55">
+        <v>-6.452704850000003</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.156672221681663</v>
+      </c>
+      <c r="T55">
+        <v>1.652864766670693</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.08249775046720149</v>
+      </c>
+      <c r="W55">
+        <v>0.1961619809501123</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.6599820037376118</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1793517940939411</v>
+      </c>
+      <c r="C56">
+        <v>69.32527064048486</v>
+      </c>
+      <c r="D56">
+        <v>552.5492706404848</v>
+      </c>
+      <c r="E56">
+        <v>302.224</v>
+      </c>
+      <c r="F56">
+        <v>615.924</v>
+      </c>
+      <c r="G56">
+        <v>132.7</v>
+      </c>
+      <c r="H56">
+        <v>826.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>117.3</v>
+      </c>
+      <c r="K56">
+        <v>32</v>
+      </c>
+      <c r="L56">
+        <v>85.3</v>
+      </c>
+      <c r="M56">
+        <v>131.6845512</v>
+      </c>
+      <c r="N56">
+        <v>-46.38455119999999</v>
+      </c>
+      <c r="O56">
+        <v>-5.798068899999999</v>
+      </c>
+      <c r="P56">
+        <v>-40.58648229999999</v>
+      </c>
+      <c r="Q56">
+        <v>-8.586482299999993</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1592346612834383</v>
+      </c>
+      <c r="T56">
+        <v>1.688796609424404</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.0809700143474385</v>
+      </c>
+      <c r="W56">
+        <v>0.1964886109325176</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.647760114779508</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1811017940939412</v>
+      </c>
+      <c r="C57">
+        <v>52.50996553552079</v>
+      </c>
+      <c r="D57">
+        <v>547.1399655355209</v>
+      </c>
+      <c r="E57">
+        <v>313.6300000000001</v>
+      </c>
+      <c r="F57">
+        <v>627.33</v>
+      </c>
+      <c r="G57">
+        <v>132.7</v>
+      </c>
+      <c r="H57">
+        <v>826.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>117.3</v>
+      </c>
+      <c r="K57">
+        <v>32</v>
+      </c>
+      <c r="L57">
+        <v>85.3</v>
+      </c>
+      <c r="M57">
+        <v>134.123154</v>
+      </c>
+      <c r="N57">
+        <v>-48.823154</v>
+      </c>
+      <c r="O57">
+        <v>-6.10289425</v>
+      </c>
+      <c r="P57">
+        <v>-42.72025975</v>
+      </c>
+      <c r="Q57">
+        <v>-10.72025975</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1619109870897369</v>
+      </c>
+      <c r="T57">
+        <v>1.726325422967169</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.07949783226839416</v>
+      </c>
+      <c r="W57">
+        <v>0.1968033634610173</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.6359826581471533</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1828517940939411</v>
+      </c>
+      <c r="C58">
+        <v>35.79954485384803</v>
+      </c>
+      <c r="D58">
+        <v>541.835544853848</v>
+      </c>
+      <c r="E58">
+        <v>325.036</v>
+      </c>
+      <c r="F58">
+        <v>638.736</v>
+      </c>
+      <c r="G58">
+        <v>132.7</v>
+      </c>
+      <c r="H58">
+        <v>826.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>117.3</v>
+      </c>
+      <c r="K58">
+        <v>32</v>
+      </c>
+      <c r="L58">
+        <v>85.3</v>
+      </c>
+      <c r="M58">
+        <v>136.5617568</v>
+      </c>
+      <c r="N58">
+        <v>-51.26175679999999</v>
+      </c>
+      <c r="O58">
+        <v>-6.407719599999998</v>
+      </c>
+      <c r="P58">
+        <v>-44.85403719999999</v>
+      </c>
+      <c r="Q58">
+        <v>-12.85403719999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1647089640690491</v>
+      </c>
+      <c r="T58">
+        <v>1.765560091670968</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.07807822812074428</v>
+      </c>
+      <c r="W58">
+        <v>0.1971068748277849</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.6246258249659542</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1846017940939412</v>
+      </c>
+      <c r="C59">
+        <v>19.19098738038224</v>
+      </c>
+      <c r="D59">
+        <v>536.6329873803824</v>
+      </c>
+      <c r="E59">
+        <v>336.4420000000001</v>
+      </c>
+      <c r="F59">
+        <v>650.1420000000001</v>
+      </c>
+      <c r="G59">
+        <v>132.7</v>
+      </c>
+      <c r="H59">
+        <v>826.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>117.3</v>
+      </c>
+      <c r="K59">
+        <v>32</v>
+      </c>
+      <c r="L59">
+        <v>85.3</v>
+      </c>
+      <c r="M59">
+        <v>139.0003596</v>
+      </c>
+      <c r="N59">
+        <v>-53.7003596</v>
+      </c>
+      <c r="O59">
+        <v>-6.71254495</v>
+      </c>
+      <c r="P59">
+        <v>-46.98781465</v>
+      </c>
+      <c r="Q59">
+        <v>-14.98781465</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1676370795125154</v>
+      </c>
+      <c r="T59">
+        <v>1.806619628686572</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.07670843464494174</v>
+      </c>
+      <c r="W59">
+        <v>0.1973997366729114</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.6136674771595338</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1863517940939411</v>
+      </c>
+      <c r="C60">
+        <v>2.681386832036537</v>
+      </c>
+      <c r="D60">
+        <v>531.5293868320364</v>
+      </c>
+      <c r="E60">
+        <v>347.8479999999999</v>
+      </c>
+      <c r="F60">
+        <v>661.5479999999999</v>
+      </c>
+      <c r="G60">
+        <v>132.7</v>
+      </c>
+      <c r="H60">
+        <v>826.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>117.3</v>
+      </c>
+      <c r="K60">
+        <v>32</v>
+      </c>
+      <c r="L60">
+        <v>85.3</v>
+      </c>
+      <c r="M60">
+        <v>141.4389624</v>
+      </c>
+      <c r="N60">
+        <v>-56.13896239999998</v>
+      </c>
+      <c r="O60">
+        <v>-7.017370299999998</v>
+      </c>
+      <c r="P60">
+        <v>-49.12159209999999</v>
+      </c>
+      <c r="Q60">
+        <v>-17.12159209999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1707046290247181</v>
+      </c>
+      <c r="T60">
+        <v>1.849634381750537</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.07538587542692551</v>
+      </c>
+      <c r="W60">
+        <v>0.1976824998337233</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.6030870034154041</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1881017940939411</v>
+      </c>
+      <c r="C61">
+        <v>-13.73205355604932</v>
+      </c>
+      <c r="D61">
+        <v>526.5219464439507</v>
+      </c>
+      <c r="E61">
+        <v>359.254</v>
+      </c>
+      <c r="F61">
+        <v>672.954</v>
+      </c>
+      <c r="G61">
+        <v>132.7</v>
+      </c>
+      <c r="H61">
+        <v>826.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>117.3</v>
+      </c>
+      <c r="K61">
+        <v>32</v>
+      </c>
+      <c r="L61">
+        <v>85.3</v>
+      </c>
+      <c r="M61">
+        <v>143.8775652</v>
+      </c>
+      <c r="N61">
+        <v>-58.5775652</v>
+      </c>
+      <c r="O61">
+        <v>-7.322195649999999</v>
+      </c>
+      <c r="P61">
+        <v>-51.25536955</v>
+      </c>
+      <c r="Q61">
+        <v>-19.25536955</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1739218150984917</v>
+      </c>
+      <c r="T61">
+        <v>1.89474741545177</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.07410814872477423</v>
+      </c>
+      <c r="W61">
+        <v>0.1979556778026433</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5928651897981938</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1898517940939412</v>
+      </c>
+      <c r="C62">
+        <v>-30.05202614111317</v>
+      </c>
+      <c r="D62">
+        <v>521.6079738588867</v>
+      </c>
+      <c r="E62">
+        <v>370.6599999999999</v>
+      </c>
+      <c r="F62">
+        <v>684.3599999999999</v>
+      </c>
+      <c r="G62">
+        <v>132.7</v>
+      </c>
+      <c r="H62">
+        <v>826.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>117.3</v>
+      </c>
+      <c r="K62">
+        <v>32</v>
+      </c>
+      <c r="L62">
+        <v>85.3</v>
+      </c>
+      <c r="M62">
+        <v>146.316168</v>
+      </c>
+      <c r="N62">
+        <v>-61.01616799999998</v>
+      </c>
+      <c r="O62">
+        <v>-7.627020999999997</v>
+      </c>
+      <c r="P62">
+        <v>-53.38914699999998</v>
+      </c>
+      <c r="Q62">
+        <v>-21.38914699999998</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.177299860475954</v>
+      </c>
+      <c r="T62">
+        <v>1.942116100838064</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.07287301291269466</v>
+      </c>
+      <c r="W62">
+        <v>0.1982197498392659</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5829841033015573</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1916017940939411</v>
+      </c>
+      <c r="C63">
+        <v>-46.28112369984922</v>
+      </c>
+      <c r="D63">
+        <v>516.7848763001508</v>
+      </c>
+      <c r="E63">
+        <v>382.066</v>
+      </c>
+      <c r="F63">
+        <v>695.766</v>
+      </c>
+      <c r="G63">
+        <v>132.7</v>
+      </c>
+      <c r="H63">
+        <v>826.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>117.3</v>
+      </c>
+      <c r="K63">
+        <v>32</v>
+      </c>
+      <c r="L63">
+        <v>85.3</v>
+      </c>
+      <c r="M63">
+        <v>148.7547708</v>
+      </c>
+      <c r="N63">
+        <v>-63.45477079999999</v>
+      </c>
+      <c r="O63">
+        <v>-7.931846349999999</v>
+      </c>
+      <c r="P63">
+        <v>-55.52292444999999</v>
+      </c>
+      <c r="Q63">
+        <v>-23.52292444999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1808511389496964</v>
+      </c>
+      <c r="T63">
+        <v>1.991913949577502</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.07167837335674884</v>
+      </c>
+      <c r="W63">
+        <v>0.1984751637763271</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5734269868539907</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1933517940939411</v>
+      </c>
+      <c r="C64">
+        <v>-62.4218439901291</v>
+      </c>
+      <c r="D64">
+        <v>512.0501560098708</v>
+      </c>
+      <c r="E64">
+        <v>393.4719999999999</v>
+      </c>
+      <c r="F64">
+        <v>707.1719999999999</v>
+      </c>
+      <c r="G64">
+        <v>132.7</v>
+      </c>
+      <c r="H64">
+        <v>826.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>117.3</v>
+      </c>
+      <c r="K64">
+        <v>32</v>
+      </c>
+      <c r="L64">
+        <v>85.3</v>
+      </c>
+      <c r="M64">
+        <v>151.1933736</v>
+      </c>
+      <c r="N64">
+        <v>-65.89337359999998</v>
+      </c>
+      <c r="O64">
+        <v>-8.236671699999997</v>
+      </c>
+      <c r="P64">
+        <v>-57.65670189999998</v>
+      </c>
+      <c r="Q64">
+        <v>-25.65670189999998</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1845893268167937</v>
+      </c>
+      <c r="T64">
+        <v>2.044332737724278</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.07052227056067226</v>
+      </c>
+      <c r="W64">
+        <v>0.1987223385541283</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5641781644853781</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1951017940939411</v>
+      </c>
+      <c r="C65">
+        <v>-78.47659406424191</v>
+      </c>
+      <c r="D65">
+        <v>507.4014059357581</v>
+      </c>
+      <c r="E65">
+        <v>404.878</v>
+      </c>
+      <c r="F65">
+        <v>718.578</v>
+      </c>
+      <c r="G65">
+        <v>132.7</v>
+      </c>
+      <c r="H65">
+        <v>826.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>117.3</v>
+      </c>
+      <c r="K65">
+        <v>32</v>
+      </c>
+      <c r="L65">
+        <v>85.3</v>
+      </c>
+      <c r="M65">
+        <v>153.6319764</v>
+      </c>
+      <c r="N65">
+        <v>-68.33197639999999</v>
+      </c>
+      <c r="O65">
+        <v>-8.541497049999998</v>
+      </c>
+      <c r="P65">
+        <v>-59.79047934999999</v>
+      </c>
+      <c r="Q65">
+        <v>-27.79047934999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1885295788929233</v>
+      </c>
+      <c r="T65">
+        <v>2.099584973878988</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.06940286944066158</v>
+      </c>
+      <c r="W65">
+        <v>0.1989616665135865</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5552229555252925</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1968517940939411</v>
+      </c>
+      <c r="C66">
+        <v>-94.44769434929128</v>
+      </c>
+      <c r="D66">
+        <v>502.8363056507087</v>
+      </c>
+      <c r="E66">
+        <v>416.2839999999999</v>
+      </c>
+      <c r="F66">
+        <v>729.9839999999999</v>
+      </c>
+      <c r="G66">
+        <v>132.7</v>
+      </c>
+      <c r="H66">
+        <v>826.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>117.3</v>
+      </c>
+      <c r="K66">
+        <v>32</v>
+      </c>
+      <c r="L66">
+        <v>85.3</v>
+      </c>
+      <c r="M66">
+        <v>156.0705792</v>
+      </c>
+      <c r="N66">
+        <v>-70.77057919999997</v>
+      </c>
+      <c r="O66">
+        <v>-8.846322399999996</v>
+      </c>
+      <c r="P66">
+        <v>-61.92425679999997</v>
+      </c>
+      <c r="Q66">
+        <v>-29.92425679999997</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1926887338621711</v>
+      </c>
+      <c r="T66">
+        <v>2.157906778708961</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.06831844960565124</v>
+      </c>
+      <c r="W66">
+        <v>0.1991935154743117</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.54654759684521</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1986017940939412</v>
+      </c>
+      <c r="C67">
+        <v>-110.3373825092924</v>
+      </c>
+      <c r="D67">
+        <v>498.3526174907076</v>
+      </c>
+      <c r="E67">
+        <v>427.69</v>
+      </c>
+      <c r="F67">
+        <v>741.39</v>
+      </c>
+      <c r="G67">
+        <v>132.7</v>
+      </c>
+      <c r="H67">
+        <v>826.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>117.3</v>
+      </c>
+      <c r="K67">
+        <v>32</v>
+      </c>
+      <c r="L67">
+        <v>85.3</v>
+      </c>
+      <c r="M67">
+        <v>158.509182</v>
+      </c>
+      <c r="N67">
+        <v>-73.20918199999998</v>
+      </c>
+      <c r="O67">
+        <v>-9.151147749999998</v>
+      </c>
+      <c r="P67">
+        <v>-64.05803424999999</v>
+      </c>
+      <c r="Q67">
+        <v>-32.05803424999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1970855548296618</v>
+      </c>
+      <c r="T67">
+        <v>2.219561258100645</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.06726739653479506</v>
+      </c>
+      <c r="W67">
+        <v>0.1994182306208608</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5381391722783606</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2003517940939411</v>
+      </c>
+      <c r="C68">
+        <v>-126.1478171024659</v>
+      </c>
+      <c r="D68">
+        <v>493.948182897534</v>
+      </c>
+      <c r="E68">
+        <v>439.0959999999999</v>
+      </c>
+      <c r="F68">
+        <v>752.7959999999999</v>
+      </c>
+      <c r="G68">
+        <v>132.7</v>
+      </c>
+      <c r="H68">
+        <v>826.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>117.3</v>
+      </c>
+      <c r="K68">
+        <v>32</v>
+      </c>
+      <c r="L68">
+        <v>85.3</v>
+      </c>
+      <c r="M68">
+        <v>160.9477848</v>
+      </c>
+      <c r="N68">
+        <v>-75.64778479999997</v>
+      </c>
+      <c r="O68">
+        <v>-9.455973099999996</v>
+      </c>
+      <c r="P68">
+        <v>-66.19181169999997</v>
+      </c>
+      <c r="Q68">
+        <v>-34.19181169999997</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2017410123246518</v>
+      </c>
+      <c r="T68">
+        <v>2.284842471574193</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.06624819355699516</v>
+      </c>
+      <c r="W68">
+        <v>0.1996361362175144</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5299855484559612</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2021017940939412</v>
+      </c>
+      <c r="C69">
+        <v>-141.8810810462967</v>
+      </c>
+      <c r="D69">
+        <v>489.6209189537033</v>
+      </c>
+      <c r="E69">
+        <v>450.502</v>
+      </c>
+      <c r="F69">
+        <v>764.202</v>
+      </c>
+      <c r="G69">
+        <v>132.7</v>
+      </c>
+      <c r="H69">
+        <v>826.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>117.3</v>
+      </c>
+      <c r="K69">
+        <v>32</v>
+      </c>
+      <c r="L69">
+        <v>85.3</v>
+      </c>
+      <c r="M69">
+        <v>163.3863876</v>
+      </c>
+      <c r="N69">
+        <v>-78.08638760000001</v>
+      </c>
+      <c r="O69">
+        <v>-9.760798450000001</v>
+      </c>
+      <c r="P69">
+        <v>-68.32558915000001</v>
+      </c>
+      <c r="Q69">
+        <v>-36.32558915000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2066786187587322</v>
+      </c>
+      <c r="T69">
+        <v>2.354080122227957</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.06525941454868177</v>
+      </c>
+      <c r="W69">
+        <v>0.1998475371694918</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5220753163894543</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2038517940939412</v>
+      </c>
+      <c r="C70">
+        <v>-157.5391849020343</v>
+      </c>
+      <c r="D70">
+        <v>485.3688150979656</v>
+      </c>
+      <c r="E70">
+        <v>461.908</v>
+      </c>
+      <c r="F70">
+        <v>775.6079999999999</v>
+      </c>
+      <c r="G70">
+        <v>132.7</v>
+      </c>
+      <c r="H70">
+        <v>826.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>117.3</v>
+      </c>
+      <c r="K70">
+        <v>32</v>
+      </c>
+      <c r="L70">
+        <v>85.3</v>
+      </c>
+      <c r="M70">
+        <v>165.8249904</v>
+      </c>
+      <c r="N70">
+        <v>-80.52499039999999</v>
+      </c>
+      <c r="O70">
+        <v>-10.0656238</v>
+      </c>
+      <c r="P70">
+        <v>-70.4593666</v>
+      </c>
+      <c r="Q70">
+        <v>-38.4593666</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2119248255949426</v>
+      </c>
+      <c r="T70">
+        <v>2.427645126047581</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.06429971727590705</v>
+      </c>
+      <c r="W70">
+        <v>0.2000527204464111</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5143977382072564</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2056017940939411</v>
+      </c>
+      <c r="C71">
+        <v>-173.1240699895263</v>
+      </c>
+      <c r="D71">
+        <v>481.1899300104737</v>
+      </c>
+      <c r="E71">
+        <v>473.314</v>
+      </c>
+      <c r="F71">
+        <v>787.014</v>
+      </c>
+      <c r="G71">
+        <v>132.7</v>
+      </c>
+      <c r="H71">
+        <v>826.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>117.3</v>
+      </c>
+      <c r="K71">
+        <v>32</v>
+      </c>
+      <c r="L71">
+        <v>85.3</v>
+      </c>
+      <c r="M71">
+        <v>168.2635932</v>
+      </c>
+      <c r="N71">
+        <v>-82.96359320000001</v>
+      </c>
+      <c r="O71">
+        <v>-10.37044915</v>
+      </c>
+      <c r="P71">
+        <v>-72.59314405000001</v>
+      </c>
+      <c r="Q71">
+        <v>-40.59314405000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2175094973883278</v>
+      </c>
+      <c r="T71">
+        <v>2.50595625914589</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.06336783731538666</v>
+      </c>
+      <c r="W71">
+        <v>0.2002519563819703</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5069426985230931</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2251169795158978</v>
+      </c>
+      <c r="C72">
+        <v>-226.6826942516021</v>
+      </c>
+      <c r="D72">
+        <v>439.0373057483978</v>
+      </c>
+      <c r="E72">
+        <v>484.72</v>
+      </c>
+      <c r="F72">
+        <v>798.42</v>
+      </c>
+      <c r="G72">
+        <v>132.7</v>
+      </c>
+      <c r="H72">
+        <v>826.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>117.3</v>
+      </c>
+      <c r="K72">
+        <v>32</v>
+      </c>
+      <c r="L72">
+        <v>85.3</v>
+      </c>
+      <c r="M72">
+        <v>190.662696</v>
+      </c>
+      <c r="N72">
+        <v>-105.362696</v>
+      </c>
+      <c r="O72">
+        <v>-13.170337</v>
+      </c>
+      <c r="P72">
+        <v>-92.19235900000001</v>
+      </c>
+      <c r="Q72">
+        <v>-60.19235900000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2243504320411275</v>
+      </c>
+      <c r="T72">
+        <v>2.601883354583578</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05592336741110594</v>
+      </c>
+      <c r="W72">
+        <v>0.2254454998622279</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4473869392888475</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2271169795158978</v>
+      </c>
+      <c r="C73">
+        <v>-241.9951710997999</v>
+      </c>
+      <c r="D73">
+        <v>435.1308289002</v>
+      </c>
+      <c r="E73">
+        <v>496.1259999999999</v>
+      </c>
+      <c r="F73">
+        <v>809.8259999999999</v>
+      </c>
+      <c r="G73">
+        <v>132.7</v>
+      </c>
+      <c r="H73">
+        <v>826.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>117.3</v>
+      </c>
+      <c r="K73">
+        <v>32</v>
+      </c>
+      <c r="L73">
+        <v>85.3</v>
+      </c>
+      <c r="M73">
+        <v>193.3864488</v>
+      </c>
+      <c r="N73">
+        <v>-108.0864488</v>
+      </c>
+      <c r="O73">
+        <v>-13.5108061</v>
+      </c>
+      <c r="P73">
+        <v>-94.57564269999999</v>
+      </c>
+      <c r="Q73">
+        <v>-62.57564269999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2307487228011663</v>
+      </c>
+      <c r="T73">
+        <v>2.691603470258872</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.0551357143489777</v>
+      </c>
+      <c r="W73">
+        <v>0.2256335914134641</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4410857147918216</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2291169795158978</v>
+      </c>
+      <c r="C74">
+        <v>-257.2387427642474</v>
+      </c>
+      <c r="D74">
+        <v>431.2932572357525</v>
+      </c>
+      <c r="E74">
+        <v>507.5319999999999</v>
+      </c>
+      <c r="F74">
+        <v>821.2319999999999</v>
+      </c>
+      <c r="G74">
+        <v>132.7</v>
+      </c>
+      <c r="H74">
+        <v>826.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>117.3</v>
+      </c>
+      <c r="K74">
+        <v>32</v>
+      </c>
+      <c r="L74">
+        <v>85.3</v>
+      </c>
+      <c r="M74">
+        <v>196.1102016</v>
+      </c>
+      <c r="N74">
+        <v>-110.8102016</v>
+      </c>
+      <c r="O74">
+        <v>-13.8512752</v>
+      </c>
+      <c r="P74">
+        <v>-96.95892639999998</v>
+      </c>
+      <c r="Q74">
+        <v>-64.95892639999998</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2376040343297794</v>
+      </c>
+      <c r="T74">
+        <v>2.787732165625261</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.05436994053857523</v>
+      </c>
+      <c r="W74">
+        <v>0.2258164581993883</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4349595243086019</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2311169795158977</v>
+      </c>
+      <c r="C75">
+        <v>-272.4152164040497</v>
+      </c>
+      <c r="D75">
+        <v>427.5227835959502</v>
+      </c>
+      <c r="E75">
+        <v>518.9379999999999</v>
+      </c>
+      <c r="F75">
+        <v>832.6379999999999</v>
+      </c>
+      <c r="G75">
+        <v>132.7</v>
+      </c>
+      <c r="H75">
+        <v>826.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>117.3</v>
+      </c>
+      <c r="K75">
+        <v>32</v>
+      </c>
+      <c r="L75">
+        <v>85.3</v>
+      </c>
+      <c r="M75">
+        <v>198.8339544</v>
+      </c>
+      <c r="N75">
+        <v>-113.5339544</v>
+      </c>
+      <c r="O75">
+        <v>-14.1917443</v>
+      </c>
+      <c r="P75">
+        <v>-99.34221009999999</v>
+      </c>
+      <c r="Q75">
+        <v>-67.34221009999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2449671467123638</v>
+      </c>
+      <c r="T75">
+        <v>2.890981505092863</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.05362514683256735</v>
+      </c>
+      <c r="W75">
+        <v>0.2259943149363829</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4290011746605388</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2331169795158978</v>
+      </c>
+      <c r="C76">
+        <v>-287.5263365314374</v>
+      </c>
+      <c r="D76">
+        <v>423.8176634685624</v>
+      </c>
+      <c r="E76">
+        <v>530.3439999999998</v>
+      </c>
+      <c r="F76">
+        <v>844.0439999999999</v>
+      </c>
+      <c r="G76">
+        <v>132.7</v>
+      </c>
+      <c r="H76">
+        <v>826.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>117.3</v>
+      </c>
+      <c r="K76">
+        <v>32</v>
+      </c>
+      <c r="L76">
+        <v>85.3</v>
+      </c>
+      <c r="M76">
+        <v>201.5577072</v>
+      </c>
+      <c r="N76">
+        <v>-116.2577072</v>
+      </c>
+      <c r="O76">
+        <v>-14.5322134</v>
+      </c>
+      <c r="P76">
+        <v>-101.7254938</v>
+      </c>
+      <c r="Q76">
+        <v>-69.72549379999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.252896652355147</v>
+      </c>
+      <c r="T76">
+        <v>3.002173101442589</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0529004826861813</v>
+      </c>
+      <c r="W76">
+        <v>0.2261673647345399</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4232038614894504</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2351169795158978</v>
+      </c>
+      <c r="C77">
+        <v>-302.5737877030834</v>
+      </c>
+      <c r="D77">
+        <v>420.1762122969165</v>
+      </c>
+      <c r="E77">
+        <v>541.75</v>
+      </c>
+      <c r="F77">
+        <v>855.4499999999999</v>
+      </c>
+      <c r="G77">
+        <v>132.7</v>
+      </c>
+      <c r="H77">
+        <v>826.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>117.3</v>
+      </c>
+      <c r="K77">
+        <v>32</v>
+      </c>
+      <c r="L77">
+        <v>85.3</v>
+      </c>
+      <c r="M77">
+        <v>204.28146</v>
+      </c>
+      <c r="N77">
+        <v>-118.98146</v>
+      </c>
+      <c r="O77">
+        <v>-14.8726825</v>
+      </c>
+      <c r="P77">
+        <v>-104.1087775</v>
+      </c>
+      <c r="Q77">
+        <v>-72.10877749999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2614605184493529</v>
+      </c>
+      <c r="T77">
+        <v>3.122260025500292</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05219514291703222</v>
+      </c>
+      <c r="W77">
+        <v>0.2263357998714127</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.4175611433362577</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2371169795158978</v>
+      </c>
+      <c r="C78">
+        <v>-317.5591970738586</v>
+      </c>
+      <c r="D78">
+        <v>416.5968029261414</v>
+      </c>
+      <c r="E78">
+        <v>553.1559999999999</v>
+      </c>
+      <c r="F78">
+        <v>866.856</v>
+      </c>
+      <c r="G78">
+        <v>132.7</v>
+      </c>
+      <c r="H78">
+        <v>826.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>117.3</v>
+      </c>
+      <c r="K78">
+        <v>32</v>
+      </c>
+      <c r="L78">
+        <v>85.3</v>
+      </c>
+      <c r="M78">
+        <v>207.0052128</v>
+      </c>
+      <c r="N78">
+        <v>-121.7052128</v>
+      </c>
+      <c r="O78">
+        <v>-15.2131516</v>
+      </c>
+      <c r="P78">
+        <v>-106.4920612</v>
+      </c>
+      <c r="Q78">
+        <v>-74.49206120000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2707380400514093</v>
+      </c>
+      <c r="T78">
+        <v>3.252354193229471</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05150836472075547</v>
+      </c>
+      <c r="W78">
+        <v>0.2264998025046836</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4120669177660438</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2391169795158978</v>
+      </c>
+      <c r="C79">
+        <v>-332.4841368211598</v>
+      </c>
+      <c r="D79">
+        <v>413.0778631788402</v>
+      </c>
+      <c r="E79">
+        <v>564.5619999999999</v>
+      </c>
+      <c r="F79">
+        <v>878.2619999999999</v>
+      </c>
+      <c r="G79">
+        <v>132.7</v>
+      </c>
+      <c r="H79">
+        <v>826.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>117.3</v>
+      </c>
+      <c r="K79">
+        <v>32</v>
+      </c>
+      <c r="L79">
+        <v>85.3</v>
+      </c>
+      <c r="M79">
+        <v>209.7289656</v>
+      </c>
+      <c r="N79">
+        <v>-124.4289656</v>
+      </c>
+      <c r="O79">
+        <v>-15.5536207</v>
+      </c>
+      <c r="P79">
+        <v>-108.8753449</v>
+      </c>
+      <c r="Q79">
+        <v>-76.87534490000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2808223026623401</v>
+      </c>
+      <c r="T79">
+        <v>3.393760897282926</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05083942491918722</v>
+      </c>
+      <c r="W79">
+        <v>0.2266595453292981</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4067153993534978</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2411169795158978</v>
+      </c>
+      <c r="C80">
+        <v>-347.3501264474</v>
+      </c>
+      <c r="D80">
+        <v>409.6178735526</v>
+      </c>
+      <c r="E80">
+        <v>575.9680000000001</v>
+      </c>
+      <c r="F80">
+        <v>889.668</v>
+      </c>
+      <c r="G80">
+        <v>132.7</v>
+      </c>
+      <c r="H80">
+        <v>826.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>117.3</v>
+      </c>
+      <c r="K80">
+        <v>32</v>
+      </c>
+      <c r="L80">
+        <v>85.3</v>
+      </c>
+      <c r="M80">
+        <v>212.4527184</v>
+      </c>
+      <c r="N80">
+        <v>-127.1527184</v>
+      </c>
+      <c r="O80">
+        <v>-15.8940898</v>
+      </c>
+      <c r="P80">
+        <v>-111.2586286</v>
+      </c>
+      <c r="Q80">
+        <v>-79.25862860000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2918233164197193</v>
+      </c>
+      <c r="T80">
+        <v>3.548022756250333</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05018763742022328</v>
+      </c>
+      <c r="W80">
+        <v>0.2268151921840507</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.4015010993617862</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2431169795158978</v>
+      </c>
+      <c r="C81">
+        <v>-362.1586349677428</v>
+      </c>
+      <c r="D81">
+        <v>406.2153650322571</v>
+      </c>
+      <c r="E81">
+        <v>587.374</v>
+      </c>
+      <c r="F81">
+        <v>901.074</v>
+      </c>
+      <c r="G81">
+        <v>132.7</v>
+      </c>
+      <c r="H81">
+        <v>826.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>117.3</v>
+      </c>
+      <c r="K81">
+        <v>32</v>
+      </c>
+      <c r="L81">
+        <v>85.3</v>
+      </c>
+      <c r="M81">
+        <v>215.1764712</v>
+      </c>
+      <c r="N81">
+        <v>-129.8764712</v>
+      </c>
+      <c r="O81">
+        <v>-16.2345589</v>
+      </c>
+      <c r="P81">
+        <v>-113.6419123</v>
+      </c>
+      <c r="Q81">
+        <v>-81.64191230000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3038720457730392</v>
+      </c>
+      <c r="T81">
+        <v>3.716976220833682</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.0495523508706002</v>
+      </c>
+      <c r="W81">
+        <v>0.2269668986121007</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3964188069648016</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2451169795158978</v>
+      </c>
+      <c r="C82">
+        <v>-376.9110829897008</v>
+      </c>
+      <c r="D82">
+        <v>402.8689170102991</v>
+      </c>
+      <c r="E82">
+        <v>598.78</v>
+      </c>
+      <c r="F82">
+        <v>912.48</v>
+      </c>
+      <c r="G82">
+        <v>132.7</v>
+      </c>
+      <c r="H82">
+        <v>826.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>117.3</v>
+      </c>
+      <c r="K82">
+        <v>32</v>
+      </c>
+      <c r="L82">
+        <v>85.3</v>
+      </c>
+      <c r="M82">
+        <v>217.900224</v>
+      </c>
+      <c r="N82">
+        <v>-132.600224</v>
+      </c>
+      <c r="O82">
+        <v>-16.575028</v>
+      </c>
+      <c r="P82">
+        <v>-116.025196</v>
+      </c>
+      <c r="Q82">
+        <v>-84.02519600000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3171256480616912</v>
+      </c>
+      <c r="T82">
+        <v>3.902825031875366</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0489329464847177</v>
+      </c>
+      <c r="W82">
+        <v>0.2271148123794494</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3914635718777415</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2471169795158978</v>
+      </c>
+      <c r="C83">
+        <v>-391.6088446907829</v>
+      </c>
+      <c r="D83">
+        <v>399.5771553092171</v>
+      </c>
+      <c r="E83">
+        <v>610.1859999999999</v>
+      </c>
+      <c r="F83">
+        <v>923.886</v>
+      </c>
+      <c r="G83">
+        <v>132.7</v>
+      </c>
+      <c r="H83">
+        <v>826.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>117.3</v>
+      </c>
+      <c r="K83">
+        <v>32</v>
+      </c>
+      <c r="L83">
+        <v>85.3</v>
+      </c>
+      <c r="M83">
+        <v>220.6239768</v>
+      </c>
+      <c r="N83">
+        <v>-135.3239768</v>
+      </c>
+      <c r="O83">
+        <v>-16.9154971</v>
+      </c>
+      <c r="P83">
+        <v>-118.4084797</v>
+      </c>
+      <c r="Q83">
+        <v>-86.40847970000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3317743663807276</v>
+      </c>
+      <c r="T83">
+        <v>4.108236875658281</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04832883603428909</v>
+      </c>
+      <c r="W83">
+        <v>0.2272590739550118</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3866306882743126</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2491169795158978</v>
+      </c>
+      <c r="C84">
+        <v>-406.2532496999708</v>
+      </c>
+      <c r="D84">
+        <v>396.3387503000293</v>
+      </c>
+      <c r="E84">
+        <v>621.5920000000001</v>
+      </c>
+      <c r="F84">
+        <v>935.292</v>
+      </c>
+      <c r="G84">
+        <v>132.7</v>
+      </c>
+      <c r="H84">
+        <v>826.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>117.3</v>
+      </c>
+      <c r="K84">
+        <v>32</v>
+      </c>
+      <c r="L84">
+        <v>85.3</v>
+      </c>
+      <c r="M84">
+        <v>223.3477296</v>
+      </c>
+      <c r="N84">
+        <v>-138.0477296</v>
+      </c>
+      <c r="O84">
+        <v>-17.2559662</v>
+      </c>
+      <c r="P84">
+        <v>-120.7917634</v>
+      </c>
+      <c r="Q84">
+        <v>-88.79176340000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3480507200685458</v>
+      </c>
+      <c r="T84">
+        <v>4.336472257639296</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04773945998509044</v>
+      </c>
+      <c r="W84">
+        <v>0.2273998169555604</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3819156798807234</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2511169795158978</v>
+      </c>
+      <c r="C85">
+        <v>-420.8455848884436</v>
+      </c>
+      <c r="D85">
+        <v>393.1524151115565</v>
+      </c>
+      <c r="E85">
+        <v>632.998</v>
+      </c>
+      <c r="F85">
+        <v>946.698</v>
+      </c>
+      <c r="G85">
+        <v>132.7</v>
+      </c>
+      <c r="H85">
+        <v>826.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>117.3</v>
+      </c>
+      <c r="K85">
+        <v>32</v>
+      </c>
+      <c r="L85">
+        <v>85.3</v>
+      </c>
+      <c r="M85">
+        <v>226.0714824</v>
+      </c>
+      <c r="N85">
+        <v>-140.7714824</v>
+      </c>
+      <c r="O85">
+        <v>-17.5964353</v>
+      </c>
+      <c r="P85">
+        <v>-123.1750471</v>
+      </c>
+      <c r="Q85">
+        <v>-91.17504710000003</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3662419388961074</v>
+      </c>
+      <c r="T85">
+        <v>4.591558861029844</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0471642857684026</v>
+      </c>
+      <c r="W85">
+        <v>0.2275371685585055</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3773142861472207</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2531169795158978</v>
+      </c>
+      <c r="C86">
+        <v>-435.3870960746091</v>
+      </c>
+      <c r="D86">
+        <v>390.0169039253908</v>
+      </c>
+      <c r="E86">
+        <v>644.404</v>
+      </c>
+      <c r="F86">
+        <v>958.1039999999999</v>
+      </c>
+      <c r="G86">
+        <v>132.7</v>
+      </c>
+      <c r="H86">
+        <v>826.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>117.3</v>
+      </c>
+      <c r="K86">
+        <v>32</v>
+      </c>
+      <c r="L86">
+        <v>85.3</v>
+      </c>
+      <c r="M86">
+        <v>228.7952352</v>
+      </c>
+      <c r="N86">
+        <v>-143.4952352</v>
+      </c>
+      <c r="O86">
+        <v>-17.9369044</v>
+      </c>
+      <c r="P86">
+        <v>-125.5583308</v>
+      </c>
+      <c r="Q86">
+        <v>-93.55833080000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3867070600771139</v>
+      </c>
+      <c r="T86">
+        <v>4.878531289844206</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.04660280617592162</v>
+      </c>
+      <c r="W86">
+        <v>0.2276712498851899</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3728224494073729</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2551169795158977</v>
+      </c>
+      <c r="C87">
+        <v>-449.8789896481949</v>
+      </c>
+      <c r="D87">
+        <v>386.931010351805</v>
+      </c>
+      <c r="E87">
+        <v>655.8099999999999</v>
+      </c>
+      <c r="F87">
+        <v>969.5099999999999</v>
+      </c>
+      <c r="G87">
+        <v>132.7</v>
+      </c>
+      <c r="H87">
+        <v>826.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>117.3</v>
+      </c>
+      <c r="K87">
+        <v>32</v>
+      </c>
+      <c r="L87">
+        <v>85.3</v>
+      </c>
+      <c r="M87">
+        <v>231.518988</v>
+      </c>
+      <c r="N87">
+        <v>-146.218988</v>
+      </c>
+      <c r="O87">
+        <v>-18.2773735</v>
+      </c>
+      <c r="P87">
+        <v>-127.9416145</v>
+      </c>
+      <c r="Q87">
+        <v>-95.94161449999997</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4099008640822548</v>
+      </c>
+      <c r="T87">
+        <v>5.203766709167153</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04605453786796961</v>
+      </c>
+      <c r="W87">
+        <v>0.2278021763571288</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.368436302943757</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2571169795158978</v>
+      </c>
+      <c r="C88">
+        <v>-464.3224341178411</v>
+      </c>
+      <c r="D88">
+        <v>383.8935658821588</v>
+      </c>
+      <c r="E88">
+        <v>667.2159999999999</v>
+      </c>
+      <c r="F88">
+        <v>980.9159999999999</v>
+      </c>
+      <c r="G88">
+        <v>132.7</v>
+      </c>
+      <c r="H88">
+        <v>826.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>117.3</v>
+      </c>
+      <c r="K88">
+        <v>32</v>
+      </c>
+      <c r="L88">
+        <v>85.3</v>
+      </c>
+      <c r="M88">
+        <v>234.2427408</v>
+      </c>
+      <c r="N88">
+        <v>-148.9427408</v>
+      </c>
+      <c r="O88">
+        <v>-18.6178426</v>
+      </c>
+      <c r="P88">
+        <v>-130.3248982</v>
+      </c>
+      <c r="Q88">
+        <v>-98.32489820000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4364080686595587</v>
+      </c>
+      <c r="T88">
+        <v>5.575464331250521</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04551901998578391</v>
+      </c>
+      <c r="W88">
+        <v>0.2279300580273948</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3641521598862711</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2591169795158977</v>
+      </c>
+      <c r="C89">
+        <v>-478.7185615863702</v>
+      </c>
+      <c r="D89">
+        <v>380.9034384136297</v>
+      </c>
+      <c r="E89">
+        <v>678.6219999999998</v>
+      </c>
+      <c r="F89">
+        <v>992.3219999999999</v>
+      </c>
+      <c r="G89">
+        <v>132.7</v>
+      </c>
+      <c r="H89">
+        <v>826.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>117.3</v>
+      </c>
+      <c r="K89">
+        <v>32</v>
+      </c>
+      <c r="L89">
+        <v>85.3</v>
+      </c>
+      <c r="M89">
+        <v>236.9664936</v>
+      </c>
+      <c r="N89">
+        <v>-151.6664936</v>
+      </c>
+      <c r="O89">
+        <v>-18.9583117</v>
+      </c>
+      <c r="P89">
+        <v>-132.7081819</v>
+      </c>
+      <c r="Q89">
+        <v>-100.7081819</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.466993304710294</v>
+      </c>
+      <c r="T89">
+        <v>6.004346202885177</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04499581285951054</v>
+      </c>
+      <c r="W89">
+        <v>0.2280549998891489</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3599665028760843</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2611169795158978</v>
+      </c>
+      <c r="C90">
+        <v>-493.068469157645</v>
+      </c>
+      <c r="D90">
+        <v>377.959530842355</v>
+      </c>
+      <c r="E90">
+        <v>690.028</v>
+      </c>
+      <c r="F90">
+        <v>1003.728</v>
+      </c>
+      <c r="G90">
+        <v>132.7</v>
+      </c>
+      <c r="H90">
+        <v>826.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>117.3</v>
+      </c>
+      <c r="K90">
+        <v>32</v>
+      </c>
+      <c r="L90">
+        <v>85.3</v>
+      </c>
+      <c r="M90">
+        <v>239.6902464</v>
+      </c>
+      <c r="N90">
+        <v>-154.3902464</v>
+      </c>
+      <c r="O90">
+        <v>-19.2987808</v>
+      </c>
+      <c r="P90">
+        <v>-135.0914656</v>
+      </c>
+      <c r="Q90">
+        <v>-103.0914656</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5026760801028185</v>
+      </c>
+      <c r="T90">
+        <v>6.504708386458942</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04448449680428882</v>
+      </c>
+      <c r="W90">
+        <v>0.2281771021631359</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3558759744343105</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2631169795158978</v>
+      </c>
+      <c r="C91">
+        <v>-507.3732202786857</v>
+      </c>
+      <c r="D91">
+        <v>375.0607797213142</v>
+      </c>
+      <c r="E91">
+        <v>701.434</v>
+      </c>
+      <c r="F91">
+        <v>1015.134</v>
+      </c>
+      <c r="G91">
+        <v>132.7</v>
+      </c>
+      <c r="H91">
+        <v>826.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>117.3</v>
+      </c>
+      <c r="K91">
+        <v>32</v>
+      </c>
+      <c r="L91">
+        <v>85.3</v>
+      </c>
+      <c r="M91">
+        <v>242.4139992</v>
+      </c>
+      <c r="N91">
+        <v>-157.1139992</v>
+      </c>
+      <c r="O91">
+        <v>-19.6392499</v>
+      </c>
+      <c r="P91">
+        <v>-137.4747493</v>
+      </c>
+      <c r="Q91">
+        <v>-105.4747493</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5448466328394386</v>
+      </c>
+      <c r="T91">
+        <v>7.096045512500665</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04398467099749906</v>
+      </c>
+      <c r="W91">
+        <v>0.2282964605657972</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3518773679799926</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2651169795158978</v>
+      </c>
+      <c r="C92">
+        <v>-521.6338460204993</v>
+      </c>
+      <c r="D92">
+        <v>372.2061539795008</v>
+      </c>
+      <c r="E92">
+        <v>712.8399999999999</v>
+      </c>
+      <c r="F92">
+        <v>1026.54</v>
+      </c>
+      <c r="G92">
+        <v>132.7</v>
+      </c>
+      <c r="H92">
+        <v>826.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>117.3</v>
+      </c>
+      <c r="K92">
+        <v>32</v>
+      </c>
+      <c r="L92">
+        <v>85.3</v>
+      </c>
+      <c r="M92">
+        <v>245.137752</v>
+      </c>
+      <c r="N92">
+        <v>-159.837752</v>
+      </c>
+      <c r="O92">
+        <v>-19.979719</v>
+      </c>
+      <c r="P92">
+        <v>-139.858033</v>
+      </c>
+      <c r="Q92">
+        <v>-107.858033</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5954512961233824</v>
+      </c>
+      <c r="T92">
+        <v>7.805650063750733</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04349595243086018</v>
+      </c>
+      <c r="W92">
+        <v>0.2284131665595106</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3479676194468814</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2671169795158977</v>
+      </c>
+      <c r="C93">
+        <v>-535.8513463008572</v>
+      </c>
+      <c r="D93">
+        <v>369.3946536991427</v>
+      </c>
+      <c r="E93">
+        <v>724.2459999999999</v>
+      </c>
+      <c r="F93">
+        <v>1037.946</v>
+      </c>
+      <c r="G93">
+        <v>132.7</v>
+      </c>
+      <c r="H93">
+        <v>826.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>117.3</v>
+      </c>
+      <c r="K93">
+        <v>32</v>
+      </c>
+      <c r="L93">
+        <v>85.3</v>
+      </c>
+      <c r="M93">
+        <v>247.8615048</v>
+      </c>
+      <c r="N93">
+        <v>-162.5615048</v>
+      </c>
+      <c r="O93">
+        <v>-20.3201881</v>
+      </c>
+      <c r="P93">
+        <v>-142.2413167</v>
+      </c>
+      <c r="Q93">
+        <v>-110.2413167</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6573014401370916</v>
+      </c>
+      <c r="T93">
+        <v>8.672944515278591</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04301797493161996</v>
+      </c>
+      <c r="W93">
+        <v>0.2285273075863292</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3441437994529596</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2691169795158977</v>
+      </c>
+      <c r="C94">
+        <v>-550.0266910520735</v>
+      </c>
+      <c r="D94">
+        <v>366.6253089479264</v>
+      </c>
+      <c r="E94">
+        <v>735.6519999999998</v>
+      </c>
+      <c r="F94">
+        <v>1049.352</v>
+      </c>
+      <c r="G94">
+        <v>132.7</v>
+      </c>
+      <c r="H94">
+        <v>826.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>117.3</v>
+      </c>
+      <c r="K94">
+        <v>32</v>
+      </c>
+      <c r="L94">
+        <v>85.3</v>
+      </c>
+      <c r="M94">
+        <v>250.5852576</v>
+      </c>
+      <c r="N94">
+        <v>-165.2852576</v>
+      </c>
+      <c r="O94">
+        <v>-20.6606572</v>
+      </c>
+      <c r="P94">
+        <v>-144.6246004</v>
+      </c>
+      <c r="Q94">
+        <v>-112.6246004</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7346141201542282</v>
+      </c>
+      <c r="T94">
+        <v>9.757062579688419</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04255038824758061</v>
+      </c>
+      <c r="W94">
+        <v>0.2286389672864778</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3404031059806449</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2711169795158978</v>
+      </c>
+      <c r="C95">
+        <v>-564.1608213366408</v>
+      </c>
+      <c r="D95">
+        <v>363.8971786633593</v>
+      </c>
+      <c r="E95">
+        <v>747.058</v>
+      </c>
+      <c r="F95">
+        <v>1060.758</v>
+      </c>
+      <c r="G95">
+        <v>132.7</v>
+      </c>
+      <c r="H95">
+        <v>826.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>117.3</v>
+      </c>
+      <c r="K95">
+        <v>32</v>
+      </c>
+      <c r="L95">
+        <v>85.3</v>
+      </c>
+      <c r="M95">
+        <v>253.3090104</v>
+      </c>
+      <c r="N95">
+        <v>-168.0090104</v>
+      </c>
+      <c r="O95">
+        <v>-21.0011263</v>
+      </c>
+      <c r="P95">
+        <v>-147.0078841</v>
+      </c>
+      <c r="Q95">
+        <v>-115.0078841</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8340161373191182</v>
+      </c>
+      <c r="T95">
+        <v>11.15092866250105</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04209285719115501</v>
+      </c>
+      <c r="W95">
+        <v>0.2287482257027522</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3367428575292402</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2731169795158978</v>
+      </c>
+      <c r="C96">
+        <v>-578.2546504134266</v>
+      </c>
+      <c r="D96">
+        <v>361.2093495865734</v>
+      </c>
+      <c r="E96">
+        <v>758.4639999999999</v>
+      </c>
+      <c r="F96">
+        <v>1072.164</v>
+      </c>
+      <c r="G96">
+        <v>132.7</v>
+      </c>
+      <c r="H96">
+        <v>826.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>117.3</v>
+      </c>
+      <c r="K96">
+        <v>32</v>
+      </c>
+      <c r="L96">
+        <v>85.3</v>
+      </c>
+      <c r="M96">
+        <v>256.0327632</v>
+      </c>
+      <c r="N96">
+        <v>-170.7327632</v>
+      </c>
+      <c r="O96">
+        <v>-21.3415954</v>
+      </c>
+      <c r="P96">
+        <v>-149.3911678</v>
+      </c>
+      <c r="Q96">
+        <v>-117.3911678</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9665521602056379</v>
+      </c>
+      <c r="T96">
+        <v>13.0094167729179</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04164506083805761</v>
+      </c>
+      <c r="W96">
+        <v>0.2288551594718718</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.333160486704461</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2751169795158978</v>
+      </c>
+      <c r="C97">
+        <v>-592.3090647569666</v>
+      </c>
+      <c r="D97">
+        <v>358.5609352430334</v>
+      </c>
+      <c r="E97">
+        <v>769.8699999999999</v>
+      </c>
+      <c r="F97">
+        <v>1083.57</v>
+      </c>
+      <c r="G97">
+        <v>132.7</v>
+      </c>
+      <c r="H97">
+        <v>826.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>117.3</v>
+      </c>
+      <c r="K97">
+        <v>32</v>
+      </c>
+      <c r="L97">
+        <v>85.3</v>
+      </c>
+      <c r="M97">
+        <v>258.756516</v>
+      </c>
+      <c r="N97">
+        <v>-173.456516</v>
+      </c>
+      <c r="O97">
+        <v>-21.6820645</v>
+      </c>
+      <c r="P97">
+        <v>-151.7744515</v>
+      </c>
+      <c r="Q97">
+        <v>-119.7744515</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.152102592246766</v>
+      </c>
+      <c r="T97">
+        <v>15.61130012750148</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04120669177660438</v>
+      </c>
+      <c r="W97">
+        <v>0.2289598420037469</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3296535342128352</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2771169795158978</v>
+      </c>
+      <c r="C98">
+        <v>-606.3249250322393</v>
+      </c>
+      <c r="D98">
+        <v>355.9510749677606</v>
+      </c>
+      <c r="E98">
+        <v>781.2759999999998</v>
+      </c>
+      <c r="F98">
+        <v>1094.976</v>
+      </c>
+      <c r="G98">
+        <v>132.7</v>
+      </c>
+      <c r="H98">
+        <v>826.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>117.3</v>
+      </c>
+      <c r="K98">
+        <v>32</v>
+      </c>
+      <c r="L98">
+        <v>85.3</v>
+      </c>
+      <c r="M98">
+        <v>261.4802688</v>
+      </c>
+      <c r="N98">
+        <v>-176.1802688</v>
+      </c>
+      <c r="O98">
+        <v>-22.0225336</v>
+      </c>
+      <c r="P98">
+        <v>-154.1577352</v>
+      </c>
+      <c r="Q98">
+        <v>-122.1577352</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.430428240308455</v>
+      </c>
+      <c r="T98">
+        <v>19.51412515937681</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04077745540393142</v>
+      </c>
+      <c r="W98">
+        <v>0.2290623436495412</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3262196432314515</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2791169795158978</v>
+      </c>
+      <c r="C99">
+        <v>-620.3030670271805</v>
+      </c>
+      <c r="D99">
+        <v>353.3789329728193</v>
+      </c>
+      <c r="E99">
+        <v>792.6819999999998</v>
+      </c>
+      <c r="F99">
+        <v>1106.382</v>
+      </c>
+      <c r="G99">
+        <v>132.7</v>
+      </c>
+      <c r="H99">
+        <v>826.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>117.3</v>
+      </c>
+      <c r="K99">
+        <v>32</v>
+      </c>
+      <c r="L99">
+        <v>85.3</v>
+      </c>
+      <c r="M99">
+        <v>264.2040216</v>
+      </c>
+      <c r="N99">
+        <v>-178.9040216</v>
+      </c>
+      <c r="O99">
+        <v>-22.3630027</v>
+      </c>
+      <c r="P99">
+        <v>-156.5410189</v>
+      </c>
+      <c r="Q99">
+        <v>-124.5410189</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.894304320411273</v>
+      </c>
+      <c r="T99">
+        <v>26.01883354583575</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04035706926574656</v>
+      </c>
+      <c r="W99">
+        <v>0.2291627318593397</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3228565541259726</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2811169795158978</v>
+      </c>
+      <c r="C100">
+        <v>-634.2443025450564</v>
+      </c>
+      <c r="D100">
+        <v>350.8436974549434</v>
+      </c>
+      <c r="E100">
+        <v>804.0879999999997</v>
+      </c>
+      <c r="F100">
+        <v>1117.788</v>
+      </c>
+      <c r="G100">
+        <v>132.7</v>
+      </c>
+      <c r="H100">
+        <v>826.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>117.3</v>
+      </c>
+      <c r="K100">
+        <v>32</v>
+      </c>
+      <c r="L100">
+        <v>85.3</v>
+      </c>
+      <c r="M100">
+        <v>266.9277744</v>
+      </c>
+      <c r="N100">
+        <v>-181.6277744</v>
+      </c>
+      <c r="O100">
+        <v>-22.7034718</v>
+      </c>
+      <c r="P100">
+        <v>-158.9243026</v>
+      </c>
+      <c r="Q100">
+        <v>-126.9243026</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.822056480616909</v>
+      </c>
+      <c r="T100">
+        <v>39.02825031875362</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03994526243650425</v>
+      </c>
+      <c r="W100">
+        <v>0.2292610713301628</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3195620994920341</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2831169795158978</v>
+      </c>
+      <c r="C101">
+        <v>-648.1494202586969</v>
+      </c>
+      <c r="D101">
+        <v>348.3445797413031</v>
+      </c>
+      <c r="E101">
+        <v>815.4939999999999</v>
+      </c>
+      <c r="F101">
+        <v>1129.194</v>
+      </c>
+      <c r="G101">
+        <v>132.7</v>
+      </c>
+      <c r="H101">
+        <v>826.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>117.3</v>
+      </c>
+      <c r="K101">
+        <v>32</v>
+      </c>
+      <c r="L101">
+        <v>85.3</v>
+      </c>
+      <c r="M101">
+        <v>269.6515272</v>
+      </c>
+      <c r="N101">
+        <v>-184.3515272</v>
+      </c>
+      <c r="O101">
+        <v>-23.0439409</v>
+      </c>
+      <c r="P101">
+        <v>-161.3075863</v>
+      </c>
+      <c r="Q101">
+        <v>-129.3075863</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.605312961233818</v>
+      </c>
+      <c r="T101">
+        <v>78.05650063750724</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03954177493714561</v>
+      </c>
+      <c r="W101">
+        <v>0.2293574241450096</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3163341994971649</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_beverage_alcoholic.xlsx
@@ -1133,7 +1133,7 @@
         <v>8.40735068912711</v>
       </c>
       <c r="F2">
-        <v>9.832503570327111</v>
+        <v>9.83250357032712</v>
       </c>
       <c r="G2">
         <v>4.15835140997831</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08125543821026998</v>
+        <v>0.08119324391250712</v>
       </c>
       <c r="C2">
-        <v>1079.156525272584</v>
+        <v>1069.143118695878</v>
       </c>
       <c r="D2">
-        <v>921.0565252725844</v>
+        <v>921.8221186958775</v>
       </c>
       <c r="E2">
-        <v>-383.4</v>
+        <v>-372.621</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.779</v>
       </c>
       <c r="G2">
         <v>158.1</v>
@@ -1451,28 +1451,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5421837</v>
       </c>
       <c r="N2">
-        <v>54.90000000000001</v>
+        <v>54.3578163</v>
       </c>
       <c r="O2">
-        <v>6.862500000000001</v>
+        <v>6.7947270375</v>
       </c>
       <c r="P2">
-        <v>48.03750000000001</v>
+        <v>47.5630892625</v>
       </c>
       <c r="Q2">
-        <v>85.33750000000001</v>
+        <v>84.8630892625</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08125543821026998</v>
+        <v>0.08156880698233043</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6972006245310457</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>101.2571938256351</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08119324391250712</v>
+        <v>0.08113104961474428</v>
       </c>
       <c r="C3">
-        <v>1069.143118695878</v>
+        <v>1059.13098591916</v>
       </c>
       <c r="D3">
-        <v>921.8221186958775</v>
+        <v>922.5889859191603</v>
       </c>
       <c r="E3">
-        <v>-372.621</v>
+        <v>-361.842</v>
       </c>
       <c r="F3">
-        <v>10.779</v>
+        <v>21.558</v>
       </c>
       <c r="G3">
         <v>158.1</v>
@@ -1533,28 +1533,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M3">
-        <v>0.5421837</v>
+        <v>1.0843674</v>
       </c>
       <c r="N3">
-        <v>54.3578163</v>
+        <v>53.81563260000001</v>
       </c>
       <c r="O3">
-        <v>6.7947270375</v>
+        <v>6.726954075000001</v>
       </c>
       <c r="P3">
-        <v>47.5630892625</v>
+        <v>47.08867852500001</v>
       </c>
       <c r="Q3">
-        <v>84.8630892625</v>
+        <v>84.388678525</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08156880698233043</v>
+        <v>0.08188857103545336</v>
       </c>
       <c r="T3">
-        <v>0.6972006245310457</v>
+        <v>0.7034334211029306</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>101.2571938256351</v>
+        <v>50.62859691281756</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08113104961474428</v>
+        <v>0.08106885531698146</v>
       </c>
       <c r="C4">
-        <v>1059.13098591916</v>
+        <v>1049.120130124116</v>
       </c>
       <c r="D4">
-        <v>922.5889859191603</v>
+        <v>923.357130124116</v>
       </c>
       <c r="E4">
-        <v>-361.842</v>
+        <v>-351.063</v>
       </c>
       <c r="F4">
-        <v>21.558</v>
+        <v>32.337</v>
       </c>
       <c r="G4">
         <v>158.1</v>
@@ -1615,28 +1615,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M4">
-        <v>1.0843674</v>
+        <v>1.6265511</v>
       </c>
       <c r="N4">
-        <v>53.81563260000001</v>
+        <v>53.27344890000001</v>
       </c>
       <c r="O4">
-        <v>6.726954075000001</v>
+        <v>6.659181112500001</v>
       </c>
       <c r="P4">
-        <v>47.08867852500001</v>
+        <v>46.6142677875</v>
       </c>
       <c r="Q4">
-        <v>84.388678525</v>
+        <v>83.91426778749999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08188857103545336</v>
+        <v>0.08221492816183656</v>
       </c>
       <c r="T4">
-        <v>0.7034334211029306</v>
+        <v>0.7097947289443389</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>50.62859691281756</v>
+        <v>33.75239794187837</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08106885531698146</v>
+        <v>0.08100666101921862</v>
       </c>
       <c r="C5">
-        <v>1049.120130124116</v>
+        <v>1039.110554503034</v>
       </c>
       <c r="D5">
-        <v>923.357130124116</v>
+        <v>924.1265545030342</v>
       </c>
       <c r="E5">
-        <v>-351.063</v>
+        <v>-340.284</v>
       </c>
       <c r="F5">
-        <v>32.337</v>
+        <v>43.11600000000001</v>
       </c>
       <c r="G5">
         <v>158.1</v>
@@ -1697,28 +1697,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M5">
-        <v>1.6265511</v>
+        <v>2.1687348</v>
       </c>
       <c r="N5">
-        <v>53.27344890000001</v>
+        <v>52.7312652</v>
       </c>
       <c r="O5">
-        <v>6.659181112500001</v>
+        <v>6.59140815</v>
       </c>
       <c r="P5">
-        <v>46.6142677875</v>
+        <v>46.13985705</v>
       </c>
       <c r="Q5">
-        <v>83.91426778749999</v>
+        <v>83.43985705</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08221492816183656</v>
+        <v>0.0825480843950194</v>
       </c>
       <c r="T5">
-        <v>0.7097947289443389</v>
+        <v>0.7162885640324432</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.75239794187837</v>
+        <v>25.31429845640878</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08100666101921862</v>
+        <v>0.08094446672145579</v>
       </c>
       <c r="C6">
-        <v>1039.110554503034</v>
+        <v>1029.102262258852</v>
       </c>
       <c r="D6">
-        <v>924.1265545030342</v>
+        <v>924.8972622588522</v>
       </c>
       <c r="E6">
-        <v>-340.284</v>
+        <v>-329.505</v>
       </c>
       <c r="F6">
-        <v>43.11600000000001</v>
+        <v>53.89500000000001</v>
       </c>
       <c r="G6">
         <v>158.1</v>
@@ -1779,28 +1779,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M6">
-        <v>2.1687348</v>
+        <v>2.7109185</v>
       </c>
       <c r="N6">
-        <v>52.7312652</v>
+        <v>52.18908150000001</v>
       </c>
       <c r="O6">
-        <v>6.59140815</v>
+        <v>6.523635187500001</v>
       </c>
       <c r="P6">
-        <v>46.13985705</v>
+        <v>45.66544631250001</v>
       </c>
       <c r="Q6">
-        <v>83.43985705</v>
+        <v>82.96544631250001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0825480843950194</v>
+        <v>0.08288825444363768</v>
       </c>
       <c r="T6">
-        <v>0.7162885640324432</v>
+        <v>0.7229191114381919</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.31429845640878</v>
+        <v>20.25143876512702</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08094446672145579</v>
+        <v>0.08088227242369295</v>
       </c>
       <c r="C7">
-        <v>1029.102262258852</v>
+        <v>1019.095256605202</v>
       </c>
       <c r="D7">
-        <v>924.8972622588522</v>
+        <v>925.6692566052018</v>
       </c>
       <c r="E7">
-        <v>-329.505</v>
+        <v>-318.726</v>
       </c>
       <c r="F7">
-        <v>53.89500000000001</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="G7">
         <v>158.1</v>
@@ -1861,28 +1861,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M7">
-        <v>2.7109185</v>
+        <v>3.2531022</v>
       </c>
       <c r="N7">
-        <v>52.18908150000001</v>
+        <v>51.6468978</v>
       </c>
       <c r="O7">
-        <v>6.523635187500001</v>
+        <v>6.455862225000001</v>
       </c>
       <c r="P7">
-        <v>45.66544631250001</v>
+        <v>45.191035575</v>
       </c>
       <c r="Q7">
-        <v>82.96544631250001</v>
+        <v>82.491035575</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08288825444363768</v>
+        <v>0.08323566215286485</v>
       </c>
       <c r="T7">
-        <v>0.7229191114381919</v>
+        <v>0.7296907343206586</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.25143876512702</v>
+        <v>16.87619897093919</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08088227242369295</v>
+        <v>0.0808200781259301</v>
       </c>
       <c r="C8">
-        <v>1019.095256605202</v>
+        <v>1009.089540766453</v>
       </c>
       <c r="D8">
-        <v>925.6692566052018</v>
+        <v>926.4425407664534</v>
       </c>
       <c r="E8">
-        <v>-318.726</v>
+        <v>-307.947</v>
       </c>
       <c r="F8">
-        <v>64.67400000000001</v>
+        <v>75.453</v>
       </c>
       <c r="G8">
         <v>158.1</v>
@@ -1943,28 +1943,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M8">
-        <v>3.2531022</v>
+        <v>3.7952859</v>
       </c>
       <c r="N8">
-        <v>51.6468978</v>
+        <v>51.1047141</v>
       </c>
       <c r="O8">
-        <v>6.455862225000001</v>
+        <v>6.3880892625</v>
       </c>
       <c r="P8">
-        <v>45.191035575</v>
+        <v>44.7166248375</v>
       </c>
       <c r="Q8">
-        <v>82.491035575</v>
+        <v>82.01662483749999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08323566215286485</v>
+        <v>0.08359054099562377</v>
       </c>
       <c r="T8">
-        <v>0.7296907343206586</v>
+        <v>0.7366079835016729</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.87619897093919</v>
+        <v>14.46531340366216</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0808200781259301</v>
+        <v>0.0808628838281673</v>
       </c>
       <c r="C9">
-        <v>1009.089540766453</v>
+        <v>997.7781834919513</v>
       </c>
       <c r="D9">
-        <v>926.4425407664534</v>
+        <v>925.9101834919512</v>
       </c>
       <c r="E9">
-        <v>-307.9469999999999</v>
+        <v>-297.1679999999999</v>
       </c>
       <c r="F9">
-        <v>75.45300000000002</v>
+        <v>86.23200000000001</v>
       </c>
       <c r="G9">
         <v>158.1</v>
@@ -2025,45 +2025,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M9">
-        <v>3.795285900000001</v>
+        <v>4.466817600000001</v>
       </c>
       <c r="N9">
-        <v>51.1047141</v>
+        <v>50.43318240000001</v>
       </c>
       <c r="O9">
-        <v>6.3880892625</v>
+        <v>6.304147800000001</v>
       </c>
       <c r="P9">
-        <v>44.7166248375</v>
+        <v>44.1290346</v>
       </c>
       <c r="Q9">
-        <v>82.01662483749999</v>
+        <v>81.42903459999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08359054099562377</v>
+        <v>0.08395313459583401</v>
       </c>
       <c r="T9">
-        <v>0.7366079835016729</v>
+        <v>0.7436756076648833</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.46531340366216</v>
+        <v>12.29062946290889</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0808628838281673</v>
+        <v>0.08081381453040443</v>
       </c>
       <c r="C10">
-        <v>997.7781834919513</v>
+        <v>987.6094899264581</v>
       </c>
       <c r="D10">
-        <v>925.9101834919512</v>
+        <v>926.520489926458</v>
       </c>
       <c r="E10">
-        <v>-297.1679999999999</v>
+        <v>-286.389</v>
       </c>
       <c r="F10">
-        <v>86.23200000000001</v>
+        <v>97.01100000000001</v>
       </c>
       <c r="G10">
         <v>158.1</v>
@@ -2107,28 +2107,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M10">
-        <v>4.466817600000001</v>
+        <v>5.0251698</v>
       </c>
       <c r="N10">
-        <v>50.43318240000001</v>
+        <v>49.87483020000001</v>
       </c>
       <c r="O10">
-        <v>6.304147800000001</v>
+        <v>6.234353775000001</v>
       </c>
       <c r="P10">
-        <v>44.1290346</v>
+        <v>43.640476425</v>
       </c>
       <c r="Q10">
-        <v>81.42903459999999</v>
+        <v>80.940476425</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08395313459583401</v>
+        <v>0.08432369728615871</v>
       </c>
       <c r="T10">
-        <v>0.7436756076648833</v>
+        <v>0.7508985642272848</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.29062946290889</v>
+        <v>10.92500396703013</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08081381453040443</v>
+        <v>0.0807647452326416</v>
       </c>
       <c r="C11">
-        <v>987.6094899264581</v>
+        <v>977.4416014490296</v>
       </c>
       <c r="D11">
-        <v>926.520489926458</v>
+        <v>927.1316014490296</v>
       </c>
       <c r="E11">
-        <v>-286.389</v>
+        <v>-275.61</v>
       </c>
       <c r="F11">
-        <v>97.01100000000001</v>
+        <v>107.79</v>
       </c>
       <c r="G11">
         <v>158.1</v>
@@ -2189,28 +2189,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M11">
-        <v>5.0251698</v>
+        <v>5.583522</v>
       </c>
       <c r="N11">
-        <v>49.87483020000001</v>
+        <v>49.316478</v>
       </c>
       <c r="O11">
-        <v>6.234353775000001</v>
+        <v>6.16455975</v>
       </c>
       <c r="P11">
-        <v>43.640476425</v>
+        <v>43.15191825</v>
       </c>
       <c r="Q11">
-        <v>80.940476425</v>
+        <v>80.45191825000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08432369728615871</v>
+        <v>0.08470249470293512</v>
       </c>
       <c r="T11">
-        <v>0.7508985642272848</v>
+        <v>0.7582820309355179</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.92500396703013</v>
+        <v>9.832503570327116</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0807647452326416</v>
+        <v>0.08087930093487876</v>
       </c>
       <c r="C12">
-        <v>977.4416014490296</v>
+        <v>965.2371728329663</v>
       </c>
       <c r="D12">
-        <v>927.1316014490296</v>
+        <v>925.7061728329663</v>
       </c>
       <c r="E12">
-        <v>-275.61</v>
+        <v>-264.831</v>
       </c>
       <c r="F12">
-        <v>107.79</v>
+        <v>118.569</v>
       </c>
       <c r="G12">
         <v>158.1</v>
@@ -2271,45 +2271,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M12">
-        <v>5.583522000000001</v>
+        <v>6.343441500000001</v>
       </c>
       <c r="N12">
-        <v>49.316478</v>
+        <v>48.55655850000001</v>
       </c>
       <c r="O12">
-        <v>6.16455975</v>
+        <v>6.069569812500001</v>
       </c>
       <c r="P12">
-        <v>43.15191825</v>
+        <v>42.48698868750001</v>
       </c>
       <c r="Q12">
-        <v>80.45191825000001</v>
+        <v>79.78698868750001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08470249470293512</v>
+        <v>0.08508980442121208</v>
       </c>
       <c r="T12">
-        <v>0.7582820309355179</v>
+        <v>0.7658314182439357</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>9.832503570327114</v>
+        <v>8.654608070398378</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08087930093487876</v>
+        <v>0.08084510663711592</v>
       </c>
       <c r="C13">
-        <v>965.2371728329663</v>
+        <v>954.8831969559426</v>
       </c>
       <c r="D13">
-        <v>925.7061728329663</v>
+        <v>926.1311969559425</v>
       </c>
       <c r="E13">
-        <v>-264.831</v>
+        <v>-254.052</v>
       </c>
       <c r="F13">
-        <v>118.569</v>
+        <v>129.348</v>
       </c>
       <c r="G13">
         <v>158.1</v>
@@ -2353,28 +2353,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M13">
-        <v>6.343441500000001</v>
+        <v>6.920118</v>
       </c>
       <c r="N13">
-        <v>48.55655850000001</v>
+        <v>47.979882</v>
       </c>
       <c r="O13">
-        <v>6.069569812500001</v>
+        <v>5.99748525</v>
       </c>
       <c r="P13">
-        <v>42.48698868750001</v>
+        <v>41.98239675000001</v>
       </c>
       <c r="Q13">
-        <v>79.78698868750001</v>
+        <v>79.28239675</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08508980442121208</v>
+        <v>0.08548591663308627</v>
       </c>
       <c r="T13">
-        <v>0.7658314182439357</v>
+        <v>0.7735523825366358</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.654608070398378</v>
+        <v>7.933390731198514</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08084510663711592</v>
+        <v>0.08090191233935309</v>
       </c>
       <c r="C14">
-        <v>954.8831969559426</v>
+        <v>943.3983345557012</v>
       </c>
       <c r="D14">
-        <v>926.1311969559425</v>
+        <v>925.4253345557012</v>
       </c>
       <c r="E14">
-        <v>-254.052</v>
+        <v>-243.273</v>
       </c>
       <c r="F14">
-        <v>129.348</v>
+        <v>140.127</v>
       </c>
       <c r="G14">
         <v>158.1</v>
@@ -2435,45 +2435,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M14">
-        <v>6.920118</v>
+        <v>7.608896100000001</v>
       </c>
       <c r="N14">
-        <v>47.979882</v>
+        <v>47.2911039</v>
       </c>
       <c r="O14">
-        <v>5.99748525</v>
+        <v>5.9113879875</v>
       </c>
       <c r="P14">
-        <v>41.98239675000001</v>
+        <v>41.3797159125</v>
       </c>
       <c r="Q14">
-        <v>79.28239675</v>
+        <v>78.6797159125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08548591663308627</v>
+        <v>0.08589113487281964</v>
       </c>
       <c r="T14">
-        <v>0.7735523825366358</v>
+        <v>0.7814508402613521</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.933390731198514</v>
+        <v>7.215238489062822</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08090191233935309</v>
+        <v>0.08087471804159026</v>
       </c>
       <c r="C15">
-        <v>943.3983345557012</v>
+        <v>932.957114082698</v>
       </c>
       <c r="D15">
-        <v>925.4253345557012</v>
+        <v>925.7631140826981</v>
       </c>
       <c r="E15">
-        <v>-243.273</v>
+        <v>-232.4939999999999</v>
       </c>
       <c r="F15">
-        <v>140.127</v>
+        <v>150.906</v>
       </c>
       <c r="G15">
         <v>158.1</v>
@@ -2517,28 +2517,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M15">
-        <v>7.608896100000001</v>
+        <v>8.194195800000003</v>
       </c>
       <c r="N15">
-        <v>47.2911039</v>
+        <v>46.7058042</v>
       </c>
       <c r="O15">
-        <v>5.9113879875</v>
+        <v>5.838225525</v>
       </c>
       <c r="P15">
-        <v>41.3797159125</v>
+        <v>40.867578675</v>
       </c>
       <c r="Q15">
-        <v>78.6797159125</v>
+        <v>78.167578675</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08589113487281964</v>
+        <v>0.08630577679254681</v>
       </c>
       <c r="T15">
-        <v>0.7814508402613521</v>
+        <v>0.7895329830494338</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.215238489062822</v>
+        <v>6.699864311272619</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08087471804159026</v>
+        <v>0.08084752374382742</v>
       </c>
       <c r="C16">
-        <v>932.957114082698</v>
+        <v>922.5161402782575</v>
       </c>
       <c r="D16">
-        <v>925.7631140826981</v>
+        <v>926.1011402782576</v>
       </c>
       <c r="E16">
-        <v>-232.4939999999999</v>
+        <v>-221.7149999999999</v>
       </c>
       <c r="F16">
-        <v>150.906</v>
+        <v>161.685</v>
       </c>
       <c r="G16">
         <v>158.1</v>
@@ -2599,28 +2599,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M16">
-        <v>8.194195800000003</v>
+        <v>8.779495500000001</v>
       </c>
       <c r="N16">
-        <v>46.7058042</v>
+        <v>46.1205045</v>
       </c>
       <c r="O16">
-        <v>5.838225525</v>
+        <v>5.7650630625</v>
       </c>
       <c r="P16">
-        <v>40.867578675</v>
+        <v>40.35544143750001</v>
       </c>
       <c r="Q16">
-        <v>78.167578675</v>
+        <v>77.6554414375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08630577679254681</v>
+        <v>0.08673017499273813</v>
       </c>
       <c r="T16">
-        <v>0.7895329830494338</v>
+        <v>0.7978052939031175</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.699864311272619</v>
+        <v>6.253206690521112</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08084752374382742</v>
+        <v>0.08096032944606457</v>
       </c>
       <c r="C17">
-        <v>922.5161402782576</v>
+        <v>910.336570292908</v>
       </c>
       <c r="D17">
-        <v>926.1011402782576</v>
+        <v>924.7005702929082</v>
       </c>
       <c r="E17">
-        <v>-221.715</v>
+        <v>-210.936</v>
       </c>
       <c r="F17">
-        <v>161.685</v>
+        <v>172.464</v>
       </c>
       <c r="G17">
         <v>158.1</v>
@@ -2681,45 +2681,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M17">
-        <v>8.779495499999999</v>
+        <v>9.537259200000001</v>
       </c>
       <c r="N17">
-        <v>46.12050450000001</v>
+        <v>45.3627408</v>
       </c>
       <c r="O17">
-        <v>5.765063062500001</v>
+        <v>5.670342600000001</v>
       </c>
       <c r="P17">
-        <v>40.35544143750001</v>
+        <v>39.69239820000001</v>
       </c>
       <c r="Q17">
-        <v>77.6554414375</v>
+        <v>76.9923982</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08673017499273813</v>
+        <v>0.08716467791198164</v>
       </c>
       <c r="T17">
-        <v>0.7978052939031174</v>
+        <v>0.8062745645390317</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.253206690521114</v>
+        <v>5.756370761109229</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08096032944606457</v>
+        <v>0.08094188514830172</v>
       </c>
       <c r="C18">
-        <v>910.336570292908</v>
+        <v>899.786280736237</v>
       </c>
       <c r="D18">
-        <v>924.7005702929082</v>
+        <v>924.9292807362372</v>
       </c>
       <c r="E18">
-        <v>-210.936</v>
+        <v>-200.157</v>
       </c>
       <c r="F18">
-        <v>172.464</v>
+        <v>183.243</v>
       </c>
       <c r="G18">
         <v>158.1</v>
@@ -2763,28 +2763,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M18">
-        <v>9.537259200000001</v>
+        <v>10.1333379</v>
       </c>
       <c r="N18">
-        <v>45.3627408</v>
+        <v>44.7666621</v>
       </c>
       <c r="O18">
-        <v>5.670342600000001</v>
+        <v>5.595832762500001</v>
       </c>
       <c r="P18">
-        <v>39.69239820000001</v>
+        <v>39.1708293375</v>
       </c>
       <c r="Q18">
-        <v>76.9923982</v>
+        <v>76.47082933749999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08716467791198164</v>
+        <v>0.08760965078108643</v>
       </c>
       <c r="T18">
-        <v>0.8062745645390317</v>
+        <v>0.8149479139854497</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.756370761109229</v>
+        <v>5.417760716338099</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08094188514830172</v>
+        <v>0.08092344085053889</v>
       </c>
       <c r="C19">
-        <v>899.786280736237</v>
+        <v>889.2361043435664</v>
       </c>
       <c r="D19">
-        <v>924.9292807362372</v>
+        <v>925.1581043435664</v>
       </c>
       <c r="E19">
-        <v>-200.157</v>
+        <v>-189.3779999999999</v>
       </c>
       <c r="F19">
-        <v>183.243</v>
+        <v>194.022</v>
       </c>
       <c r="G19">
         <v>158.1</v>
@@ -2845,28 +2845,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M19">
-        <v>10.1333379</v>
+        <v>10.7294166</v>
       </c>
       <c r="N19">
-        <v>44.7666621</v>
+        <v>44.17058340000001</v>
       </c>
       <c r="O19">
-        <v>5.595832762500001</v>
+        <v>5.521322925000001</v>
       </c>
       <c r="P19">
-        <v>39.1708293375</v>
+        <v>38.64926047500001</v>
       </c>
       <c r="Q19">
-        <v>76.47082933749999</v>
+        <v>75.949260475</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08760965078108643</v>
+        <v>0.08806547664699865</v>
       </c>
       <c r="T19">
-        <v>0.8149479139854497</v>
+        <v>0.8238328085403172</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.417760716338099</v>
+        <v>5.11677400987487</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0809234408505389</v>
+        <v>0.08090499655277605</v>
       </c>
       <c r="C20">
-        <v>889.2361043435661</v>
+        <v>878.6860411989054</v>
       </c>
       <c r="D20">
-        <v>925.1581043435663</v>
+        <v>925.3870411989055</v>
       </c>
       <c r="E20">
-        <v>-189.378</v>
+        <v>-178.599</v>
       </c>
       <c r="F20">
-        <v>194.022</v>
+        <v>204.801</v>
       </c>
       <c r="G20">
         <v>158.1</v>
@@ -2927,28 +2927,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M20">
-        <v>10.7294166</v>
+        <v>11.3254953</v>
       </c>
       <c r="N20">
-        <v>44.17058340000001</v>
+        <v>43.57450470000001</v>
       </c>
       <c r="O20">
-        <v>5.521322925000001</v>
+        <v>5.446813087500001</v>
       </c>
       <c r="P20">
-        <v>38.64926047500001</v>
+        <v>38.1276916125</v>
       </c>
       <c r="Q20">
-        <v>75.949260475</v>
+        <v>75.4276916125</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08806547664699865</v>
+        <v>0.08853255747256303</v>
       </c>
       <c r="T20">
-        <v>0.8238328085403172</v>
+        <v>0.8329370832076504</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.11677400987487</v>
+        <v>4.847470114618298</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08090499655277605</v>
+        <v>0.08088655225501322</v>
       </c>
       <c r="C21">
-        <v>878.6860411989054</v>
+        <v>868.1360913863474</v>
       </c>
       <c r="D21">
-        <v>925.3870411989055</v>
+        <v>925.6160913863474</v>
       </c>
       <c r="E21">
-        <v>-178.599</v>
+        <v>-167.8199999999999</v>
       </c>
       <c r="F21">
-        <v>204.801</v>
+        <v>215.58</v>
       </c>
       <c r="G21">
         <v>158.1</v>
@@ -3009,28 +3009,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M21">
-        <v>11.3254953</v>
+        <v>11.921574</v>
       </c>
       <c r="N21">
-        <v>43.57450470000001</v>
+        <v>42.978426</v>
       </c>
       <c r="O21">
-        <v>5.446813087500001</v>
+        <v>5.37230325</v>
       </c>
       <c r="P21">
-        <v>38.1276916125</v>
+        <v>37.60612275</v>
       </c>
       <c r="Q21">
-        <v>75.4276916125</v>
+        <v>74.90612274999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08853255747256303</v>
+        <v>0.08901131531876652</v>
       </c>
       <c r="T21">
-        <v>0.8329370832076504</v>
+        <v>0.8422689647416669</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.847470114618298</v>
+        <v>4.605096608887383</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08088655225501322</v>
+        <v>0.08132748295725038</v>
       </c>
       <c r="C22">
-        <v>868.1360913863474</v>
+        <v>851.9122639545632</v>
       </c>
       <c r="D22">
-        <v>925.6160913863474</v>
+        <v>920.1712639545632</v>
       </c>
       <c r="E22">
-        <v>-167.8199999999999</v>
+        <v>-157.0409999999999</v>
       </c>
       <c r="F22">
-        <v>215.58</v>
+        <v>226.359</v>
       </c>
       <c r="G22">
         <v>158.1</v>
@@ -3091,45 +3091,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M22">
-        <v>11.921574</v>
+        <v>13.0835502</v>
       </c>
       <c r="N22">
-        <v>42.978426</v>
+        <v>41.8164498</v>
       </c>
       <c r="O22">
-        <v>5.37230325</v>
+        <v>5.227056225</v>
       </c>
       <c r="P22">
-        <v>37.60612275</v>
+        <v>36.589393575</v>
       </c>
       <c r="Q22">
-        <v>74.90612274999999</v>
+        <v>73.889393575</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08901131531876652</v>
+        <v>0.08950219361677264</v>
       </c>
       <c r="T22">
-        <v>0.8422689647416669</v>
+        <v>0.8518370964411017</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.605096608887383</v>
+        <v>4.196108790104997</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08132748295725038</v>
+        <v>0.08133091365948755</v>
       </c>
       <c r="C23">
-        <v>851.9122639545632</v>
+        <v>841.0911510981545</v>
       </c>
       <c r="D23">
-        <v>920.1712639545632</v>
+        <v>920.1291510981546</v>
       </c>
       <c r="E23">
-        <v>-157.041</v>
+        <v>-146.2619999999999</v>
       </c>
       <c r="F23">
-        <v>226.359</v>
+        <v>237.138</v>
       </c>
       <c r="G23">
         <v>158.1</v>
@@ -3173,28 +3173,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M23">
-        <v>13.0835502</v>
+        <v>13.7065764</v>
       </c>
       <c r="N23">
-        <v>41.8164498</v>
+        <v>41.1934236</v>
       </c>
       <c r="O23">
-        <v>5.227056225</v>
+        <v>5.14917795</v>
       </c>
       <c r="P23">
-        <v>36.589393575</v>
+        <v>36.04424565</v>
       </c>
       <c r="Q23">
-        <v>73.889393575</v>
+        <v>73.34424565</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08950219361677264</v>
+        <v>0.09000565853780455</v>
       </c>
       <c r="T23">
-        <v>0.8518370964411016</v>
+        <v>0.8616505648507783</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.196108790104997</v>
+        <v>4.005376572372952</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08133091365948755</v>
+        <v>0.08203871936172472</v>
       </c>
       <c r="C24">
-        <v>841.0911510981545</v>
+        <v>821.7052985726931</v>
       </c>
       <c r="D24">
-        <v>920.1291510981546</v>
+        <v>911.5222985726931</v>
       </c>
       <c r="E24">
-        <v>-146.2619999999999</v>
+        <v>-135.4829999999999</v>
       </c>
       <c r="F24">
-        <v>237.138</v>
+        <v>247.917</v>
       </c>
       <c r="G24">
         <v>158.1</v>
@@ -3255,45 +3255,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M24">
-        <v>13.7065764</v>
+        <v>15.1973121</v>
       </c>
       <c r="N24">
-        <v>41.1934236</v>
+        <v>39.7026879</v>
       </c>
       <c r="O24">
-        <v>5.14917795</v>
+        <v>4.9628359875</v>
       </c>
       <c r="P24">
-        <v>36.04424565</v>
+        <v>34.7398519125</v>
       </c>
       <c r="Q24">
-        <v>73.34424565</v>
+        <v>72.0398519125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09000565853780455</v>
+        <v>0.09052220046977236</v>
       </c>
       <c r="T24">
-        <v>0.8616505648507783</v>
+        <v>0.871718928543823</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.005376572372952</v>
+        <v>3.612480920227992</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08203871936172472</v>
+        <v>0.08266077506396188</v>
       </c>
       <c r="C25">
-        <v>821.7052985726931</v>
+        <v>803.4940117521907</v>
       </c>
       <c r="D25">
-        <v>911.5222985726931</v>
+        <v>904.0900117521907</v>
       </c>
       <c r="E25">
-        <v>-135.4829999999999</v>
+        <v>-124.704</v>
       </c>
       <c r="F25">
-        <v>247.917</v>
+        <v>258.696</v>
       </c>
       <c r="G25">
         <v>158.1</v>
@@ -3337,45 +3337,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M25">
-        <v>15.1973121</v>
+        <v>16.5824136</v>
       </c>
       <c r="N25">
-        <v>39.7026879</v>
+        <v>38.3175864</v>
       </c>
       <c r="O25">
-        <v>4.9628359875</v>
+        <v>4.7896983</v>
       </c>
       <c r="P25">
-        <v>34.7398519125</v>
+        <v>33.52788810000001</v>
       </c>
       <c r="Q25">
-        <v>72.0398519125</v>
+        <v>70.8278881</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09052220046977236</v>
+        <v>0.09105233561047615</v>
       </c>
       <c r="T25">
-        <v>0.871718928543823</v>
+        <v>0.8820522491761587</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.612480920227992</v>
+        <v>3.310736381584403</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08266077506396188</v>
+        <v>0.08271933076619904</v>
       </c>
       <c r="C26">
-        <v>803.4940117521907</v>
+        <v>792.0216281809991</v>
       </c>
       <c r="D26">
-        <v>904.0900117521907</v>
+        <v>903.3966281809991</v>
       </c>
       <c r="E26">
-        <v>-124.704</v>
+        <v>-113.925</v>
       </c>
       <c r="F26">
-        <v>258.696</v>
+        <v>269.475</v>
       </c>
       <c r="G26">
         <v>158.1</v>
@@ -3419,28 +3419,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M26">
-        <v>16.5824136</v>
+        <v>17.2733475</v>
       </c>
       <c r="N26">
-        <v>38.3175864</v>
+        <v>37.62665250000001</v>
       </c>
       <c r="O26">
-        <v>4.7896983</v>
+        <v>4.703331562500001</v>
       </c>
       <c r="P26">
-        <v>33.52788810000001</v>
+        <v>32.92332093750001</v>
       </c>
       <c r="Q26">
-        <v>70.8278881</v>
+        <v>70.22332093750001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09105233561047615</v>
+        <v>0.09159660768826539</v>
       </c>
       <c r="T26">
-        <v>0.8820522491761585</v>
+        <v>0.8926611250253563</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.310736381584403</v>
+        <v>3.178306926321027</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08271933076619904</v>
+        <v>0.08277788646843622</v>
       </c>
       <c r="C27">
-        <v>792.0216281809991</v>
+        <v>780.5503073631231</v>
       </c>
       <c r="D27">
-        <v>903.3966281809991</v>
+        <v>902.7043073631231</v>
       </c>
       <c r="E27">
-        <v>-113.925</v>
+        <v>-103.146</v>
       </c>
       <c r="F27">
-        <v>269.475</v>
+        <v>280.254</v>
       </c>
       <c r="G27">
         <v>158.1</v>
@@ -3501,28 +3501,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M27">
-        <v>17.2733475</v>
+        <v>17.9642814</v>
       </c>
       <c r="N27">
-        <v>37.62665250000001</v>
+        <v>36.9357186</v>
       </c>
       <c r="O27">
-        <v>4.703331562500001</v>
+        <v>4.616964825</v>
       </c>
       <c r="P27">
-        <v>32.92332093750001</v>
+        <v>32.318753775</v>
       </c>
       <c r="Q27">
-        <v>70.22332093750001</v>
+        <v>69.618753775</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09159660768826539</v>
+        <v>0.09215558982221109</v>
       </c>
       <c r="T27">
-        <v>0.8926611250253563</v>
+        <v>0.9035567272488568</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.178306926321027</v>
+        <v>3.056064352231757</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08277788646843622</v>
+        <v>0.08467919217067338</v>
       </c>
       <c r="C28">
-        <v>780.5503073631231</v>
+        <v>747.8542274650237</v>
       </c>
       <c r="D28">
-        <v>902.7043073631231</v>
+        <v>880.7872274650238</v>
       </c>
       <c r="E28">
-        <v>-103.146</v>
+        <v>-92.36699999999996</v>
       </c>
       <c r="F28">
-        <v>280.254</v>
+        <v>291.033</v>
       </c>
       <c r="G28">
         <v>158.1</v>
@@ -3583,45 +3583,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M28">
-        <v>17.9642814</v>
+        <v>20.9252727</v>
       </c>
       <c r="N28">
-        <v>36.9357186</v>
+        <v>33.9747273</v>
       </c>
       <c r="O28">
-        <v>4.616964825</v>
+        <v>4.2468409125</v>
       </c>
       <c r="P28">
-        <v>32.318753775</v>
+        <v>29.7278863875</v>
       </c>
       <c r="Q28">
-        <v>69.618753775</v>
+        <v>67.02788638749999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09215558982221109</v>
+        <v>0.09272988653516899</v>
       </c>
       <c r="T28">
-        <v>0.9035567272488568</v>
+        <v>0.9147508391223163</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.056064352231757</v>
+        <v>2.623621722263146</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08467919217067338</v>
+        <v>0.08480599787291053</v>
       </c>
       <c r="C29">
-        <v>747.8542274650237</v>
+        <v>735.651285339997</v>
       </c>
       <c r="D29">
-        <v>880.7872274650238</v>
+        <v>879.3632853399972</v>
       </c>
       <c r="E29">
-        <v>-92.36699999999996</v>
+        <v>-81.58799999999991</v>
       </c>
       <c r="F29">
-        <v>291.033</v>
+        <v>301.8120000000001</v>
       </c>
       <c r="G29">
         <v>158.1</v>
@@ -3665,28 +3665,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M29">
-        <v>20.9252727</v>
+        <v>21.70028280000001</v>
       </c>
       <c r="N29">
-        <v>33.9747273</v>
+        <v>33.19971719999999</v>
       </c>
       <c r="O29">
-        <v>4.2468409125</v>
+        <v>4.149964649999999</v>
       </c>
       <c r="P29">
-        <v>29.7278863875</v>
+        <v>29.04975254999999</v>
       </c>
       <c r="Q29">
-        <v>67.02788638749999</v>
+        <v>66.34975254999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09272988653516899</v>
+        <v>0.09332013593459795</v>
       </c>
       <c r="T29">
-        <v>0.9147508391223163</v>
+        <v>0.9262558985478162</v>
       </c>
       <c r="U29">
         <v>0.07190000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.623621722263146</v>
+        <v>2.529920946468033</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08480599787291053</v>
+        <v>0.08592242857514769</v>
       </c>
       <c r="C30">
-        <v>735.651285339997</v>
+        <v>712.5314471171503</v>
       </c>
       <c r="D30">
-        <v>879.3632853399972</v>
+        <v>867.0224471171505</v>
       </c>
       <c r="E30">
-        <v>-81.58799999999991</v>
+        <v>-70.80899999999991</v>
       </c>
       <c r="F30">
-        <v>301.8120000000001</v>
+        <v>312.5910000000001</v>
       </c>
       <c r="G30">
         <v>158.1</v>
@@ -3747,45 +3747,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M30">
-        <v>21.70028280000001</v>
+        <v>23.69439780000001</v>
       </c>
       <c r="N30">
-        <v>33.19971719999999</v>
+        <v>31.2056022</v>
       </c>
       <c r="O30">
-        <v>4.149964649999999</v>
+        <v>3.900700275</v>
       </c>
       <c r="P30">
-        <v>29.04975254999999</v>
+        <v>27.304901925</v>
       </c>
       <c r="Q30">
-        <v>66.34975254999999</v>
+        <v>64.60490192499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09332013593459795</v>
+        <v>0.0939270120776728</v>
       </c>
       <c r="T30">
-        <v>0.9262558985478162</v>
+        <v>0.938085044154316</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.529920946468033</v>
+        <v>2.317003388877011</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08592242857514767</v>
+        <v>0.08608335927738484</v>
       </c>
       <c r="C31">
-        <v>712.5314471171506</v>
+        <v>700.0020518059296</v>
       </c>
       <c r="D31">
-        <v>867.0224471171507</v>
+        <v>865.2720518059296</v>
       </c>
       <c r="E31">
-        <v>-70.80899999999997</v>
+        <v>-60.02999999999997</v>
       </c>
       <c r="F31">
-        <v>312.591</v>
+        <v>323.37</v>
       </c>
       <c r="G31">
         <v>158.1</v>
@@ -3829,28 +3829,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M31">
-        <v>23.6943978</v>
+        <v>24.511446</v>
       </c>
       <c r="N31">
-        <v>31.2056022</v>
+        <v>30.388554</v>
       </c>
       <c r="O31">
-        <v>3.900700275000001</v>
+        <v>3.79856925</v>
       </c>
       <c r="P31">
-        <v>27.304901925</v>
+        <v>26.58998475</v>
       </c>
       <c r="Q31">
-        <v>64.60490192500001</v>
+        <v>63.88998475</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09392701207767279</v>
+        <v>0.09455122753912121</v>
       </c>
       <c r="T31">
-        <v>0.9380850441543159</v>
+        <v>0.950252165349573</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.317003388877011</v>
+        <v>2.239769942581111</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08608335927738484</v>
+        <v>0.08624428997962201</v>
       </c>
       <c r="C32">
-        <v>700.0020518059296</v>
+        <v>687.4797098545647</v>
       </c>
       <c r="D32">
-        <v>865.2720518059296</v>
+        <v>863.5287098545647</v>
       </c>
       <c r="E32">
-        <v>-60.02999999999997</v>
+        <v>-49.25099999999998</v>
       </c>
       <c r="F32">
-        <v>323.37</v>
+        <v>334.149</v>
       </c>
       <c r="G32">
         <v>158.1</v>
@@ -3911,28 +3911,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M32">
-        <v>24.511446</v>
+        <v>25.3284942</v>
       </c>
       <c r="N32">
-        <v>30.388554</v>
+        <v>29.5715058</v>
       </c>
       <c r="O32">
-        <v>3.79856925</v>
+        <v>3.696438225000001</v>
       </c>
       <c r="P32">
-        <v>26.58998475</v>
+        <v>25.875067575</v>
       </c>
       <c r="Q32">
-        <v>63.88998475</v>
+        <v>63.175067575</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09455122753912121</v>
+        <v>0.09519353620235074</v>
       </c>
       <c r="T32">
-        <v>0.950252165349573</v>
+        <v>0.9627719567244027</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.239769942581111</v>
+        <v>2.167519299272043</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08624428997962201</v>
+        <v>0.08640522068185919</v>
       </c>
       <c r="C33">
-        <v>687.4797098545647</v>
+        <v>674.9643787156522</v>
       </c>
       <c r="D33">
-        <v>863.5287098545647</v>
+        <v>861.7923787156521</v>
       </c>
       <c r="E33">
-        <v>-49.25099999999998</v>
+        <v>-38.47199999999992</v>
       </c>
       <c r="F33">
-        <v>334.149</v>
+        <v>344.9280000000001</v>
       </c>
       <c r="G33">
         <v>158.1</v>
@@ -3993,28 +3993,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M33">
-        <v>25.3284942</v>
+        <v>26.14554240000001</v>
       </c>
       <c r="N33">
-        <v>29.5715058</v>
+        <v>28.7544576</v>
       </c>
       <c r="O33">
-        <v>3.696438225000001</v>
+        <v>3.5943072</v>
       </c>
       <c r="P33">
-        <v>25.875067575</v>
+        <v>25.1601504</v>
       </c>
       <c r="Q33">
-        <v>63.175067575</v>
+        <v>62.4601504</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09519353620235074</v>
+        <v>0.09585473629685173</v>
       </c>
       <c r="T33">
-        <v>0.9627719567244027</v>
+        <v>0.9756599772573156</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.167519299272043</v>
+        <v>2.099784321169791</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08640522068185919</v>
+        <v>0.08656615138409635</v>
       </c>
       <c r="C34">
-        <v>674.9643787156522</v>
+        <v>662.4560161833078</v>
       </c>
       <c r="D34">
-        <v>861.7923787156521</v>
+        <v>860.0630161833078</v>
       </c>
       <c r="E34">
-        <v>-38.47199999999992</v>
+        <v>-27.69299999999993</v>
       </c>
       <c r="F34">
-        <v>344.9280000000001</v>
+        <v>355.7070000000001</v>
       </c>
       <c r="G34">
         <v>158.1</v>
@@ -4075,28 +4075,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M34">
-        <v>26.14554240000001</v>
+        <v>26.96259060000001</v>
       </c>
       <c r="N34">
-        <v>28.7544576</v>
+        <v>27.9374094</v>
       </c>
       <c r="O34">
-        <v>3.5943072</v>
+        <v>3.492176175</v>
       </c>
       <c r="P34">
-        <v>25.1601504</v>
+        <v>24.445233225</v>
       </c>
       <c r="Q34">
-        <v>62.4601504</v>
+        <v>61.74523322499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09585473629685173</v>
+        <v>0.09653567370760648</v>
       </c>
       <c r="T34">
-        <v>0.9756599772573156</v>
+        <v>0.9889327148210617</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.099784321169791</v>
+        <v>2.036154493255555</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08656615138409635</v>
+        <v>0.0909515820863335</v>
       </c>
       <c r="C35">
-        <v>662.4560161833078</v>
+        <v>607.0842060789216</v>
       </c>
       <c r="D35">
-        <v>860.0630161833078</v>
+        <v>815.4702060789217</v>
       </c>
       <c r="E35">
-        <v>-27.69299999999993</v>
+        <v>-16.91399999999993</v>
       </c>
       <c r="F35">
-        <v>355.7070000000001</v>
+        <v>366.486</v>
       </c>
       <c r="G35">
         <v>158.1</v>
@@ -4157,45 +4157,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M35">
-        <v>26.96259060000001</v>
+        <v>32.98374</v>
       </c>
       <c r="N35">
-        <v>27.9374094</v>
+        <v>21.91626</v>
       </c>
       <c r="O35">
-        <v>3.492176175</v>
+        <v>2.7395325</v>
       </c>
       <c r="P35">
-        <v>24.445233225</v>
+        <v>19.1767275</v>
       </c>
       <c r="Q35">
-        <v>61.74523322499999</v>
+        <v>56.4767275</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09653567370760648</v>
+        <v>0.09723724558535379</v>
       </c>
       <c r="T35">
-        <v>0.9889327148210617</v>
+        <v>1.002607656553406</v>
       </c>
       <c r="U35">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.036154493255555</v>
+        <v>1.664456486741649</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0909515820863335</v>
+        <v>0.09123676278857067</v>
       </c>
       <c r="C36">
-        <v>607.0842060789216</v>
+        <v>593.5649653182636</v>
       </c>
       <c r="D36">
-        <v>815.4702060789217</v>
+        <v>812.7299653182636</v>
       </c>
       <c r="E36">
-        <v>-16.91399999999993</v>
+        <v>-6.134999999999934</v>
       </c>
       <c r="F36">
-        <v>366.486</v>
+        <v>377.265</v>
       </c>
       <c r="G36">
         <v>158.1</v>
@@ -4239,28 +4239,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M36">
-        <v>32.98374</v>
+        <v>33.95385</v>
       </c>
       <c r="N36">
-        <v>21.91626</v>
+        <v>20.94615</v>
       </c>
       <c r="O36">
-        <v>2.7395325</v>
+        <v>2.61826875</v>
       </c>
       <c r="P36">
-        <v>19.1767275</v>
+        <v>18.32788125</v>
       </c>
       <c r="Q36">
-        <v>56.4767275</v>
+        <v>55.62788125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09723724558535379</v>
+        <v>0.09796040429010872</v>
       </c>
       <c r="T36">
-        <v>1.002607656553406</v>
+        <v>1.016703365723669</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.664456486741649</v>
+        <v>1.616900587120459</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09123676278857067</v>
+        <v>0.09152194349080782</v>
       </c>
       <c r="C37">
-        <v>593.5649653182636</v>
+        <v>580.0640790517467</v>
       </c>
       <c r="D37">
-        <v>812.7299653182636</v>
+        <v>810.0080790517468</v>
       </c>
       <c r="E37">
-        <v>-6.134999999999934</v>
+        <v>4.644000000000119</v>
       </c>
       <c r="F37">
-        <v>377.265</v>
+        <v>388.0440000000001</v>
       </c>
       <c r="G37">
         <v>158.1</v>
@@ -4321,28 +4321,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M37">
-        <v>33.95385</v>
+        <v>34.92396000000001</v>
       </c>
       <c r="N37">
-        <v>20.94615</v>
+        <v>19.97604</v>
       </c>
       <c r="O37">
-        <v>2.61826875</v>
+        <v>2.497005</v>
       </c>
       <c r="P37">
-        <v>18.32788125</v>
+        <v>17.479035</v>
       </c>
       <c r="Q37">
-        <v>55.62788125</v>
+        <v>54.77903499999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09796040429010872</v>
+        <v>0.09870616170438723</v>
       </c>
       <c r="T37">
-        <v>1.016703365723669</v>
+        <v>1.031239565805502</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.616900587120459</v>
+        <v>1.571986681922668</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09152194349080783</v>
+        <v>0.09180712419304499</v>
       </c>
       <c r="C38">
-        <v>580.0640790517466</v>
+        <v>566.58136348368</v>
       </c>
       <c r="D38">
-        <v>810.0080790517467</v>
+        <v>807.3043634836799</v>
       </c>
       <c r="E38">
-        <v>4.644000000000062</v>
+        <v>15.42300000000006</v>
       </c>
       <c r="F38">
-        <v>388.044</v>
+        <v>398.823</v>
       </c>
       <c r="G38">
         <v>158.1</v>
@@ -4403,28 +4403,28 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M38">
-        <v>34.92396</v>
+        <v>35.89407</v>
       </c>
       <c r="N38">
-        <v>19.97604</v>
+        <v>19.00593000000001</v>
       </c>
       <c r="O38">
-        <v>2.497005000000001</v>
+        <v>2.375741250000001</v>
       </c>
       <c r="P38">
-        <v>17.479035</v>
+        <v>16.63018875000001</v>
       </c>
       <c r="Q38">
-        <v>54.779035</v>
+        <v>53.93018875</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09870616170438723</v>
+        <v>0.09947559395721427</v>
       </c>
       <c r="T38">
-        <v>1.031239565805502</v>
+        <v>1.046237232556601</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.571986681922669</v>
+        <v>1.529500555384218</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09180712419304499</v>
+        <v>0.1117312308371309</v>
       </c>
       <c r="C39">
-        <v>566.58136348368</v>
+        <v>403.1393563863593</v>
       </c>
       <c r="D39">
-        <v>807.3043634836799</v>
+        <v>654.6413563863593</v>
       </c>
       <c r="E39">
-        <v>15.42300000000006</v>
+        <v>26.20200000000006</v>
       </c>
       <c r="F39">
-        <v>398.823</v>
+        <v>409.602</v>
       </c>
       <c r="G39">
         <v>158.1</v>
@@ -4485,45 +4485,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M39">
-        <v>35.89407</v>
+        <v>60.12957360000001</v>
       </c>
       <c r="N39">
-        <v>19.00593000000001</v>
+        <v>-5.229573600000002</v>
       </c>
       <c r="O39">
-        <v>2.375741250000001</v>
+        <v>-0.6536967000000002</v>
       </c>
       <c r="P39">
-        <v>16.63018875000001</v>
+        <v>-4.575876900000002</v>
       </c>
       <c r="Q39">
-        <v>53.93018875</v>
+        <v>32.72412309999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09947559395721427</v>
+        <v>0.1005060917724478</v>
       </c>
       <c r="T39">
-        <v>1.046237232556601</v>
+        <v>1.066323553040078</v>
       </c>
       <c r="U39">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.125</v>
+        <v>0.1141285325861682</v>
       </c>
       <c r="W39">
-        <v>0.07875</v>
+        <v>0.1300459314163505</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.529500555384218</v>
+        <v>0.9130282606893457</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1117312308371309</v>
+        <v>0.1127412308371309</v>
       </c>
       <c r="C40">
-        <v>403.1393563863593</v>
+        <v>386.1445263290041</v>
       </c>
       <c r="D40">
-        <v>654.6413563863593</v>
+        <v>648.4255263290041</v>
       </c>
       <c r="E40">
-        <v>26.20200000000006</v>
+        <v>36.98100000000005</v>
       </c>
       <c r="F40">
-        <v>409.602</v>
+        <v>420.381</v>
       </c>
       <c r="G40">
         <v>158.1</v>
@@ -4567,37 +4567,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M40">
-        <v>60.12957360000001</v>
+        <v>61.71193080000001</v>
       </c>
       <c r="N40">
-        <v>-5.229573600000002</v>
+        <v>-6.811930800000006</v>
       </c>
       <c r="O40">
-        <v>-0.6536967000000002</v>
+        <v>-0.8514913500000008</v>
       </c>
       <c r="P40">
-        <v>-4.575876900000002</v>
+        <v>-5.960439450000005</v>
       </c>
       <c r="Q40">
-        <v>32.72412309999999</v>
+        <v>31.33956054999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1005060917724478</v>
+        <v>0.1014029129490454</v>
       </c>
       <c r="T40">
-        <v>1.066323553040078</v>
+        <v>1.083804267024341</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1141285325861682</v>
+        <v>0.1112021599557536</v>
       </c>
       <c r="W40">
-        <v>0.1300459314163505</v>
+        <v>0.1304755229184954</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9130282606893457</v>
+        <v>0.8896172796460291</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1127412308371309</v>
+        <v>0.1137512308371309</v>
       </c>
       <c r="C41">
-        <v>386.1445263290041</v>
+        <v>369.2666248428878</v>
       </c>
       <c r="D41">
-        <v>648.4255263290041</v>
+        <v>642.3266248428879</v>
       </c>
       <c r="E41">
-        <v>36.98100000000005</v>
+        <v>47.7600000000001</v>
       </c>
       <c r="F41">
-        <v>420.381</v>
+        <v>431.1600000000001</v>
       </c>
       <c r="G41">
         <v>158.1</v>
@@ -4649,37 +4649,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M41">
-        <v>61.71193080000001</v>
+        <v>63.29428800000002</v>
       </c>
       <c r="N41">
-        <v>-6.811930800000006</v>
+        <v>-8.39428800000001</v>
       </c>
       <c r="O41">
-        <v>-0.8514913500000008</v>
+        <v>-1.049286000000001</v>
       </c>
       <c r="P41">
-        <v>-5.960439450000005</v>
+        <v>-7.345002000000009</v>
       </c>
       <c r="Q41">
-        <v>31.33956054999999</v>
+        <v>29.95499799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1014029129490454</v>
+        <v>0.1023296281648628</v>
       </c>
       <c r="T41">
-        <v>1.083804267024341</v>
+        <v>1.101867671474747</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1112021599557536</v>
+        <v>0.1084221059568598</v>
       </c>
       <c r="W41">
-        <v>0.1304755229184954</v>
+        <v>0.130883634845533</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8896172796460291</v>
+        <v>0.8673768476548783</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1137512308371309</v>
+        <v>0.1147612308371309</v>
       </c>
       <c r="C42">
-        <v>369.2666248428878</v>
+        <v>352.5023832837558</v>
       </c>
       <c r="D42">
-        <v>642.3266248428879</v>
+        <v>636.3413832837558</v>
       </c>
       <c r="E42">
-        <v>47.7600000000001</v>
+        <v>58.5390000000001</v>
       </c>
       <c r="F42">
-        <v>431.1600000000001</v>
+        <v>441.9390000000001</v>
       </c>
       <c r="G42">
         <v>158.1</v>
@@ -4731,37 +4731,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M42">
-        <v>63.29428800000002</v>
+        <v>64.87664520000001</v>
       </c>
       <c r="N42">
-        <v>-8.39428800000001</v>
+        <v>-9.976645200000007</v>
       </c>
       <c r="O42">
-        <v>-1.049286000000001</v>
+        <v>-1.247080650000001</v>
       </c>
       <c r="P42">
-        <v>-7.345002000000009</v>
+        <v>-8.729564550000006</v>
       </c>
       <c r="Q42">
-        <v>29.95499799999999</v>
+        <v>28.57043544999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1023296281648628</v>
+        <v>0.1032877574557926</v>
       </c>
       <c r="T42">
-        <v>1.101867671474747</v>
+        <v>1.120543394720082</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1084221059568598</v>
+        <v>0.1057776643481559</v>
       </c>
       <c r="W42">
-        <v>0.130883634845533</v>
+        <v>0.1312718388736907</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8673768476548783</v>
+        <v>0.8462213147852472</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1147612308371309</v>
+        <v>0.1157712308371309</v>
       </c>
       <c r="C43">
-        <v>352.5023832837558</v>
+        <v>335.8486537123802</v>
       </c>
       <c r="D43">
-        <v>636.3413832837558</v>
+        <v>630.4666537123802</v>
       </c>
       <c r="E43">
-        <v>58.5390000000001</v>
+        <v>69.3180000000001</v>
       </c>
       <c r="F43">
-        <v>441.9390000000001</v>
+        <v>452.7180000000001</v>
       </c>
       <c r="G43">
         <v>158.1</v>
@@ -4813,37 +4813,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M43">
-        <v>64.87664520000001</v>
+        <v>66.45900240000002</v>
       </c>
       <c r="N43">
-        <v>-9.976645200000007</v>
+        <v>-11.55900240000001</v>
       </c>
       <c r="O43">
-        <v>-1.247080650000001</v>
+        <v>-1.444875300000001</v>
       </c>
       <c r="P43">
-        <v>-8.729564550000006</v>
+        <v>-10.11412710000001</v>
       </c>
       <c r="Q43">
-        <v>28.57043544999999</v>
+        <v>27.18587289999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1032877574557926</v>
+        <v>0.1042789256877891</v>
       </c>
       <c r="T43">
-        <v>1.120543394720082</v>
+        <v>1.139863108422152</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1057776643481559</v>
+        <v>0.1032591485303427</v>
       </c>
       <c r="W43">
-        <v>0.1312718388736907</v>
+        <v>0.1316415569957457</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8462213147852472</v>
+        <v>0.8260731882427412</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1157712308371309</v>
+        <v>0.1167812308371309</v>
       </c>
       <c r="C44">
-        <v>335.8486537123801</v>
+        <v>319.3024033737613</v>
       </c>
       <c r="D44">
-        <v>630.4666537123801</v>
+        <v>624.6994033737612</v>
       </c>
       <c r="E44">
-        <v>69.31800000000004</v>
+        <v>80.09700000000004</v>
       </c>
       <c r="F44">
-        <v>452.718</v>
+        <v>463.497</v>
       </c>
       <c r="G44">
         <v>158.1</v>
@@ -4895,37 +4895,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M44">
-        <v>66.4590024</v>
+        <v>68.04135960000001</v>
       </c>
       <c r="N44">
-        <v>-11.5590024</v>
+        <v>-13.1413596</v>
       </c>
       <c r="O44">
-        <v>-1.4448753</v>
+        <v>-1.64266995</v>
       </c>
       <c r="P44">
-        <v>-10.1141271</v>
+        <v>-11.49868965</v>
       </c>
       <c r="Q44">
-        <v>27.1858729</v>
+        <v>25.80131034999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1042789256877891</v>
+        <v>0.1053048717524871</v>
       </c>
       <c r="T44">
-        <v>1.139863108422152</v>
+        <v>1.159860706815523</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1032591485303427</v>
+        <v>0.1008577729831254</v>
       </c>
       <c r="W44">
-        <v>0.1316415569957457</v>
+        <v>0.1319940789260772</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8260731882427415</v>
+        <v>0.8068621838650032</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1167812308371309</v>
+        <v>0.1419647453332117</v>
       </c>
       <c r="C45">
-        <v>319.3024033737613</v>
+        <v>192.5005887922231</v>
       </c>
       <c r="D45">
-        <v>624.6994033737612</v>
+        <v>508.6765887922231</v>
       </c>
       <c r="E45">
-        <v>80.09700000000004</v>
+        <v>90.87600000000009</v>
       </c>
       <c r="F45">
-        <v>463.497</v>
+        <v>474.2760000000001</v>
       </c>
       <c r="G45">
         <v>158.1</v>
@@ -4977,45 +4977,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M45">
-        <v>68.04135960000001</v>
+        <v>95.23462080000002</v>
       </c>
       <c r="N45">
-        <v>-13.1413596</v>
+        <v>-40.33462080000001</v>
       </c>
       <c r="O45">
-        <v>-1.64266995</v>
+        <v>-5.041827600000001</v>
       </c>
       <c r="P45">
-        <v>-11.49868965</v>
+        <v>-35.29279320000001</v>
       </c>
       <c r="Q45">
-        <v>25.80131034999999</v>
+        <v>2.007206799999992</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1053048717524871</v>
+        <v>0.1071058774910687</v>
       </c>
       <c r="T45">
-        <v>1.159860706815523</v>
+        <v>1.194965660870696</v>
       </c>
       <c r="U45">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1008577729831254</v>
+        <v>0.07205887882319367</v>
       </c>
       <c r="W45">
-        <v>0.1319940789260772</v>
+        <v>0.1863305771323027</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8068621838650032</v>
+        <v>0.5764710305855494</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1419647453332117</v>
+        <v>0.1435147453332117</v>
       </c>
       <c r="C46">
-        <v>192.5005887922231</v>
+        <v>175.9725780986345</v>
       </c>
       <c r="D46">
-        <v>508.6765887922231</v>
+        <v>502.9275780986346</v>
       </c>
       <c r="E46">
-        <v>90.87600000000009</v>
+        <v>101.6550000000001</v>
       </c>
       <c r="F46">
-        <v>474.2760000000001</v>
+        <v>485.0550000000001</v>
       </c>
       <c r="G46">
         <v>158.1</v>
@@ -5059,37 +5059,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M46">
-        <v>95.23462080000002</v>
+        <v>97.39904400000002</v>
       </c>
       <c r="N46">
-        <v>-40.33462080000001</v>
+        <v>-42.49904400000001</v>
       </c>
       <c r="O46">
-        <v>-5.041827600000001</v>
+        <v>-5.312380500000002</v>
       </c>
       <c r="P46">
-        <v>-35.29279320000001</v>
+        <v>-37.18666350000001</v>
       </c>
       <c r="Q46">
-        <v>2.007206799999992</v>
+        <v>0.1133364999999884</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1071058774910687</v>
+        <v>0.1082205298090881</v>
       </c>
       <c r="T46">
-        <v>1.194965660870696</v>
+        <v>1.216692309250163</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.07205887882319367</v>
+        <v>0.07045757040490047</v>
       </c>
       <c r="W46">
-        <v>0.1863305771323027</v>
+        <v>0.186652119862696</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5764710305855494</v>
+        <v>0.5636605632392038</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1435147453332117</v>
+        <v>0.1450647453332117</v>
       </c>
       <c r="C47">
-        <v>175.9725780986345</v>
+        <v>159.5730646026506</v>
       </c>
       <c r="D47">
-        <v>502.9275780986346</v>
+        <v>497.3070646026507</v>
       </c>
       <c r="E47">
-        <v>101.6550000000001</v>
+        <v>112.4340000000001</v>
       </c>
       <c r="F47">
-        <v>485.0550000000001</v>
+        <v>495.8340000000001</v>
       </c>
       <c r="G47">
         <v>158.1</v>
@@ -5141,37 +5141,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M47">
-        <v>97.39904400000002</v>
+        <v>99.56346720000002</v>
       </c>
       <c r="N47">
-        <v>-42.49904400000001</v>
+        <v>-44.66346720000001</v>
       </c>
       <c r="O47">
-        <v>-5.312380500000002</v>
+        <v>-5.582933400000002</v>
       </c>
       <c r="P47">
-        <v>-37.18666350000001</v>
+        <v>-39.08053380000001</v>
       </c>
       <c r="Q47">
-        <v>0.1133364999999884</v>
+        <v>-1.780533800000015</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1082205298090881</v>
+        <v>0.1093764655462935</v>
       </c>
       <c r="T47">
-        <v>1.216692309250163</v>
+        <v>1.239223648310352</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.07045757040490047</v>
+        <v>0.06892588409175046</v>
       </c>
       <c r="W47">
-        <v>0.186652119862696</v>
+        <v>0.1869596824743765</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5636605632392038</v>
+        <v>0.5514070727340037</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1450647453332117</v>
+        <v>0.1466147453332117</v>
       </c>
       <c r="C48">
-        <v>159.5730646026506</v>
+        <v>143.297787820876</v>
       </c>
       <c r="D48">
-        <v>497.3070646026507</v>
+        <v>491.8107878208761</v>
       </c>
       <c r="E48">
-        <v>112.4340000000001</v>
+        <v>123.2130000000001</v>
       </c>
       <c r="F48">
-        <v>495.8340000000001</v>
+        <v>506.6130000000001</v>
       </c>
       <c r="G48">
         <v>158.1</v>
@@ -5223,37 +5223,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M48">
-        <v>99.56346720000002</v>
+        <v>101.7278904</v>
       </c>
       <c r="N48">
-        <v>-44.66346720000001</v>
+        <v>-46.82789040000002</v>
       </c>
       <c r="O48">
-        <v>-5.582933400000002</v>
+        <v>-5.853486300000002</v>
       </c>
       <c r="P48">
-        <v>-39.08053380000001</v>
+        <v>-40.97440410000002</v>
       </c>
       <c r="Q48">
-        <v>-1.780533800000015</v>
+        <v>-3.674404100000018</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1093764655462935</v>
+        <v>0.1105760214999971</v>
       </c>
       <c r="T48">
-        <v>1.239223648310352</v>
+        <v>1.262605226580358</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.06892588409175046</v>
+        <v>0.06745937591958556</v>
       </c>
       <c r="W48">
-        <v>0.1869596824743765</v>
+        <v>0.1872541573153472</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5514070727340037</v>
+        <v>0.5396750073566845</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1466147453332117</v>
+        <v>0.1481647453332117</v>
       </c>
       <c r="C49">
-        <v>143.297787820876</v>
+        <v>127.1426735598145</v>
       </c>
       <c r="D49">
-        <v>491.8107878208761</v>
+        <v>486.4346735598146</v>
       </c>
       <c r="E49">
-        <v>123.2130000000001</v>
+        <v>133.9920000000001</v>
       </c>
       <c r="F49">
-        <v>506.6130000000001</v>
+        <v>517.3920000000001</v>
       </c>
       <c r="G49">
         <v>158.1</v>
@@ -5305,37 +5305,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M49">
-        <v>101.7278904</v>
+        <v>103.8923136</v>
       </c>
       <c r="N49">
-        <v>-46.82789040000002</v>
+        <v>-48.9923136</v>
       </c>
       <c r="O49">
-        <v>-5.853486300000002</v>
+        <v>-6.1240392</v>
       </c>
       <c r="P49">
-        <v>-40.97440410000002</v>
+        <v>-42.8682744</v>
       </c>
       <c r="Q49">
-        <v>-3.674404100000018</v>
+        <v>-5.568274400000007</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1105760214999971</v>
+        <v>0.1118217142211509</v>
       </c>
       <c r="T49">
-        <v>1.262605226580358</v>
+        <v>1.286886096322288</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.06745937591958556</v>
+        <v>0.06605397225459421</v>
       </c>
       <c r="W49">
-        <v>0.1872541573153472</v>
+        <v>0.1875363623712775</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5396750073566845</v>
+        <v>0.5284317780367536</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1481647453332117</v>
+        <v>0.1497147453332117</v>
       </c>
       <c r="C50">
-        <v>127.1426735598145</v>
+        <v>111.1038238440456</v>
       </c>
       <c r="D50">
-        <v>486.4346735598146</v>
+        <v>481.1748238440456</v>
       </c>
       <c r="E50">
-        <v>133.9920000000001</v>
+        <v>144.7710000000001</v>
       </c>
       <c r="F50">
-        <v>517.3920000000001</v>
+        <v>528.171</v>
       </c>
       <c r="G50">
         <v>158.1</v>
@@ -5387,37 +5387,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M50">
-        <v>103.8923136</v>
+        <v>106.0567368</v>
       </c>
       <c r="N50">
-        <v>-48.9923136</v>
+        <v>-51.1567368</v>
       </c>
       <c r="O50">
-        <v>-6.1240392</v>
+        <v>-6.394592100000001</v>
       </c>
       <c r="P50">
-        <v>-42.8682744</v>
+        <v>-44.76214470000001</v>
       </c>
       <c r="Q50">
-        <v>-5.568274400000007</v>
+        <v>-7.46214470000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1118217142211509</v>
+        <v>0.1131162576372519</v>
       </c>
       <c r="T50">
-        <v>1.286886096322288</v>
+        <v>1.31211915703449</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.06605397225459421</v>
+        <v>0.06470593200450045</v>
       </c>
       <c r="W50">
-        <v>0.1875363623712775</v>
+        <v>0.1878070488534963</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5284317780367536</v>
+        <v>0.5176474560360036</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1497147453332117</v>
+        <v>0.1512647453332117</v>
       </c>
       <c r="C51">
-        <v>111.1038238440456</v>
+        <v>95.17750749085371</v>
       </c>
       <c r="D51">
-        <v>481.1748238440456</v>
+        <v>476.0275074908538</v>
       </c>
       <c r="E51">
-        <v>144.7710000000001</v>
+        <v>155.5500000000001</v>
       </c>
       <c r="F51">
-        <v>528.171</v>
+        <v>538.95</v>
       </c>
       <c r="G51">
         <v>158.1</v>
@@ -5469,37 +5469,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M51">
-        <v>106.0567368</v>
+        <v>108.22116</v>
       </c>
       <c r="N51">
-        <v>-51.1567368</v>
+        <v>-53.32116000000001</v>
       </c>
       <c r="O51">
-        <v>-6.394592100000001</v>
+        <v>-6.665145000000001</v>
       </c>
       <c r="P51">
-        <v>-44.76214470000001</v>
+        <v>-46.656015</v>
       </c>
       <c r="Q51">
-        <v>-7.46214470000001</v>
+        <v>-9.356015000000006</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1131162576372519</v>
+        <v>0.1144625827899969</v>
       </c>
       <c r="T51">
-        <v>1.31211915703449</v>
+        <v>1.33836154017518</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.06470593200450045</v>
+        <v>0.06341181336441043</v>
       </c>
       <c r="W51">
-        <v>0.1878070488534963</v>
+        <v>0.1880669078764264</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5176474560360036</v>
+        <v>0.5072945069152834</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1512647453332117</v>
+        <v>0.1708316034270815</v>
       </c>
       <c r="C52">
-        <v>95.17750749085371</v>
+        <v>27.76314850513245</v>
       </c>
       <c r="D52">
-        <v>476.0275074908538</v>
+        <v>419.3921485051325</v>
       </c>
       <c r="E52">
-        <v>155.5500000000001</v>
+        <v>166.3290000000001</v>
       </c>
       <c r="F52">
-        <v>538.95</v>
+        <v>549.729</v>
       </c>
       <c r="G52">
         <v>158.1</v>
@@ -5551,45 +5551,45 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M52">
-        <v>108.22116</v>
+        <v>129.6260982</v>
       </c>
       <c r="N52">
-        <v>-53.32116000000001</v>
+        <v>-74.7260982</v>
       </c>
       <c r="O52">
-        <v>-6.665145000000001</v>
+        <v>-9.340762274999999</v>
       </c>
       <c r="P52">
-        <v>-46.656015</v>
+        <v>-65.38533592499999</v>
       </c>
       <c r="Q52">
-        <v>-9.356015000000006</v>
+        <v>-28.085335925</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1144625827899969</v>
+        <v>0.1162043867119761</v>
       </c>
       <c r="T52">
-        <v>1.33836154017518</v>
+        <v>1.372312540632489</v>
       </c>
       <c r="U52">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06341181336441043</v>
+        <v>0.052940727949798</v>
       </c>
       <c r="W52">
-        <v>0.1880669078764264</v>
+        <v>0.2233165763494376</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.5072945069152834</v>
+        <v>0.423525823598384</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1708316034270815</v>
+        <v>0.1727316034270815</v>
       </c>
       <c r="C53">
-        <v>27.76314850513245</v>
+        <v>12.1943213344706</v>
       </c>
       <c r="D53">
-        <v>419.3921485051325</v>
+        <v>414.6023213344706</v>
       </c>
       <c r="E53">
-        <v>166.3290000000001</v>
+        <v>177.1080000000001</v>
       </c>
       <c r="F53">
-        <v>549.729</v>
+        <v>560.508</v>
       </c>
       <c r="G53">
         <v>158.1</v>
@@ -5633,37 +5633,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M53">
-        <v>129.6260982</v>
+        <v>132.1677864</v>
       </c>
       <c r="N53">
-        <v>-74.7260982</v>
+        <v>-77.26778640000001</v>
       </c>
       <c r="O53">
-        <v>-9.340762274999999</v>
+        <v>-9.658473300000001</v>
       </c>
       <c r="P53">
-        <v>-65.38533592499999</v>
+        <v>-67.60931310000001</v>
       </c>
       <c r="Q53">
-        <v>-28.085335925</v>
+        <v>-30.30931310000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1162043867119761</v>
+        <v>0.1176711447684756</v>
       </c>
       <c r="T53">
-        <v>1.372312540632489</v>
+        <v>1.400902385228999</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.052940727949798</v>
+        <v>0.0519226370276865</v>
       </c>
       <c r="W53">
-        <v>0.2233165763494376</v>
+        <v>0.2235566421888715</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.423525823598384</v>
+        <v>0.415381096221492</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1727316034270815</v>
+        <v>0.1746316034270815</v>
       </c>
       <c r="C54">
-        <v>12.1943213344706</v>
+        <v>-3.266333185581743</v>
       </c>
       <c r="D54">
-        <v>414.6023213344706</v>
+        <v>409.9206668144183</v>
       </c>
       <c r="E54">
-        <v>177.1080000000001</v>
+        <v>187.8870000000001</v>
       </c>
       <c r="F54">
-        <v>560.508</v>
+        <v>571.287</v>
       </c>
       <c r="G54">
         <v>158.1</v>
@@ -5715,37 +5715,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M54">
-        <v>132.1677864</v>
+        <v>134.7094746</v>
       </c>
       <c r="N54">
-        <v>-77.26778640000001</v>
+        <v>-79.80947460000002</v>
       </c>
       <c r="O54">
-        <v>-9.658473300000001</v>
+        <v>-9.976184325000002</v>
       </c>
       <c r="P54">
-        <v>-67.60931310000001</v>
+        <v>-69.83329027500001</v>
       </c>
       <c r="Q54">
-        <v>-30.30931310000001</v>
+        <v>-32.53329027500001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1176711447684756</v>
+        <v>0.1192003180614219</v>
       </c>
       <c r="T54">
-        <v>1.400902385228999</v>
+        <v>1.430708818957275</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0519226370276865</v>
+        <v>0.05094296463093769</v>
       </c>
       <c r="W54">
-        <v>0.2235566421888715</v>
+        <v>0.2237876489400249</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.415381096221492</v>
+        <v>0.4075437170475016</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1746316034270815</v>
+        <v>0.1765316034270815</v>
       </c>
       <c r="C55">
-        <v>-3.266333185581743</v>
+        <v>-18.62243856802195</v>
       </c>
       <c r="D55">
-        <v>409.9206668144183</v>
+        <v>405.3435614319781</v>
       </c>
       <c r="E55">
-        <v>187.8870000000001</v>
+        <v>198.6660000000001</v>
       </c>
       <c r="F55">
-        <v>571.287</v>
+        <v>582.066</v>
       </c>
       <c r="G55">
         <v>158.1</v>
@@ -5797,37 +5797,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M55">
-        <v>134.7094746</v>
+        <v>137.2511628</v>
       </c>
       <c r="N55">
-        <v>-79.80947460000002</v>
+        <v>-82.3511628</v>
       </c>
       <c r="O55">
-        <v>-9.976184325000002</v>
+        <v>-10.29389535</v>
       </c>
       <c r="P55">
-        <v>-69.83329027500001</v>
+        <v>-72.05726745</v>
       </c>
       <c r="Q55">
-        <v>-32.53329027500001</v>
+        <v>-34.75726745</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1192003180614219</v>
+        <v>0.1207959771497137</v>
       </c>
       <c r="T55">
-        <v>1.430708818957275</v>
+        <v>1.461811184586781</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05094296463093769</v>
+        <v>0.04999957639703145</v>
       </c>
       <c r="W55">
-        <v>0.2237876489400249</v>
+        <v>0.22401009988558</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4075437170475016</v>
+        <v>0.3999966111762516</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1765316034270815</v>
+        <v>0.1784316034270815</v>
       </c>
       <c r="C56">
-        <v>-18.62243856802195</v>
+        <v>-33.87745827479762</v>
       </c>
       <c r="D56">
-        <v>405.3435614319781</v>
+        <v>400.8675417252025</v>
       </c>
       <c r="E56">
-        <v>198.6660000000001</v>
+        <v>209.4450000000002</v>
       </c>
       <c r="F56">
-        <v>582.066</v>
+        <v>592.8450000000001</v>
       </c>
       <c r="G56">
         <v>158.1</v>
@@ -5879,37 +5879,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M56">
-        <v>137.2511628</v>
+        <v>139.792851</v>
       </c>
       <c r="N56">
-        <v>-82.3511628</v>
+        <v>-84.89285100000004</v>
       </c>
       <c r="O56">
-        <v>-10.29389535</v>
+        <v>-10.611606375</v>
       </c>
       <c r="P56">
-        <v>-72.05726745</v>
+        <v>-74.28124462500003</v>
       </c>
       <c r="Q56">
-        <v>-34.75726745</v>
+        <v>-36.98124462500003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1207959771497137</v>
+        <v>0.1224625544197073</v>
       </c>
       <c r="T56">
-        <v>1.461811184586781</v>
+        <v>1.494295877577599</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04999957639703145</v>
+        <v>0.04909049318981268</v>
       </c>
       <c r="W56">
-        <v>0.22401009988558</v>
+        <v>0.2242244617058422</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3999966111762516</v>
+        <v>0.3927239455185014</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1784316034270815</v>
+        <v>0.1803316034270815</v>
       </c>
       <c r="C57">
-        <v>-33.87745827479762</v>
+        <v>-49.03470445713708</v>
       </c>
       <c r="D57">
-        <v>400.8675417252025</v>
+        <v>396.489295542863</v>
       </c>
       <c r="E57">
-        <v>209.4450000000002</v>
+        <v>220.2240000000002</v>
       </c>
       <c r="F57">
-        <v>592.8450000000001</v>
+        <v>603.6240000000001</v>
       </c>
       <c r="G57">
         <v>158.1</v>
@@ -5961,37 +5961,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M57">
-        <v>139.792851</v>
+        <v>142.3345392000001</v>
       </c>
       <c r="N57">
-        <v>-84.89285100000004</v>
+        <v>-87.43453920000005</v>
       </c>
       <c r="O57">
-        <v>-10.611606375</v>
+        <v>-10.92931740000001</v>
       </c>
       <c r="P57">
-        <v>-74.28124462500003</v>
+        <v>-76.50522180000004</v>
       </c>
       <c r="Q57">
-        <v>-36.98124462500003</v>
+        <v>-39.20522180000005</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1224625544197073</v>
+        <v>0.1242048852019734</v>
       </c>
       <c r="T57">
-        <v>1.494295877577599</v>
+        <v>1.528257147522544</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04909049318981268</v>
+        <v>0.0482138772399946</v>
       </c>
       <c r="W57">
-        <v>0.2242244617058422</v>
+        <v>0.2244311677468093</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3927239455185014</v>
+        <v>0.3857110179199568</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1803316034270815</v>
+        <v>0.1822316034270815</v>
       </c>
       <c r="C58">
-        <v>-49.03470445713708</v>
+        <v>-64.09734612929935</v>
       </c>
       <c r="D58">
-        <v>396.489295542863</v>
+        <v>392.2056538707008</v>
       </c>
       <c r="E58">
-        <v>220.2240000000002</v>
+        <v>231.0030000000002</v>
       </c>
       <c r="F58">
-        <v>603.6240000000001</v>
+        <v>614.4030000000001</v>
       </c>
       <c r="G58">
         <v>158.1</v>
@@ -6043,37 +6043,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M58">
-        <v>142.3345392000001</v>
+        <v>144.8762274</v>
       </c>
       <c r="N58">
-        <v>-87.43453920000005</v>
+        <v>-89.97622740000003</v>
       </c>
       <c r="O58">
-        <v>-10.92931740000001</v>
+        <v>-11.247028425</v>
       </c>
       <c r="P58">
-        <v>-76.50522180000004</v>
+        <v>-78.72919897500003</v>
       </c>
       <c r="Q58">
-        <v>-39.20522180000005</v>
+        <v>-41.42919897500003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1242048852019734</v>
+        <v>0.1260282546252751</v>
       </c>
       <c r="T58">
-        <v>1.528257147522544</v>
+        <v>1.563798011418417</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0482138772399946</v>
+        <v>0.04736801974455609</v>
       </c>
       <c r="W58">
-        <v>0.2244311677468093</v>
+        <v>0.2246306209442337</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3857110179199568</v>
+        <v>0.3789441579564488</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1822316034270815</v>
+        <v>0.1841316034270815</v>
       </c>
       <c r="C59">
-        <v>-64.09734612929935</v>
+        <v>-79.06841681813626</v>
       </c>
       <c r="D59">
-        <v>392.2056538707008</v>
+        <v>388.0135831818639</v>
       </c>
       <c r="E59">
-        <v>231.0030000000002</v>
+        <v>241.7820000000002</v>
       </c>
       <c r="F59">
-        <v>614.4030000000001</v>
+        <v>625.1820000000001</v>
       </c>
       <c r="G59">
         <v>158.1</v>
@@ -6125,37 +6125,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M59">
-        <v>144.8762274</v>
+        <v>147.4179156</v>
       </c>
       <c r="N59">
-        <v>-89.97622740000003</v>
+        <v>-92.51791560000004</v>
       </c>
       <c r="O59">
-        <v>-11.247028425</v>
+        <v>-11.56473945</v>
       </c>
       <c r="P59">
-        <v>-78.72919897500003</v>
+        <v>-80.95317615000003</v>
       </c>
       <c r="Q59">
-        <v>-41.42919897500003</v>
+        <v>-43.65317615000004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1260282546252751</v>
+        <v>0.1279384511639721</v>
       </c>
       <c r="T59">
-        <v>1.563798011418417</v>
+        <v>1.60103129740457</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04736801974455609</v>
+        <v>0.0465513297489603</v>
       </c>
       <c r="W59">
-        <v>0.2246306209442337</v>
+        <v>0.2248231964451952</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3789441579564488</v>
+        <v>0.3724106379916824</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1841316034270815</v>
+        <v>0.1860316034270814</v>
       </c>
       <c r="C60">
-        <v>-79.06841681813614</v>
+        <v>-93.95082172727052</v>
       </c>
       <c r="D60">
-        <v>388.0135831818639</v>
+        <v>383.9101782727295</v>
       </c>
       <c r="E60">
-        <v>241.782</v>
+        <v>252.561</v>
       </c>
       <c r="F60">
-        <v>625.182</v>
+        <v>635.961</v>
       </c>
       <c r="G60">
         <v>158.1</v>
@@ -6207,37 +6207,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M60">
-        <v>147.4179156</v>
+        <v>149.9596038</v>
       </c>
       <c r="N60">
-        <v>-92.51791560000001</v>
+        <v>-95.05960379999999</v>
       </c>
       <c r="O60">
-        <v>-11.56473945</v>
+        <v>-11.882450475</v>
       </c>
       <c r="P60">
-        <v>-80.95317615</v>
+        <v>-83.17715332499999</v>
       </c>
       <c r="Q60">
-        <v>-43.65317615000001</v>
+        <v>-45.87715332499999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1279384511639721</v>
+        <v>0.1299418280216299</v>
       </c>
       <c r="T60">
-        <v>1.60103129740457</v>
+        <v>1.640080841243705</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04655132974896031</v>
+        <v>0.04576232415999489</v>
       </c>
       <c r="W60">
-        <v>0.2248231964451952</v>
+        <v>0.2250092439630732</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3724106379916825</v>
+        <v>0.3660985932799591</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1860316034270814</v>
+        <v>0.1879316034270815</v>
       </c>
       <c r="C61">
-        <v>-93.95082172727052</v>
+        <v>-108.7473444514463</v>
       </c>
       <c r="D61">
-        <v>383.9101782727295</v>
+        <v>379.8926555485536</v>
       </c>
       <c r="E61">
-        <v>252.561</v>
+        <v>263.34</v>
       </c>
       <c r="F61">
-        <v>635.961</v>
+        <v>646.74</v>
       </c>
       <c r="G61">
         <v>158.1</v>
@@ -6289,37 +6289,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M61">
-        <v>149.9596038</v>
+        <v>152.501292</v>
       </c>
       <c r="N61">
-        <v>-95.05960379999999</v>
+        <v>-97.601292</v>
       </c>
       <c r="O61">
-        <v>-11.882450475</v>
+        <v>-12.2001615</v>
       </c>
       <c r="P61">
-        <v>-83.17715332499999</v>
+        <v>-85.40113049999999</v>
       </c>
       <c r="Q61">
-        <v>-45.87715332499999</v>
+        <v>-48.1011305</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1299418280216299</v>
+        <v>0.1320453737221707</v>
       </c>
       <c r="T61">
-        <v>1.640080841243705</v>
+        <v>1.681082862274798</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04576232415999489</v>
+        <v>0.0449996187573283</v>
       </c>
       <c r="W61">
-        <v>0.2250092439630732</v>
+        <v>0.225189089897022</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3660985932799591</v>
+        <v>0.3599969500586264</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1879316034270815</v>
+        <v>0.1898316034270815</v>
       </c>
       <c r="C62">
-        <v>-108.7473444514463</v>
+        <v>-123.4606532736616</v>
       </c>
       <c r="D62">
-        <v>379.8926555485536</v>
+        <v>375.9583467263384</v>
       </c>
       <c r="E62">
-        <v>263.34</v>
+        <v>274.119</v>
       </c>
       <c r="F62">
-        <v>646.74</v>
+        <v>657.519</v>
       </c>
       <c r="G62">
         <v>158.1</v>
@@ -6371,37 +6371,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M62">
-        <v>152.501292</v>
+        <v>155.0429802</v>
       </c>
       <c r="N62">
-        <v>-97.601292</v>
+        <v>-100.1429802</v>
       </c>
       <c r="O62">
-        <v>-12.2001615</v>
+        <v>-12.517872525</v>
       </c>
       <c r="P62">
-        <v>-85.40113049999999</v>
+        <v>-87.62510767500001</v>
       </c>
       <c r="Q62">
-        <v>-48.1011305</v>
+        <v>-50.32510767500001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1320453737221707</v>
+        <v>0.1342567935612007</v>
       </c>
       <c r="T62">
-        <v>1.681082862274798</v>
+        <v>1.724187551051075</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0449996187573283</v>
+        <v>0.04426192008917538</v>
       </c>
       <c r="W62">
-        <v>0.225189089897022</v>
+        <v>0.2253630392429725</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3599969500586264</v>
+        <v>0.354095360713403</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1898316034270815</v>
+        <v>0.1917316034270815</v>
       </c>
       <c r="C63">
-        <v>-123.4606532736616</v>
+        <v>-138.0933070750191</v>
       </c>
       <c r="D63">
-        <v>375.9583467263384</v>
+        <v>372.1046929249809</v>
       </c>
       <c r="E63">
-        <v>274.119</v>
+        <v>284.898</v>
       </c>
       <c r="F63">
-        <v>657.519</v>
+        <v>668.298</v>
       </c>
       <c r="G63">
         <v>158.1</v>
@@ -6453,37 +6453,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M63">
-        <v>155.0429802</v>
+        <v>157.5846684</v>
       </c>
       <c r="N63">
-        <v>-100.1429802</v>
+        <v>-102.6846684</v>
       </c>
       <c r="O63">
-        <v>-12.517872525</v>
+        <v>-12.83558355</v>
       </c>
       <c r="P63">
-        <v>-87.62510767500001</v>
+        <v>-89.84908485</v>
       </c>
       <c r="Q63">
-        <v>-50.32510767500001</v>
+        <v>-52.54908485</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1342567935612007</v>
+        <v>0.1365846039180744</v>
       </c>
       <c r="T63">
-        <v>1.724187551051075</v>
+        <v>1.769560907657683</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04426192008917538</v>
+        <v>0.0435480181522532</v>
       </c>
       <c r="W63">
-        <v>0.2253630392429725</v>
+        <v>0.2255313773196987</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.354095360713403</v>
+        <v>0.3483841452180256</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1917316034270815</v>
+        <v>0.1936316034270815</v>
       </c>
       <c r="C64">
-        <v>-138.0933070750191</v>
+        <v>-152.6477608848014</v>
       </c>
       <c r="D64">
-        <v>372.1046929249809</v>
+        <v>368.3292391151987</v>
       </c>
       <c r="E64">
-        <v>284.898</v>
+        <v>295.6770000000001</v>
       </c>
       <c r="F64">
-        <v>668.298</v>
+        <v>679.0770000000001</v>
       </c>
       <c r="G64">
         <v>158.1</v>
@@ -6535,37 +6535,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M64">
-        <v>157.5846684</v>
+        <v>160.1263566</v>
       </c>
       <c r="N64">
-        <v>-102.6846684</v>
+        <v>-105.2263566</v>
       </c>
       <c r="O64">
-        <v>-12.83558355</v>
+        <v>-13.153294575</v>
       </c>
       <c r="P64">
-        <v>-89.84908485</v>
+        <v>-92.07306202500003</v>
       </c>
       <c r="Q64">
-        <v>-52.54908485</v>
+        <v>-54.77306202500003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1365846039180744</v>
+        <v>0.1390382418618062</v>
       </c>
       <c r="T64">
-        <v>1.769560907657683</v>
+        <v>1.817386878134917</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0435480181522532</v>
+        <v>0.04285677976888409</v>
       </c>
       <c r="W64">
-        <v>0.2255313773196987</v>
+        <v>0.2256943713304971</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3483841452180256</v>
+        <v>0.3428542381510727</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1936316034270815</v>
+        <v>0.1955316034270815</v>
       </c>
       <c r="C65">
-        <v>-152.6477608848014</v>
+        <v>-167.1263710960664</v>
       </c>
       <c r="D65">
-        <v>368.3292391151987</v>
+        <v>364.6296289039338</v>
       </c>
       <c r="E65">
-        <v>295.6770000000001</v>
+        <v>306.4560000000001</v>
       </c>
       <c r="F65">
-        <v>679.0770000000001</v>
+        <v>689.8560000000001</v>
       </c>
       <c r="G65">
         <v>158.1</v>
@@ -6617,37 +6617,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M65">
-        <v>160.1263566</v>
+        <v>162.6680448</v>
       </c>
       <c r="N65">
-        <v>-105.2263566</v>
+        <v>-107.7680448</v>
       </c>
       <c r="O65">
-        <v>-13.153294575</v>
+        <v>-13.4710056</v>
       </c>
       <c r="P65">
-        <v>-92.07306202500003</v>
+        <v>-94.29703920000001</v>
       </c>
       <c r="Q65">
-        <v>-54.77306202500003</v>
+        <v>-56.99703920000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1390382418618062</v>
+        <v>0.1416281930246341</v>
       </c>
       <c r="T65">
-        <v>1.817386878134917</v>
+        <v>1.867869846971998</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04285677976888409</v>
+        <v>0.04218714258499528</v>
       </c>
       <c r="W65">
-        <v>0.2256943713304971</v>
+        <v>0.2258522717784581</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3428542381510727</v>
+        <v>0.3374971406799623</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1955316034270815</v>
+        <v>0.1974316034270815</v>
       </c>
       <c r="C66">
-        <v>-167.1263710960664</v>
+        <v>-181.5314003700458</v>
       </c>
       <c r="D66">
-        <v>364.6296289039338</v>
+        <v>361.0035996299542</v>
       </c>
       <c r="E66">
-        <v>306.4560000000001</v>
+        <v>317.2350000000001</v>
       </c>
       <c r="F66">
-        <v>689.8560000000001</v>
+        <v>700.6350000000001</v>
       </c>
       <c r="G66">
         <v>158.1</v>
@@ -6699,37 +6699,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M66">
-        <v>162.6680448</v>
+        <v>165.209733</v>
       </c>
       <c r="N66">
-        <v>-107.7680448</v>
+        <v>-110.309733</v>
       </c>
       <c r="O66">
-        <v>-13.4710056</v>
+        <v>-13.788716625</v>
       </c>
       <c r="P66">
-        <v>-94.29703920000001</v>
+        <v>-96.52101637500002</v>
       </c>
       <c r="Q66">
-        <v>-56.99703920000002</v>
+        <v>-59.22101637500002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1416281930246341</v>
+        <v>0.1443661413967665</v>
       </c>
       <c r="T66">
-        <v>1.867869846971998</v>
+        <v>1.921237556885484</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04218714258499528</v>
+        <v>0.0415381096221492</v>
       </c>
       <c r="W66">
-        <v>0.2258522717784581</v>
+        <v>0.2260053137510972</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3374971406799623</v>
+        <v>0.3323048769771936</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1974316034270815</v>
+        <v>0.1993316034270814</v>
       </c>
       <c r="C67">
-        <v>-181.5314003700458</v>
+        <v>-195.8650222507987</v>
       </c>
       <c r="D67">
-        <v>361.0035996299542</v>
+        <v>357.4489777492014</v>
       </c>
       <c r="E67">
-        <v>317.2350000000001</v>
+        <v>328.0140000000001</v>
       </c>
       <c r="F67">
-        <v>700.6350000000001</v>
+        <v>711.4140000000001</v>
       </c>
       <c r="G67">
         <v>158.1</v>
@@ -6781,37 +6781,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M67">
-        <v>165.209733</v>
+        <v>167.7514212</v>
       </c>
       <c r="N67">
-        <v>-110.309733</v>
+        <v>-112.8514212</v>
       </c>
       <c r="O67">
-        <v>-13.788716625</v>
+        <v>-14.10642765</v>
       </c>
       <c r="P67">
-        <v>-96.52101637500002</v>
+        <v>-98.74499355000003</v>
       </c>
       <c r="Q67">
-        <v>-59.22101637500002</v>
+        <v>-61.44499355000004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1443661413967665</v>
+        <v>0.1472651455554949</v>
       </c>
       <c r="T67">
-        <v>1.921237556885484</v>
+        <v>1.977744543852704</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0415381096221492</v>
+        <v>0.04090874432484391</v>
       </c>
       <c r="W67">
-        <v>0.2260053137510972</v>
+        <v>0.2261537180882018</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3323048769771936</v>
+        <v>0.3272699545987512</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1993316034270814</v>
+        <v>0.2012316034270815</v>
       </c>
       <c r="C68">
-        <v>-195.8650222507987</v>
+        <v>-210.1293255098907</v>
       </c>
       <c r="D68">
-        <v>357.4489777492014</v>
+        <v>353.9636744901094</v>
       </c>
       <c r="E68">
-        <v>328.0140000000001</v>
+        <v>338.7930000000001</v>
       </c>
       <c r="F68">
-        <v>711.4140000000001</v>
+        <v>722.1930000000001</v>
       </c>
       <c r="G68">
         <v>158.1</v>
@@ -6863,37 +6863,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M68">
-        <v>167.7514212</v>
+        <v>170.2931094</v>
       </c>
       <c r="N68">
-        <v>-112.8514212</v>
+        <v>-115.3931094</v>
       </c>
       <c r="O68">
-        <v>-14.10642765</v>
+        <v>-14.424138675</v>
       </c>
       <c r="P68">
-        <v>-98.74499355000003</v>
+        <v>-100.968970725</v>
       </c>
       <c r="Q68">
-        <v>-61.44499355000004</v>
+        <v>-63.66897072500002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1472651455554949</v>
+        <v>0.1503398469359645</v>
       </c>
       <c r="T68">
-        <v>1.977744543852704</v>
+        <v>2.037676196696725</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04090874432484391</v>
+        <v>0.04029816605133878</v>
       </c>
       <c r="W68">
-        <v>0.2261537180882018</v>
+        <v>0.2262976924450943</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3272699545987512</v>
+        <v>0.3223853284107102</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2012316034270815</v>
+        <v>0.2031316034270815</v>
       </c>
       <c r="C69">
-        <v>-210.1293255098907</v>
+        <v>-224.3263182393542</v>
       </c>
       <c r="D69">
-        <v>353.9636744901094</v>
+        <v>350.5456817606458</v>
       </c>
       <c r="E69">
-        <v>338.7930000000001</v>
+        <v>349.5720000000001</v>
       </c>
       <c r="F69">
-        <v>722.1930000000001</v>
+        <v>732.9720000000001</v>
       </c>
       <c r="G69">
         <v>158.1</v>
@@ -6945,37 +6945,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M69">
-        <v>170.2931094</v>
+        <v>172.8347976</v>
       </c>
       <c r="N69">
-        <v>-115.3931094</v>
+        <v>-117.9347976</v>
       </c>
       <c r="O69">
-        <v>-14.424138675</v>
+        <v>-14.7418497</v>
       </c>
       <c r="P69">
-        <v>-100.968970725</v>
+        <v>-103.1929479</v>
       </c>
       <c r="Q69">
-        <v>-63.66897072500002</v>
+        <v>-65.89294790000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1503398469359645</v>
+        <v>0.1536067171527134</v>
       </c>
       <c r="T69">
-        <v>2.037676196696725</v>
+        <v>2.101353577843498</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04029816605133878</v>
+        <v>0.03970554596234849</v>
       </c>
       <c r="W69">
-        <v>0.2262976924450943</v>
+        <v>0.2264374322620782</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3223853284107102</v>
+        <v>0.317644367698788</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2031316034270815</v>
+        <v>0.2050316034270815</v>
       </c>
       <c r="C70">
-        <v>-224.3263182393542</v>
+        <v>-238.4579317097778</v>
       </c>
       <c r="D70">
-        <v>350.5456817606458</v>
+        <v>347.1930682902223</v>
       </c>
       <c r="E70">
-        <v>349.5720000000001</v>
+        <v>360.3510000000001</v>
       </c>
       <c r="F70">
-        <v>732.9720000000001</v>
+        <v>743.7510000000001</v>
       </c>
       <c r="G70">
         <v>158.1</v>
@@ -7027,37 +7027,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M70">
-        <v>172.8347976</v>
+        <v>175.3764858</v>
       </c>
       <c r="N70">
-        <v>-117.9347976</v>
+        <v>-120.4764858</v>
       </c>
       <c r="O70">
-        <v>-14.7418497</v>
+        <v>-15.059560725</v>
       </c>
       <c r="P70">
-        <v>-103.1929479</v>
+        <v>-105.416925075</v>
       </c>
       <c r="Q70">
-        <v>-65.89294790000002</v>
+        <v>-68.11692507500003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1536067171527134</v>
+        <v>0.1570843531898977</v>
       </c>
       <c r="T70">
-        <v>2.101353577843498</v>
+        <v>2.169139177128772</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03970554596234849</v>
+        <v>0.03913010326724199</v>
       </c>
       <c r="W70">
-        <v>0.2264374322620782</v>
+        <v>0.2265731216495843</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.317644367698788</v>
+        <v>0.3130408261379359</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2050316034270815</v>
+        <v>0.2069316034270815</v>
       </c>
       <c r="C71">
-        <v>-238.4579317097778</v>
+        <v>-252.5260240090993</v>
       </c>
       <c r="D71">
-        <v>347.1930682902223</v>
+        <v>343.9039759909008</v>
       </c>
       <c r="E71">
-        <v>360.3510000000001</v>
+        <v>371.1300000000001</v>
       </c>
       <c r="F71">
-        <v>743.7510000000001</v>
+        <v>754.5300000000001</v>
       </c>
       <c r="G71">
         <v>158.1</v>
@@ -7109,37 +7109,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M71">
-        <v>175.3764858</v>
+        <v>177.918174</v>
       </c>
       <c r="N71">
-        <v>-120.4764858</v>
+        <v>-123.018174</v>
       </c>
       <c r="O71">
-        <v>-15.059560725</v>
+        <v>-15.37727175</v>
       </c>
       <c r="P71">
-        <v>-105.416925075</v>
+        <v>-107.64090225</v>
       </c>
       <c r="Q71">
-        <v>-68.11692507500003</v>
+        <v>-70.34090225000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1570843531898977</v>
+        <v>0.160793831629561</v>
       </c>
       <c r="T71">
-        <v>2.169139177128772</v>
+        <v>2.241443816366398</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03913010326724199</v>
+        <v>0.03857110179199568</v>
       </c>
       <c r="W71">
-        <v>0.2265731216495843</v>
+        <v>0.2267049341974474</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3130408261379359</v>
+        <v>0.3085688143359655</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2069316034270815</v>
+        <v>0.2088316034270815</v>
       </c>
       <c r="C72">
-        <v>-252.5260240090993</v>
+        <v>-266.5323834765113</v>
       </c>
       <c r="D72">
-        <v>343.9039759909008</v>
+        <v>340.6766165234889</v>
       </c>
       <c r="E72">
-        <v>371.1300000000001</v>
+        <v>381.9090000000002</v>
       </c>
       <c r="F72">
-        <v>754.5300000000001</v>
+        <v>765.3090000000002</v>
       </c>
       <c r="G72">
         <v>158.1</v>
@@ -7191,37 +7191,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M72">
-        <v>177.918174</v>
+        <v>180.4598622000001</v>
       </c>
       <c r="N72">
-        <v>-123.018174</v>
+        <v>-125.5598622000001</v>
       </c>
       <c r="O72">
-        <v>-15.37727175</v>
+        <v>-15.69498277500001</v>
       </c>
       <c r="P72">
-        <v>-107.64090225</v>
+        <v>-109.8648794250001</v>
       </c>
       <c r="Q72">
-        <v>-70.34090225000001</v>
+        <v>-72.56487942500006</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.160793831629561</v>
+        <v>0.1647591361685113</v>
       </c>
       <c r="T72">
-        <v>2.241443816366398</v>
+        <v>2.318734982447999</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03857110179199568</v>
+        <v>0.03802784683717884</v>
       </c>
       <c r="W72">
-        <v>0.2267049341974474</v>
+        <v>0.2268330337157932</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3085688143359655</v>
+        <v>0.3042227746974306</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2088316034270815</v>
+        <v>0.2107316034270815</v>
       </c>
       <c r="C73">
-        <v>-266.5323834765112</v>
+        <v>-280.4787319448117</v>
       </c>
       <c r="D73">
-        <v>340.6766165234889</v>
+        <v>337.5092680551884</v>
       </c>
       <c r="E73">
-        <v>381.9090000000001</v>
+        <v>392.6880000000001</v>
       </c>
       <c r="F73">
-        <v>765.3090000000001</v>
+        <v>776.0880000000001</v>
       </c>
       <c r="G73">
         <v>158.1</v>
@@ -7273,37 +7273,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M73">
-        <v>180.4598622</v>
+        <v>183.0015504</v>
       </c>
       <c r="N73">
-        <v>-125.5598622</v>
+        <v>-128.1015504</v>
       </c>
       <c r="O73">
-        <v>-15.694982775</v>
+        <v>-16.0126938</v>
       </c>
       <c r="P73">
-        <v>-109.864879425</v>
+        <v>-112.0888566</v>
       </c>
       <c r="Q73">
-        <v>-72.56487942500003</v>
+        <v>-74.78885660000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1647591361685113</v>
+        <v>0.1690076767459582</v>
       </c>
       <c r="T73">
-        <v>2.318734982447997</v>
+        <v>2.401546946106855</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03802784683717884</v>
+        <v>0.03749968229777358</v>
       </c>
       <c r="W73">
-        <v>0.2268330337157932</v>
+        <v>0.226957574914185</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3042227746974308</v>
+        <v>0.2999974583821887</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2107316034270815</v>
+        <v>0.2126316034270815</v>
       </c>
       <c r="C74">
-        <v>-280.4787319448117</v>
+        <v>-294.3667278035505</v>
       </c>
       <c r="D74">
-        <v>337.5092680551884</v>
+        <v>334.4002721964496</v>
       </c>
       <c r="E74">
-        <v>392.6880000000001</v>
+        <v>403.4670000000001</v>
       </c>
       <c r="F74">
-        <v>776.0880000000001</v>
+        <v>786.8670000000001</v>
       </c>
       <c r="G74">
         <v>158.1</v>
@@ -7355,37 +7355,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M74">
-        <v>183.0015504</v>
+        <v>185.5432386</v>
       </c>
       <c r="N74">
-        <v>-128.1015504</v>
+        <v>-130.6432386</v>
       </c>
       <c r="O74">
-        <v>-16.0126938</v>
+        <v>-16.330404825</v>
       </c>
       <c r="P74">
-        <v>-112.0888566</v>
+        <v>-114.312833775</v>
       </c>
       <c r="Q74">
-        <v>-74.78885660000002</v>
+        <v>-77.01283377500002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1690076767459582</v>
+        <v>0.1735709240328455</v>
       </c>
       <c r="T74">
-        <v>2.401546946106855</v>
+        <v>2.490493129295997</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03749968229777358</v>
+        <v>0.03698598801972189</v>
       </c>
       <c r="W74">
-        <v>0.226957574914185</v>
+        <v>0.2270787040249496</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2999974583821887</v>
+        <v>0.2958879041577751</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2126316034270815</v>
+        <v>0.2145316034270815</v>
       </c>
       <c r="C75">
-        <v>-294.3667278035505</v>
+        <v>-308.1979688944234</v>
       </c>
       <c r="D75">
-        <v>334.4002721964496</v>
+        <v>331.3480311055767</v>
       </c>
       <c r="E75">
-        <v>403.4670000000001</v>
+        <v>414.2460000000001</v>
       </c>
       <c r="F75">
-        <v>786.8670000000001</v>
+        <v>797.6460000000001</v>
       </c>
       <c r="G75">
         <v>158.1</v>
@@ -7437,37 +7437,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M75">
-        <v>185.5432386</v>
+        <v>188.0849268</v>
       </c>
       <c r="N75">
-        <v>-130.6432386</v>
+        <v>-133.1849268</v>
       </c>
       <c r="O75">
-        <v>-16.330404825</v>
+        <v>-16.64811585</v>
       </c>
       <c r="P75">
-        <v>-114.312833775</v>
+        <v>-116.53681095</v>
       </c>
       <c r="Q75">
-        <v>-77.01283377500002</v>
+        <v>-79.23681095000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1735709240328455</v>
+        <v>0.1784851903418011</v>
       </c>
       <c r="T75">
-        <v>2.490493129295997</v>
+        <v>2.586281326576613</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03698598801972189</v>
+        <v>0.03648617737080673</v>
       </c>
       <c r="W75">
-        <v>0.2270787040249496</v>
+        <v>0.2271965593759638</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2958879041577751</v>
+        <v>0.2918894189664538</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2145316034270815</v>
+        <v>0.2164316034270815</v>
       </c>
       <c r="C76">
-        <v>-308.1979688944234</v>
+        <v>-321.9739952495337</v>
       </c>
       <c r="D76">
-        <v>331.3480311055767</v>
+        <v>328.3510047504664</v>
       </c>
       <c r="E76">
-        <v>414.2460000000001</v>
+        <v>425.0250000000001</v>
       </c>
       <c r="F76">
-        <v>797.6460000000001</v>
+        <v>808.4250000000001</v>
       </c>
       <c r="G76">
         <v>158.1</v>
@@ -7519,37 +7519,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M76">
-        <v>188.0849268</v>
+        <v>190.626615</v>
       </c>
       <c r="N76">
-        <v>-133.1849268</v>
+        <v>-135.726615</v>
       </c>
       <c r="O76">
-        <v>-16.64811585</v>
+        <v>-16.965826875</v>
       </c>
       <c r="P76">
-        <v>-116.53681095</v>
+        <v>-118.760788125</v>
       </c>
       <c r="Q76">
-        <v>-79.23681095000002</v>
+        <v>-81.46078812500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1784851903418011</v>
+        <v>0.1837925979554731</v>
       </c>
       <c r="T76">
-        <v>2.586281326576613</v>
+        <v>2.689732579639677</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03648617737080673</v>
+        <v>0.03599969500586264</v>
       </c>
       <c r="W76">
-        <v>0.2271965593759638</v>
+        <v>0.2273112719176176</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2918894189664538</v>
+        <v>0.2879975600469011</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2164316034270815</v>
+        <v>0.2183316034270815</v>
       </c>
       <c r="C77">
-        <v>-321.9739952495337</v>
+        <v>-335.6962916823807</v>
       </c>
       <c r="D77">
-        <v>328.3510047504664</v>
+        <v>325.4077083176194</v>
       </c>
       <c r="E77">
-        <v>425.0250000000001</v>
+        <v>435.8040000000001</v>
       </c>
       <c r="F77">
-        <v>808.4250000000001</v>
+        <v>819.2040000000001</v>
       </c>
       <c r="G77">
         <v>158.1</v>
@@ -7601,37 +7601,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M77">
-        <v>190.626615</v>
+        <v>193.1683032</v>
       </c>
       <c r="N77">
-        <v>-135.726615</v>
+        <v>-138.2683032</v>
       </c>
       <c r="O77">
-        <v>-16.965826875</v>
+        <v>-17.2835379</v>
       </c>
       <c r="P77">
-        <v>-118.760788125</v>
+        <v>-120.9847653</v>
       </c>
       <c r="Q77">
-        <v>-81.46078812500001</v>
+        <v>-83.68476530000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1837925979554731</v>
+        <v>0.1895422895369512</v>
       </c>
       <c r="T77">
-        <v>2.689732579639677</v>
+        <v>2.801804770457997</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03599969500586264</v>
+        <v>0.03552601480841708</v>
       </c>
       <c r="W77">
-        <v>0.2273112719176176</v>
+        <v>0.2274229657081752</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2879975600469011</v>
+        <v>0.2842081184673366</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2183316034270815</v>
+        <v>0.2202316034270815</v>
       </c>
       <c r="C78">
-        <v>-335.6962916823807</v>
+        <v>-349.3662902407357</v>
       </c>
       <c r="D78">
-        <v>325.4077083176194</v>
+        <v>322.5167097592644</v>
       </c>
       <c r="E78">
-        <v>435.8040000000001</v>
+        <v>446.5830000000001</v>
       </c>
       <c r="F78">
-        <v>819.2040000000001</v>
+        <v>829.9830000000001</v>
       </c>
       <c r="G78">
         <v>158.1</v>
@@ -7683,37 +7683,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M78">
-        <v>193.1683032</v>
+        <v>195.7099914</v>
       </c>
       <c r="N78">
-        <v>-138.2683032</v>
+        <v>-140.8099914</v>
       </c>
       <c r="O78">
-        <v>-17.2835379</v>
+        <v>-17.601248925</v>
       </c>
       <c r="P78">
-        <v>-120.9847653</v>
+        <v>-123.208742475</v>
       </c>
       <c r="Q78">
-        <v>-83.68476530000002</v>
+        <v>-85.90874247500003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1895422895369512</v>
+        <v>0.1957919542994273</v>
       </c>
       <c r="T78">
-        <v>2.801804770457997</v>
+        <v>2.923622369173562</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03552601480841708</v>
+        <v>0.03506463799272334</v>
       </c>
       <c r="W78">
-        <v>0.2274229657081752</v>
+        <v>0.2275317583613159</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2842081184673366</v>
+        <v>0.2805171039417867</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2202316034270815</v>
+        <v>0.2221316034270815</v>
       </c>
       <c r="C79">
-        <v>-349.3662902407357</v>
+        <v>-362.9853725299165</v>
       </c>
       <c r="D79">
-        <v>322.5167097592644</v>
+        <v>319.6766274700836</v>
       </c>
       <c r="E79">
-        <v>446.5830000000001</v>
+        <v>457.3620000000001</v>
       </c>
       <c r="F79">
-        <v>829.9830000000001</v>
+        <v>840.7620000000001</v>
       </c>
       <c r="G79">
         <v>158.1</v>
@@ -7765,37 +7765,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M79">
-        <v>195.7099914</v>
+        <v>198.2516796</v>
       </c>
       <c r="N79">
-        <v>-140.8099914</v>
+        <v>-143.3516796</v>
       </c>
       <c r="O79">
-        <v>-17.601248925</v>
+        <v>-17.91895995</v>
       </c>
       <c r="P79">
-        <v>-123.208742475</v>
+        <v>-125.43271965</v>
       </c>
       <c r="Q79">
-        <v>-85.90874247500003</v>
+        <v>-88.13271965000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1957919542994273</v>
+        <v>0.2026097704039468</v>
       </c>
       <c r="T79">
-        <v>2.923622369173562</v>
+        <v>3.056514295045088</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03506463799272334</v>
+        <v>0.034615091351791</v>
       </c>
       <c r="W79">
-        <v>0.2275317583613159</v>
+        <v>0.2276377614592477</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2805171039417867</v>
+        <v>0.276920730814328</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2221316034270815</v>
+        <v>0.2240316034270815</v>
       </c>
       <c r="C80">
-        <v>-362.9853725299165</v>
+        <v>-376.5548719143819</v>
       </c>
       <c r="D80">
-        <v>319.6766274700836</v>
+        <v>316.8861280856182</v>
       </c>
       <c r="E80">
-        <v>457.3620000000001</v>
+        <v>468.1410000000001</v>
       </c>
       <c r="F80">
-        <v>840.7620000000001</v>
+        <v>851.5410000000001</v>
       </c>
       <c r="G80">
         <v>158.1</v>
@@ -7847,37 +7847,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M80">
-        <v>198.2516796</v>
+        <v>200.7933678</v>
       </c>
       <c r="N80">
-        <v>-143.3516796</v>
+        <v>-145.8933678</v>
       </c>
       <c r="O80">
-        <v>-17.91895995</v>
+        <v>-18.236670975</v>
       </c>
       <c r="P80">
-        <v>-125.43271965</v>
+        <v>-127.656696825</v>
       </c>
       <c r="Q80">
-        <v>-88.13271965000001</v>
+        <v>-90.35669682500001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2026097704039468</v>
+        <v>0.2100769023279442</v>
       </c>
       <c r="T80">
-        <v>3.056514295045088</v>
+        <v>3.20206259480914</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.034615091351791</v>
+        <v>0.03417692563847718</v>
       </c>
       <c r="W80">
-        <v>0.2276377614592477</v>
+        <v>0.2277410809344471</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.276920730814328</v>
+        <v>0.2734154051078175</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2240316034270815</v>
+        <v>0.2259316034270815</v>
       </c>
       <c r="C81">
-        <v>-376.5548719143819</v>
+        <v>-390.0760756050155</v>
       </c>
       <c r="D81">
-        <v>316.8861280856182</v>
+        <v>314.1439243949847</v>
       </c>
       <c r="E81">
-        <v>468.1410000000001</v>
+        <v>478.9200000000002</v>
       </c>
       <c r="F81">
-        <v>851.5410000000001</v>
+        <v>862.3200000000002</v>
       </c>
       <c r="G81">
         <v>158.1</v>
@@ -7929,37 +7929,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M81">
-        <v>200.7933678</v>
+        <v>203.335056</v>
       </c>
       <c r="N81">
-        <v>-145.8933678</v>
+        <v>-148.435056</v>
       </c>
       <c r="O81">
-        <v>-18.236670975</v>
+        <v>-18.554382</v>
       </c>
       <c r="P81">
-        <v>-127.656696825</v>
+        <v>-129.880674</v>
       </c>
       <c r="Q81">
-        <v>-90.35669682500001</v>
+        <v>-92.58067400000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2100769023279442</v>
+        <v>0.2182907474443414</v>
       </c>
       <c r="T81">
-        <v>3.20206259480914</v>
+        <v>3.362165724549597</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03417692563847718</v>
+        <v>0.03374971406799622</v>
       </c>
       <c r="W81">
-        <v>0.2277410809344471</v>
+        <v>0.2278418174227665</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2734154051078175</v>
+        <v>0.2699977125439698</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2259316034270815</v>
+        <v>0.2278316034270815</v>
       </c>
       <c r="C82">
-        <v>-390.0760756050155</v>
+        <v>-403.5502266389642</v>
       </c>
       <c r="D82">
-        <v>314.1439243949847</v>
+        <v>311.448773361036</v>
       </c>
       <c r="E82">
-        <v>478.9200000000002</v>
+        <v>489.6990000000002</v>
       </c>
       <c r="F82">
-        <v>862.3200000000002</v>
+        <v>873.0990000000002</v>
       </c>
       <c r="G82">
         <v>158.1</v>
@@ -8011,37 +8011,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M82">
-        <v>203.335056</v>
+        <v>205.8767442</v>
       </c>
       <c r="N82">
-        <v>-148.435056</v>
+        <v>-150.9767442</v>
       </c>
       <c r="O82">
-        <v>-18.554382</v>
+        <v>-18.87209302500001</v>
       </c>
       <c r="P82">
-        <v>-129.880674</v>
+        <v>-132.104651175</v>
       </c>
       <c r="Q82">
-        <v>-92.58067400000003</v>
+        <v>-94.80465117500005</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2182907474443414</v>
+        <v>0.2273692078361489</v>
       </c>
       <c r="T82">
-        <v>3.362165724549597</v>
+        <v>3.539121815315366</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03374971406799622</v>
+        <v>0.03333305093135429</v>
       </c>
       <c r="W82">
-        <v>0.2278418174227665</v>
+        <v>0.2279400665903867</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2699977125439698</v>
+        <v>0.2666644074508343</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2278316034270815</v>
+        <v>0.2297316034270815</v>
       </c>
       <c r="C83">
-        <v>-403.5502266389642</v>
+        <v>-416.9785257584294</v>
       </c>
       <c r="D83">
-        <v>311.448773361036</v>
+        <v>308.7994742415707</v>
       </c>
       <c r="E83">
-        <v>489.6990000000002</v>
+        <v>500.4780000000002</v>
       </c>
       <c r="F83">
-        <v>873.0990000000002</v>
+        <v>883.8780000000002</v>
       </c>
       <c r="G83">
         <v>158.1</v>
@@ -8093,37 +8093,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M83">
-        <v>205.8767442</v>
+        <v>208.4184324000001</v>
       </c>
       <c r="N83">
-        <v>-150.9767442</v>
+        <v>-153.5184324000001</v>
       </c>
       <c r="O83">
-        <v>-18.87209302500001</v>
+        <v>-19.18980405000001</v>
       </c>
       <c r="P83">
-        <v>-132.104651175</v>
+        <v>-134.32862835</v>
       </c>
       <c r="Q83">
-        <v>-94.80465117500005</v>
+        <v>-97.02862835000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2273692078361489</v>
+        <v>0.2374563860492683</v>
       </c>
       <c r="T83">
-        <v>3.539121815315366</v>
+        <v>3.735739693943998</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03333305093135429</v>
+        <v>0.03292655031024021</v>
       </c>
       <c r="W83">
-        <v>0.2279400665903867</v>
+        <v>0.2280359194368454</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2666644074508343</v>
+        <v>0.2634124024819217</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2297316034270815</v>
+        <v>0.2316316034270815</v>
       </c>
       <c r="C84">
-        <v>-416.9785257584294</v>
+        <v>-430.362133194377</v>
       </c>
       <c r="D84">
-        <v>308.7994742415707</v>
+        <v>306.1948668056232</v>
       </c>
       <c r="E84">
-        <v>500.4780000000002</v>
+        <v>511.2570000000002</v>
       </c>
       <c r="F84">
-        <v>883.8780000000002</v>
+        <v>894.6570000000002</v>
       </c>
       <c r="G84">
         <v>158.1</v>
@@ -8175,37 +8175,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M84">
-        <v>208.4184324000001</v>
+        <v>210.9601206</v>
       </c>
       <c r="N84">
-        <v>-153.5184324000001</v>
+        <v>-156.0601206</v>
       </c>
       <c r="O84">
-        <v>-19.18980405000001</v>
+        <v>-19.507515075</v>
       </c>
       <c r="P84">
-        <v>-134.32862835</v>
+        <v>-136.552605525</v>
       </c>
       <c r="Q84">
-        <v>-97.02862835000003</v>
+        <v>-99.25260552500002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2374563860492683</v>
+        <v>0.24873029111099</v>
       </c>
       <c r="T84">
-        <v>3.735739693943998</v>
+        <v>3.955489087705409</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03292655031024021</v>
+        <v>0.03252984488481563</v>
       </c>
       <c r="W84">
-        <v>0.2280359194368454</v>
+        <v>0.2281294625761605</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2634124024819217</v>
+        <v>0.2602387590785251</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2316316034270815</v>
+        <v>0.2335316034270815</v>
       </c>
       <c r="C85">
-        <v>-430.362133194377</v>
+        <v>-443.7021703607322</v>
       </c>
       <c r="D85">
-        <v>306.1948668056232</v>
+        <v>303.6338296392679</v>
       </c>
       <c r="E85">
-        <v>511.2570000000002</v>
+        <v>522.0360000000002</v>
       </c>
       <c r="F85">
-        <v>894.6570000000002</v>
+        <v>905.4360000000001</v>
       </c>
       <c r="G85">
         <v>158.1</v>
@@ -8257,37 +8257,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M85">
-        <v>210.9601206</v>
+        <v>213.5018088</v>
       </c>
       <c r="N85">
-        <v>-156.0601206</v>
+        <v>-158.6018088</v>
       </c>
       <c r="O85">
-        <v>-19.507515075</v>
+        <v>-19.82522610000001</v>
       </c>
       <c r="P85">
-        <v>-136.552605525</v>
+        <v>-138.7765827</v>
       </c>
       <c r="Q85">
-        <v>-99.25260552500002</v>
+        <v>-101.4765827</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.24873029111099</v>
+        <v>0.2614134343054269</v>
       </c>
       <c r="T85">
-        <v>3.955489087705409</v>
+        <v>4.202707155686998</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03252984488481563</v>
+        <v>0.03214258482666307</v>
       </c>
       <c r="W85">
-        <v>0.2281294625761605</v>
+        <v>0.2282207784978728</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2602387590785251</v>
+        <v>0.2571406786133046</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2335316034270815</v>
+        <v>0.2354316034270814</v>
       </c>
       <c r="C86">
-        <v>-443.7021703607321</v>
+        <v>-456.9997214642588</v>
       </c>
       <c r="D86">
-        <v>303.6338296392679</v>
+        <v>301.1152785357413</v>
       </c>
       <c r="E86">
-        <v>522.0360000000001</v>
+        <v>532.8150000000001</v>
       </c>
       <c r="F86">
-        <v>905.436</v>
+        <v>916.215</v>
       </c>
       <c r="G86">
         <v>158.1</v>
@@ -8339,37 +8339,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M86">
-        <v>213.5018088</v>
+        <v>216.043497</v>
       </c>
       <c r="N86">
-        <v>-158.6018088</v>
+        <v>-161.143497</v>
       </c>
       <c r="O86">
-        <v>-19.8252261</v>
+        <v>-20.142937125</v>
       </c>
       <c r="P86">
-        <v>-138.7765827</v>
+        <v>-141.000559875</v>
       </c>
       <c r="Q86">
-        <v>-101.4765827</v>
+        <v>-103.700559875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2614134343054267</v>
+        <v>0.2757876632591218</v>
       </c>
       <c r="T86">
-        <v>4.202707155686995</v>
+        <v>4.482887632732795</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03214258482666307</v>
+        <v>0.0317644367698788</v>
       </c>
       <c r="W86">
-        <v>0.2282207784978728</v>
+        <v>0.2283099458096626</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2571406786133046</v>
+        <v>0.2541154941590305</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2354316034270814</v>
+        <v>0.2373316034270815</v>
       </c>
       <c r="C87">
-        <v>-456.9997214642588</v>
+        <v>-470.2558350349746</v>
       </c>
       <c r="D87">
-        <v>301.1152785357413</v>
+        <v>298.6381649650255</v>
       </c>
       <c r="E87">
-        <v>532.8150000000001</v>
+        <v>543.5940000000001</v>
       </c>
       <c r="F87">
-        <v>916.215</v>
+        <v>926.994</v>
       </c>
       <c r="G87">
         <v>158.1</v>
@@ -8421,37 +8421,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M87">
-        <v>216.043497</v>
+        <v>218.5851852</v>
       </c>
       <c r="N87">
-        <v>-161.143497</v>
+        <v>-163.6851852</v>
       </c>
       <c r="O87">
-        <v>-20.142937125</v>
+        <v>-20.46064815</v>
       </c>
       <c r="P87">
-        <v>-141.000559875</v>
+        <v>-143.22453705</v>
       </c>
       <c r="Q87">
-        <v>-103.700559875</v>
+        <v>-105.92453705</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2757876632591218</v>
+        <v>0.2922153534919162</v>
       </c>
       <c r="T87">
-        <v>4.482887632732795</v>
+        <v>4.803093892213709</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0317644367698788</v>
+        <v>0.03139508285394998</v>
       </c>
       <c r="W87">
-        <v>0.2283099458096626</v>
+        <v>0.2283970394630386</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2541154941590305</v>
+        <v>0.2511606628315998</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2373316034270815</v>
+        <v>0.2392316034270815</v>
       </c>
       <c r="C88">
-        <v>-470.2558350349746</v>
+        <v>-483.4715253816454</v>
       </c>
       <c r="D88">
-        <v>298.6381649650255</v>
+        <v>296.2014746183546</v>
       </c>
       <c r="E88">
-        <v>543.5940000000001</v>
+        <v>554.373</v>
       </c>
       <c r="F88">
-        <v>926.994</v>
+        <v>937.773</v>
       </c>
       <c r="G88">
         <v>158.1</v>
@@ -8503,37 +8503,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M88">
-        <v>218.5851852</v>
+        <v>221.1268734</v>
       </c>
       <c r="N88">
-        <v>-163.6851852</v>
+        <v>-166.2268734</v>
       </c>
       <c r="O88">
-        <v>-20.46064815</v>
+        <v>-20.778359175</v>
       </c>
       <c r="P88">
-        <v>-143.22453705</v>
+        <v>-145.448514225</v>
       </c>
       <c r="Q88">
-        <v>-105.92453705</v>
+        <v>-108.148514225</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2922153534919162</v>
+        <v>0.3111703806836021</v>
       </c>
       <c r="T88">
-        <v>4.803093892213709</v>
+        <v>5.172562653153226</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03139508285394998</v>
+        <v>0.03103421983264021</v>
       </c>
       <c r="W88">
-        <v>0.2283970394630386</v>
+        <v>0.2284821309634635</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2511606628315998</v>
+        <v>0.2482737586611217</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2392316034270815</v>
+        <v>0.2411316034270815</v>
       </c>
       <c r="C89">
-        <v>-483.4715253816454</v>
+        <v>-496.6477739766003</v>
       </c>
       <c r="D89">
-        <v>296.2014746183546</v>
+        <v>293.8042260233998</v>
       </c>
       <c r="E89">
-        <v>554.373</v>
+        <v>565.1520000000002</v>
       </c>
       <c r="F89">
-        <v>937.773</v>
+        <v>948.5520000000001</v>
       </c>
       <c r="G89">
         <v>158.1</v>
@@ -8585,37 +8585,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M89">
-        <v>221.1268734</v>
+        <v>223.6685616</v>
       </c>
       <c r="N89">
-        <v>-166.2268734</v>
+        <v>-168.7685616</v>
       </c>
       <c r="O89">
-        <v>-20.778359175</v>
+        <v>-21.0960702</v>
       </c>
       <c r="P89">
-        <v>-145.448514225</v>
+        <v>-147.6724914</v>
       </c>
       <c r="Q89">
-        <v>-108.148514225</v>
+        <v>-110.3724914</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3111703806836021</v>
+        <v>0.3332845790739023</v>
       </c>
       <c r="T89">
-        <v>5.172562653153226</v>
+        <v>5.603609540915994</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03103421983264021</v>
+        <v>0.03068155824363293</v>
       </c>
       <c r="W89">
-        <v>0.2284821309634635</v>
+        <v>0.2285652885661514</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2482737586611217</v>
+        <v>0.2454524659490634</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2411316034270815</v>
+        <v>0.2430316034270815</v>
       </c>
       <c r="C90">
-        <v>-496.6477739766003</v>
+        <v>-509.7855307738399</v>
       </c>
       <c r="D90">
-        <v>293.8042260233998</v>
+        <v>291.4454692261602</v>
       </c>
       <c r="E90">
-        <v>565.1520000000002</v>
+        <v>575.9310000000002</v>
       </c>
       <c r="F90">
-        <v>948.5520000000001</v>
+        <v>959.3310000000001</v>
       </c>
       <c r="G90">
         <v>158.1</v>
@@ -8667,37 +8667,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M90">
-        <v>223.6685616</v>
+        <v>226.2102498</v>
       </c>
       <c r="N90">
-        <v>-168.7685616</v>
+        <v>-171.3102498</v>
       </c>
       <c r="O90">
-        <v>-21.0960702</v>
+        <v>-21.413781225</v>
       </c>
       <c r="P90">
-        <v>-147.6724914</v>
+        <v>-149.896468575</v>
       </c>
       <c r="Q90">
-        <v>-110.3724914</v>
+        <v>-112.596468575</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3332845790739023</v>
+        <v>0.3594195408078935</v>
       </c>
       <c r="T90">
-        <v>5.603609540915994</v>
+        <v>6.113028590090177</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03068155824363293</v>
+        <v>0.03033682163415391</v>
       </c>
       <c r="W90">
-        <v>0.2285652885661514</v>
+        <v>0.2286465774586665</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2454524659490634</v>
+        <v>0.2426945730732313</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2430316034270815</v>
+        <v>0.2449316034270815</v>
       </c>
       <c r="C91">
-        <v>-509.7855307738399</v>
+        <v>-522.8857154641566</v>
       </c>
       <c r="D91">
-        <v>291.4454692261602</v>
+        <v>289.1242845358435</v>
       </c>
       <c r="E91">
-        <v>575.9310000000002</v>
+        <v>586.7100000000002</v>
       </c>
       <c r="F91">
-        <v>959.3310000000001</v>
+        <v>970.1100000000001</v>
       </c>
       <c r="G91">
         <v>158.1</v>
@@ -8749,37 +8749,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M91">
-        <v>226.2102498</v>
+        <v>228.7519380000001</v>
       </c>
       <c r="N91">
-        <v>-171.3102498</v>
+        <v>-173.851938</v>
       </c>
       <c r="O91">
-        <v>-21.413781225</v>
+        <v>-21.73149225000001</v>
       </c>
       <c r="P91">
-        <v>-149.896468575</v>
+        <v>-152.12044575</v>
       </c>
       <c r="Q91">
-        <v>-112.596468575</v>
+        <v>-114.82044575</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3594195408078935</v>
+        <v>0.3907814948886828</v>
       </c>
       <c r="T91">
-        <v>6.113028590090177</v>
+        <v>6.724331449099194</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03033682163415391</v>
+        <v>0.02999974583821886</v>
       </c>
       <c r="W91">
-        <v>0.2286465774586665</v>
+        <v>0.228726059931348</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2426945730732313</v>
+        <v>0.2399979667057509</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2449316034270815</v>
+        <v>0.2468316034270815</v>
       </c>
       <c r="C92">
-        <v>-522.8857154641566</v>
+        <v>-535.9492186707535</v>
       </c>
       <c r="D92">
-        <v>289.1242845358435</v>
+        <v>286.8397813292466</v>
       </c>
       <c r="E92">
-        <v>586.7100000000002</v>
+        <v>597.4890000000001</v>
       </c>
       <c r="F92">
-        <v>970.1100000000001</v>
+        <v>980.8890000000001</v>
       </c>
       <c r="G92">
         <v>158.1</v>
@@ -8831,37 +8831,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M92">
-        <v>228.7519380000001</v>
+        <v>231.2936262</v>
       </c>
       <c r="N92">
-        <v>-173.851938</v>
+        <v>-176.3936262</v>
       </c>
       <c r="O92">
-        <v>-21.73149225000001</v>
+        <v>-22.049203275</v>
       </c>
       <c r="P92">
-        <v>-152.12044575</v>
+        <v>-154.344422925</v>
       </c>
       <c r="Q92">
-        <v>-114.82044575</v>
+        <v>-117.044422925</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3907814948886828</v>
+        <v>0.4291127720985365</v>
       </c>
       <c r="T92">
-        <v>6.724331449099194</v>
+        <v>7.471479387887995</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02999974583821886</v>
+        <v>0.02967007830153514</v>
       </c>
       <c r="W92">
-        <v>0.228726059931348</v>
+        <v>0.228803795536498</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2399979667057509</v>
+        <v>0.2373606264122812</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2468316034270815</v>
+        <v>0.2487316034270815</v>
       </c>
       <c r="C93">
-        <v>-535.9492186707535</v>
+        <v>-548.9769030886215</v>
       </c>
       <c r="D93">
-        <v>286.8397813292466</v>
+        <v>284.5910969113787</v>
       </c>
       <c r="E93">
-        <v>597.4890000000001</v>
+        <v>608.2680000000001</v>
       </c>
       <c r="F93">
-        <v>980.8890000000001</v>
+        <v>991.6680000000001</v>
       </c>
       <c r="G93">
         <v>158.1</v>
@@ -8913,37 +8913,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M93">
-        <v>231.2936262</v>
+        <v>233.8353144</v>
       </c>
       <c r="N93">
-        <v>-176.3936262</v>
+        <v>-178.9353144</v>
       </c>
       <c r="O93">
-        <v>-22.049203275</v>
+        <v>-22.3669143</v>
       </c>
       <c r="P93">
-        <v>-154.344422925</v>
+        <v>-156.5684001</v>
       </c>
       <c r="Q93">
-        <v>-117.044422925</v>
+        <v>-119.2684001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4291127720985365</v>
+        <v>0.4770268686108537</v>
       </c>
       <c r="T93">
-        <v>7.471479387887995</v>
+        <v>8.405414311373995</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02967007830153514</v>
+        <v>0.0293475774504315</v>
       </c>
       <c r="W93">
-        <v>0.228803795536498</v>
+        <v>0.2288798412371883</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2373606264122812</v>
+        <v>0.234780619603452</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487316034270815</v>
+        <v>0.2506316034270815</v>
       </c>
       <c r="C94">
-        <v>-548.9769030886215</v>
+        <v>-561.9696045707427</v>
       </c>
       <c r="D94">
-        <v>284.5910969113787</v>
+        <v>282.3773954292574</v>
       </c>
       <c r="E94">
-        <v>608.2680000000001</v>
+        <v>619.0470000000001</v>
       </c>
       <c r="F94">
-        <v>991.6680000000001</v>
+        <v>1002.447</v>
       </c>
       <c r="G94">
         <v>158.1</v>
@@ -8995,37 +8995,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M94">
-        <v>233.8353144</v>
+        <v>236.3770026</v>
       </c>
       <c r="N94">
-        <v>-178.9353144</v>
+        <v>-181.4770026</v>
       </c>
       <c r="O94">
-        <v>-22.3669143</v>
+        <v>-22.684625325</v>
       </c>
       <c r="P94">
-        <v>-156.5684001</v>
+        <v>-158.792377275</v>
       </c>
       <c r="Q94">
-        <v>-119.2684001</v>
+        <v>-121.492377275</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4770268686108537</v>
+        <v>0.5386307069838329</v>
       </c>
       <c r="T94">
-        <v>8.405414311373995</v>
+        <v>9.606187784427426</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0293475774504315</v>
+        <v>0.02903201210150213</v>
       </c>
       <c r="W94">
-        <v>0.2288798412371883</v>
+        <v>0.2289542515464658</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.234780619603452</v>
+        <v>0.232256096812017</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2506316034270815</v>
+        <v>0.2525316034270815</v>
       </c>
       <c r="C95">
-        <v>-561.9696045707427</v>
+        <v>-574.9281331639904</v>
       </c>
       <c r="D95">
-        <v>282.3773954292574</v>
+        <v>280.1978668360097</v>
       </c>
       <c r="E95">
-        <v>619.0470000000001</v>
+        <v>629.8260000000001</v>
       </c>
       <c r="F95">
-        <v>1002.447</v>
+        <v>1013.226</v>
       </c>
       <c r="G95">
         <v>158.1</v>
@@ -9077,37 +9077,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M95">
-        <v>236.3770026</v>
+        <v>238.9186908</v>
       </c>
       <c r="N95">
-        <v>-181.4770026</v>
+        <v>-184.0186908</v>
       </c>
       <c r="O95">
-        <v>-22.684625325</v>
+        <v>-23.00233635</v>
       </c>
       <c r="P95">
-        <v>-158.792377275</v>
+        <v>-161.01635445</v>
       </c>
       <c r="Q95">
-        <v>-121.492377275</v>
+        <v>-123.71635445</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5386307069838329</v>
+        <v>0.6207691581478052</v>
       </c>
       <c r="T95">
-        <v>9.606187784427426</v>
+        <v>11.207219081832</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02903201210150213</v>
+        <v>0.02872316090893295</v>
       </c>
       <c r="W95">
-        <v>0.2289542515464658</v>
+        <v>0.2290270786576736</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.232256096812017</v>
+        <v>0.2297852872714636</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2525316034270815</v>
+        <v>0.2544316034270815</v>
       </c>
       <c r="C96">
-        <v>-574.9281331639904</v>
+        <v>-587.8532740974222</v>
       </c>
       <c r="D96">
-        <v>280.1978668360097</v>
+        <v>278.051725902578</v>
       </c>
       <c r="E96">
-        <v>629.8260000000001</v>
+        <v>640.6050000000001</v>
       </c>
       <c r="F96">
-        <v>1013.226</v>
+        <v>1024.005</v>
       </c>
       <c r="G96">
         <v>158.1</v>
@@ -9159,37 +9159,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M96">
-        <v>238.9186908</v>
+        <v>241.460379</v>
       </c>
       <c r="N96">
-        <v>-184.0186908</v>
+        <v>-186.560379</v>
       </c>
       <c r="O96">
-        <v>-23.00233635</v>
+        <v>-23.32004737500001</v>
       </c>
       <c r="P96">
-        <v>-161.01635445</v>
+        <v>-163.240331625</v>
       </c>
       <c r="Q96">
-        <v>-123.71635445</v>
+        <v>-125.940331625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6207691581478052</v>
+        <v>0.7357629897773664</v>
       </c>
       <c r="T96">
-        <v>11.207219081832</v>
+        <v>13.44866289819841</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02872316090893295</v>
+        <v>0.02842081184673366</v>
       </c>
       <c r="W96">
-        <v>0.2290270786576736</v>
+        <v>0.2290983725665402</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2297852872714636</v>
+        <v>0.2273664947738693</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2544316034270815</v>
+        <v>0.2563316034270815</v>
       </c>
       <c r="C97">
-        <v>-587.8532740974222</v>
+        <v>-600.7457887255001</v>
       </c>
       <c r="D97">
-        <v>278.051725902578</v>
+        <v>275.9382112745</v>
       </c>
       <c r="E97">
-        <v>640.6050000000001</v>
+        <v>651.3840000000001</v>
       </c>
       <c r="F97">
-        <v>1024.005</v>
+        <v>1034.784</v>
       </c>
       <c r="G97">
         <v>158.1</v>
@@ -9241,37 +9241,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M97">
-        <v>241.460379</v>
+        <v>244.0020672</v>
       </c>
       <c r="N97">
-        <v>-186.560379</v>
+        <v>-189.1020672</v>
       </c>
       <c r="O97">
-        <v>-23.32004737500001</v>
+        <v>-23.6377584</v>
       </c>
       <c r="P97">
-        <v>-163.240331625</v>
+        <v>-165.4643088</v>
       </c>
       <c r="Q97">
-        <v>-125.940331625</v>
+        <v>-128.1643088</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7357629897773664</v>
+        <v>0.9082537372217085</v>
       </c>
       <c r="T97">
-        <v>13.44866289819841</v>
+        <v>16.81082862274802</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02842081184673366</v>
+        <v>0.02812476172333019</v>
       </c>
       <c r="W97">
-        <v>0.2290983725665402</v>
+        <v>0.2291681811856388</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2273664947738693</v>
+        <v>0.2249980937866415</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2563316034270814</v>
+        <v>0.2582316034270815</v>
       </c>
       <c r="C98">
-        <v>-600.7457887255</v>
+        <v>-613.6064154286187</v>
       </c>
       <c r="D98">
-        <v>275.9382112745001</v>
+        <v>273.8565845713814</v>
       </c>
       <c r="E98">
-        <v>651.3840000000001</v>
+        <v>662.1630000000001</v>
       </c>
       <c r="F98">
-        <v>1034.784</v>
+        <v>1045.563</v>
       </c>
       <c r="G98">
         <v>158.1</v>
@@ -9323,37 +9323,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M98">
-        <v>244.0020672</v>
+        <v>246.5437554</v>
       </c>
       <c r="N98">
-        <v>-189.1020672</v>
+        <v>-191.6437554</v>
       </c>
       <c r="O98">
-        <v>-23.6377584</v>
+        <v>-23.955469425</v>
       </c>
       <c r="P98">
-        <v>-165.4643088</v>
+        <v>-167.688285975</v>
       </c>
       <c r="Q98">
-        <v>-128.1643088</v>
+        <v>-130.388285975</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9082537372217062</v>
+        <v>1.195738316295609</v>
       </c>
       <c r="T98">
-        <v>16.81082862274797</v>
+        <v>22.41443816366396</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02812476172333019</v>
+        <v>0.02783481572618245</v>
       </c>
       <c r="W98">
-        <v>0.2291681811856388</v>
+        <v>0.2292365504517662</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2249980937866415</v>
+        <v>0.2226785258094596</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2582316034270815</v>
+        <v>0.2601316034270815</v>
       </c>
       <c r="C99">
-        <v>-613.6064154286187</v>
+        <v>-626.4358704731778</v>
       </c>
       <c r="D99">
-        <v>273.8565845713814</v>
+        <v>271.8061295268223</v>
       </c>
       <c r="E99">
-        <v>662.1630000000001</v>
+        <v>672.9420000000001</v>
       </c>
       <c r="F99">
-        <v>1045.563</v>
+        <v>1056.342</v>
       </c>
       <c r="G99">
         <v>158.1</v>
@@ -9405,37 +9405,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M99">
-        <v>246.5437554</v>
+        <v>249.0854436</v>
       </c>
       <c r="N99">
-        <v>-191.6437554</v>
+        <v>-194.1854436</v>
       </c>
       <c r="O99">
-        <v>-23.955469425</v>
+        <v>-24.27318045</v>
       </c>
       <c r="P99">
-        <v>-167.688285975</v>
+        <v>-169.91226315</v>
       </c>
       <c r="Q99">
-        <v>-130.388285975</v>
+        <v>-132.61226315</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.195738316295609</v>
+        <v>1.770707474443413</v>
       </c>
       <c r="T99">
-        <v>22.41443816366396</v>
+        <v>33.62165724549594</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02783481572618245</v>
+        <v>0.02755078699428263</v>
       </c>
       <c r="W99">
-        <v>0.2292365504517662</v>
+        <v>0.2293035244267482</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2226785258094596</v>
+        <v>0.2204062959542611</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2601316034270815</v>
+        <v>0.2620316034270815</v>
       </c>
       <c r="C100">
-        <v>-626.4358704731778</v>
+        <v>-639.2348488333027</v>
       </c>
       <c r="D100">
-        <v>271.8061295268223</v>
+        <v>269.7861511666974</v>
       </c>
       <c r="E100">
-        <v>672.9420000000001</v>
+        <v>683.7210000000001</v>
       </c>
       <c r="F100">
-        <v>1056.342</v>
+        <v>1067.121</v>
       </c>
       <c r="G100">
         <v>158.1</v>
@@ -9487,37 +9487,37 @@
         <v>54.90000000000001</v>
       </c>
       <c r="M100">
-        <v>249.0854436</v>
+        <v>251.6271318</v>
       </c>
       <c r="N100">
-        <v>-194.1854436</v>
+        <v>-196.7271318</v>
       </c>
       <c r="O100">
-        <v>-24.27318045</v>
+        <v>-24.590891475</v>
       </c>
       <c r="P100">
-        <v>-169.91226315</v>
+        <v>-172.136240325</v>
       </c>
       <c r="Q100">
-        <v>-132.61226315</v>
+        <v>-134.836240325</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.770707474443413</v>
+        <v>3.495614948886825</v>
       </c>
       <c r="T100">
-        <v>33.62165724549594</v>
+        <v>67.24331449099188</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02755078699428263</v>
+        <v>0.0272724962165626</v>
       </c>
       <c r="W100">
-        <v>0.2293035244267482</v>
+        <v>0.2293691453921345</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2204062959542611</v>
+        <v>0.2181799697325009</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2620316034270815</v>
-      </c>
-      <c r="C101">
-        <v>-639.2348488333027</v>
-      </c>
-      <c r="D101">
-        <v>269.7861511666974</v>
-      </c>
-      <c r="E101">
-        <v>683.7210000000001</v>
-      </c>
-      <c r="F101">
-        <v>1067.121</v>
-      </c>
-      <c r="G101">
-        <v>158.1</v>
-      </c>
-      <c r="H101">
-        <v>694.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>92.2</v>
-      </c>
-      <c r="K101">
-        <v>37.3</v>
-      </c>
-      <c r="L101">
-        <v>54.90000000000001</v>
-      </c>
-      <c r="M101">
-        <v>251.6271318</v>
-      </c>
-      <c r="N101">
-        <v>-196.7271318</v>
-      </c>
-      <c r="O101">
-        <v>-24.590891475</v>
-      </c>
-      <c r="P101">
-        <v>-172.136240325</v>
-      </c>
-      <c r="Q101">
-        <v>-134.836240325</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.495614948886825</v>
-      </c>
-      <c r="T101">
-        <v>67.24331449099188</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0272724962165626</v>
-      </c>
-      <c r="W101">
-        <v>0.2293691453921345</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2181799697325009</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
